--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0B5B97-9DDC-4862-8A2E-12080A566FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E85F0DD-A13F-4980-9D95-EA0AAD49D306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -112,9 +112,11 @@
     <externalReference r:id="rId95"/>
     <externalReference r:id="rId96"/>
     <externalReference r:id="rId97"/>
+    <externalReference r:id="rId98"/>
+    <externalReference r:id="rId99"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AE$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AE$183</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -159,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="905">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2309,9 +2311,6 @@
     <t>FQ126</t>
   </si>
   <si>
-    <t>IPO in Q2/Q3 2025 on LSE for 50 b. USD valuation</t>
-  </si>
-  <si>
     <t>Buyer</t>
   </si>
   <si>
@@ -2862,6 +2861,21 @@
   </si>
   <si>
     <t>Q227</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>CPNG</t>
+  </si>
+  <si>
+    <t>Shein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO on </t>
+  </si>
+  <si>
+    <t>0625.HK</t>
   </si>
 </sst>
 </file>
@@ -2875,13 +2889,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3036,6 +3056,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3108,21 +3135,99 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3136,194 +3241,120 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="17" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3418,17 +3449,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>110.86</v>
+            <v>99.65</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>12021.43191302</v>
+            <v>10522.448477600001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1514.729</v>
+            <v>189.73699999999999</v>
           </cell>
         </row>
         <row r="6">
@@ -4138,26 +4169,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>47.12</v>
+            <v>35.46</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>62332.018625043194</v>
+            <v>46907.754253905601</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>25437.420999999998</v>
+            <v>26779.968000000001</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>14701.28</v>
+            <v>197</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4298,22 +4329,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>55</v>
+            <v>54.85</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>171386.35277500001</v>
+            <v>170908.29641415001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>10797</v>
+            <v>10399</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -4399,7 +4430,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4580,26 +4611,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>17550</v>
+            <v>21560</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>32570.869500000001</v>
+            <v>40073.744480000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1577</v>
+            <v>1384</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>2262</v>
+            <v>2565</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5156,17 +5187,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>58.06</v>
+            <v>56.92</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2969.2344415800003</v>
+            <v>2913.9166024800002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>535.35400000000004</v>
+            <v>624.601</v>
           </cell>
         </row>
         <row r="6">
@@ -5175,7 +5206,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5236,22 +5267,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>77.790000000000006</v>
+            <v>72.459999999999994</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>3586.7484766800003</v>
+            <v>3343.1473791799999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>592.5</v>
+            <v>965.9</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2282.3000000000002</v>
+            <v>2236.5</v>
           </cell>
         </row>
       </sheetData>
@@ -5594,22 +5625,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>14.35</v>
+            <v>17.37</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2756.6605860499999</v>
+            <v>2910.7487942100001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>160.19499999999999</v>
+            <v>103.286</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>0</v>
+            <v>85</v>
           </cell>
         </row>
       </sheetData>
@@ -5718,12 +5749,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>74.900000000000006</v>
+            <v>73.62</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>5953.9305021000009</v>
+            <v>5852.1810889800008</v>
           </cell>
         </row>
         <row r="5">
@@ -5838,22 +5869,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>10.61</v>
+            <v>11.0596</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2684.5824118999999</v>
+            <v>2798.3419078839997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>297.553</v>
+            <v>226.715</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>246.18899999999999</v>
+            <v>224.79700000000003</v>
           </cell>
         </row>
       </sheetData>
@@ -6567,6 +6598,46 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Modle"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>48.5</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>26772.307449745003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>15210</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
@@ -6598,7 +6669,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6640,7 +6711,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6682,7 +6753,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6722,7 +6793,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6753,6 +6824,46 @@
         <row r="7">
           <cell r="I7">
             <v>38</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>22.51</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>40518</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6030</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1533</v>
           </cell>
         </row>
       </sheetData>
@@ -7256,10 +7367,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>809</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>810</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>89</v>
@@ -7326,48 +7437,48 @@
         <v>405</v>
       </c>
       <c r="C4" s="15">
-        <f>+COUNTA(C6:C181)</f>
-        <v>176</v>
+        <f>+COUNTA(C6:C183)</f>
+        <v>178</v>
       </c>
       <c r="D4" s="15">
-        <f>+COUNTA(_xlfn.UNIQUE(D6:D181))</f>
-        <v>31</v>
+        <f>+COUNTA(_xlfn.UNIQUE(D6:D183))</f>
+        <v>32</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F4" s="17">
-        <f>SUM(F6:F153)</f>
-        <v>1768001.6271764727</v>
+        <f>SUM(F6:F156)</f>
+        <v>1834524.3301594281</v>
       </c>
       <c r="G4" s="17">
-        <f>SUM(G6:G153)</f>
-        <v>11313.114543799997</v>
+        <f>SUM(G6:G156)</f>
+        <v>-8675.0033961999943</v>
       </c>
       <c r="H4" s="17">
-        <f>SUM(H6:H153)</f>
-        <v>1779314.741720272</v>
+        <f>SUM(H6:H156)</f>
+        <v>1825849.3267632276</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="K4" s="17">
-        <f>SUM(K6:K153)</f>
+        <f>SUM(K6:K156)</f>
         <v>492429.91060000006</v>
       </c>
       <c r="L4" s="18">
-        <f>SUMPRODUCT(L6:L182,K6:K182)/SUM(K6:K1820)</f>
+        <f>SUMPRODUCT(L6:L183,K6:K183)/SUM(K6:K1820)</f>
         <v>3.9002440539402931E-2</v>
       </c>
       <c r="M4" s="17">
-        <f>SUM(M6:M85)</f>
+        <f>SUM(M6:M87)</f>
         <v>86102.331999999995</v>
       </c>
       <c r="N4" s="17">
-        <f>SUM(N6:N85)</f>
+        <f>SUM(N6:N87)</f>
         <v>51484.742999999995</v>
       </c>
       <c r="O4" s="16"/>
@@ -7397,43 +7508,43 @@
         <v>88</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D5" s="82" t="str" cm="1">
-        <f t="array" ref="D5">_xlfn.LET(_xlpm.rng,D6:D182,INDEX(_xlpm.rng,MATCH(MAX(COUNTIF(_xlpm.rng,_xlpm.rng)),COUNTIF(_xlpm.rng,_xlpm.rng),0)))</f>
+        <f t="array" ref="D5">_xlfn.LET(_xlpm.rng,D6:D183,INDEX(_xlpm.rng,MATCH(MAX(COUNTIF(_xlpm.rng,_xlpm.rng)),COUNTIF(_xlpm.rng,_xlpm.rng),0)))</f>
         <v>US</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F5" s="83">
-        <f>+AVERAGE(F6:F181)</f>
-        <v>22405.714040888364</v>
+        <f>+AVERAGE(F6:F183)</f>
+        <v>22653.501309833657</v>
       </c>
       <c r="G5" s="83">
-        <f>AVERAGE(G6:G153)</f>
-        <v>146.92356550389607</v>
+        <f>AVERAGE(G6:G156)</f>
+        <v>-108.43754245249993</v>
       </c>
       <c r="H5" s="83">
-        <f>AVERAGE(H6:H153)</f>
-        <v>23107.98365870483</v>
+        <f>AVERAGE(H6:H156)</f>
+        <v>22823.116584540345</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="K5" s="83">
-        <f>AVERAGE(K6:K153)</f>
+        <f>AVERAGE(K6:K156)</f>
         <v>25917.363715789477</v>
       </c>
       <c r="L5" s="85">
-        <f>AVERAGE(L6:L182)</f>
+        <f>AVERAGE(L6:L183)</f>
         <v>5.8894736842105264E-2</v>
       </c>
       <c r="M5" s="83">
-        <f t="shared" ref="M5:AA5" si="0">AVERAGE(M6:M85)</f>
+        <f t="shared" ref="M5:AA5" si="0">AVERAGE(M6:M87)</f>
         <v>4783.4628888888883</v>
       </c>
       <c r="N5" s="83">
@@ -7530,7 +7641,7 @@
         <v>250961.22150112005</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J6" s="26">
         <v>46308</v>
@@ -7633,7 +7744,7 @@
         <v>156456.45617367997</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J7" s="26">
         <v>46318</v>
@@ -7721,25 +7832,25 @@
       </c>
       <c r="E8" s="24">
         <f>+[3]Main!$J$3</f>
-        <v>55</v>
+        <v>54.85</v>
       </c>
       <c r="F8" s="17">
         <f>+[3]Main!$J$5*FX!C3</f>
-        <v>178241.80688600001</v>
+        <v>177744.62827071603</v>
       </c>
       <c r="G8" s="17">
         <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
-        <v>-11228.880000000001</v>
+        <v>-10813.92</v>
       </c>
       <c r="H8" s="17">
-        <f t="shared" ref="H8:H35" si="1">F8+G8</f>
-        <v>167012.926886</v>
+        <f t="shared" ref="H8:H37" si="1">F8+G8</f>
+        <v>166930.70827071602</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="J8" s="26">
-        <v>46274</v>
+        <v>46358</v>
       </c>
       <c r="K8" s="17">
         <f>35947*FX!C3</f>
@@ -7807,7 +7918,7 @@
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="15">
-        <f t="shared" ref="A9:A72" si="2">+A8+1</f>
+        <f t="shared" ref="A9:A74" si="2">+A8+1</f>
         <v>4</v>
       </c>
       <c r="B9" s="23" t="s">
@@ -7836,7 +7947,7 @@
         <v>154576.23000000001</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="J9" s="26">
         <v>46344</v>
@@ -8006,7 +8117,7 @@
         <v>64263.117867149995</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J11" s="26">
         <v>46294</v>
@@ -8103,7 +8214,7 @@
         <v>160183.89110417402</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="J12" s="26">
         <v>46303</v>
@@ -8191,7 +8302,7 @@
         <v>84285.862482079989</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J13" s="26">
         <v>46288</v>
@@ -8270,7 +8381,7 @@
         <v>76050.478160000013</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J14" s="26">
         <v>46345</v>
@@ -8330,25 +8441,25 @@
       </c>
       <c r="E15" s="24">
         <f>+[10]Main!$I$2</f>
-        <v>110.86</v>
+        <v>99.65</v>
       </c>
       <c r="F15" s="17">
         <f>+[10]Main!$I$4</f>
-        <v>12021.43191302</v>
+        <v>10522.448477600001</v>
       </c>
       <c r="G15" s="17">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
-        <v>-1514.729</v>
+        <v>-189.73699999999999</v>
       </c>
       <c r="H15" s="17">
         <f>F15+G15</f>
-        <v>10506.702913020001</v>
+        <v>10332.711477600002</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J15" s="26">
-        <v>46268</v>
+        <v>46366</v>
       </c>
       <c r="K15" s="17">
         <v>9619.2999999999993</v>
@@ -8420,7 +8531,7 @@
         <v>31132.194425488</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J16" s="26">
         <v>46324</v>
@@ -8472,99 +8583,56 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>7</v>
+      <c r="B17" s="44" t="s">
+        <v>802</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>20</v>
+        <v>901</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>900</v>
       </c>
       <c r="E17" s="24">
-        <f>+[12]Main!$H$2</f>
-        <v>250.5</v>
+        <f>+[86]Main!$I$2</f>
+        <v>22.51</v>
       </c>
       <c r="F17" s="17">
-        <f>+[12]Main!$H$4*FX!C3</f>
-        <v>31944.883201920002</v>
+        <f>+[86]Main!$I$4</f>
+        <v>40518</v>
       </c>
       <c r="G17" s="17">
-        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
-        <v>3456.96</v>
+        <f>+[86]Main!$I$6-[86]Main!$I$5</f>
+        <v>-4497</v>
       </c>
       <c r="H17" s="17">
-        <f t="shared" si="1"/>
-        <v>35401.843201920005</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>806</v>
-      </c>
-      <c r="J17" s="26">
-        <v>46316</v>
-      </c>
-      <c r="K17" s="17">
-        <f>17194*FX!C3</f>
-        <v>17881.760000000002</v>
-      </c>
-      <c r="L17" s="21">
-        <v>-0.12</v>
-      </c>
-      <c r="M17" s="17">
-        <f>2313*FX!C3</f>
-        <v>2405.52</v>
-      </c>
-      <c r="N17" s="17">
-        <f>1133*FX!C3</f>
-        <v>1178.32</v>
-      </c>
-      <c r="O17" s="21">
-        <v>0.74</v>
-      </c>
-      <c r="P17" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>16.7</v>
-      </c>
+        <f>+F17+G17</f>
+        <v>36021</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="22"/>
       <c r="R17" s="22"/>
-      <c r="S17" s="22">
-        <v>0.7</v>
-      </c>
+      <c r="S17" s="22"/>
       <c r="T17" s="22"/>
-      <c r="U17" s="22">
-        <v>5.3</v>
-      </c>
-      <c r="V17" s="22">
-        <v>4</v>
-      </c>
-      <c r="W17" s="27">
-        <v>7.67</v>
-      </c>
-      <c r="X17" s="22">
-        <v>0.87</v>
-      </c>
-      <c r="Y17" s="28">
-        <v>0.08</v>
-      </c>
-      <c r="Z17" s="28">
-        <v>0.08</v>
-      </c>
-      <c r="AA17" s="28">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AB17" s="17">
-        <v>1794</v>
-      </c>
-      <c r="AC17" s="17">
-        <v>46930</v>
-      </c>
-      <c r="AD17" s="5">
-        <v>1962</v>
-      </c>
-      <c r="AE17" s="28" t="s">
-        <v>114</v>
-      </c>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="28"/>
       <c r="AF17" s="2"/>
     </row>
     <row r="18" spans="1:32">
@@ -8573,74 +8641,97 @@
         <v>13</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>454</v>
+        <v>446</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="E18" s="24">
-        <f>+[13]Main!$H$2</f>
-        <v>78.75</v>
+        <f>+[12]Main!$H$2</f>
+        <v>250.5</v>
       </c>
       <c r="F18" s="17">
-        <f>+[13]Main!$H$5*FX!C9</f>
-        <v>28408.679775000001</v>
+        <f>+[12]Main!$H$4*FX!C3</f>
+        <v>31944.883201920002</v>
       </c>
       <c r="G18" s="17">
-        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
-        <v>-2787.26</v>
+        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
+        <v>3456.96</v>
       </c>
       <c r="H18" s="17">
         <f t="shared" si="1"/>
-        <v>25621.419775000002</v>
+        <v>35401.843201920005</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>806</v>
-      </c>
-      <c r="J18" s="26"/>
+        <v>805</v>
+      </c>
+      <c r="J18" s="26">
+        <v>46316</v>
+      </c>
       <c r="K18" s="17">
-        <f>70826*FX!C9</f>
-        <v>9915.6400000000012</v>
+        <f>17194*FX!C3</f>
+        <v>17881.760000000002</v>
       </c>
       <c r="L18" s="21">
-        <v>0.14000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="M18" s="17">
-        <f>16595*FX!C9</f>
-        <v>2323.3000000000002</v>
-      </c>
-      <c r="N18" s="17"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
+        <f>2313*FX!C3</f>
+        <v>2405.52</v>
+      </c>
+      <c r="N18" s="17">
+        <f>1133*FX!C3</f>
+        <v>1178.32</v>
+      </c>
+      <c r="O18" s="21">
+        <v>0.74</v>
+      </c>
+      <c r="P18" s="21">
+        <v>0.15</v>
+      </c>
       <c r="Q18" s="22">
-        <v>19.5</v>
-      </c>
-      <c r="R18" s="22">
-        <v>19.5</v>
-      </c>
-      <c r="S18" s="22"/>
+        <v>16.7</v>
+      </c>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22">
+        <v>0.7</v>
+      </c>
       <c r="T18" s="22"/>
       <c r="U18" s="22">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="V18" s="22">
-        <v>3</v>
-      </c>
-      <c r="W18" s="27"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="17"/>
+        <v>4</v>
+      </c>
+      <c r="W18" s="27">
+        <v>7.67</v>
+      </c>
+      <c r="X18" s="22">
+        <v>0.87</v>
+      </c>
+      <c r="Y18" s="28">
+        <v>0.08</v>
+      </c>
+      <c r="Z18" s="28">
+        <v>0.08</v>
+      </c>
+      <c r="AA18" s="28">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AB18" s="17">
+        <v>1794</v>
+      </c>
+      <c r="AC18" s="17">
+        <v>46930</v>
+      </c>
       <c r="AD18" s="5">
-        <v>1991</v>
+        <v>1962</v>
       </c>
       <c r="AE18" s="28" t="s">
-        <v>402</v>
+        <v>114</v>
       </c>
       <c r="AF18" s="2"/>
     </row>
@@ -8650,68 +8741,61 @@
         <v>14</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>17</v>
+        <v>447</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E19" s="24">
-        <f>+[14]Main!$M$2</f>
-        <v>103.91</v>
+        <f>+[13]Main!$H$2</f>
+        <v>78.75</v>
       </c>
       <c r="F19" s="17">
-        <f>+[14]Main!$M$4</f>
-        <v>14174.802327570002</v>
+        <f>+[13]Main!$H$5*FX!C9</f>
+        <v>28408.679775000001</v>
       </c>
       <c r="G19" s="17">
-        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
-        <v>-1602.5889999999999</v>
+        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
+        <v>-2787.26</v>
       </c>
       <c r="H19" s="17">
-        <f>F19+G19</f>
-        <v>12572.213327570002</v>
+        <f t="shared" si="1"/>
+        <v>25621.419775000002</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>874</v>
-      </c>
-      <c r="J19" s="26">
-        <v>46317</v>
-      </c>
+        <v>805</v>
+      </c>
+      <c r="J19" s="26"/>
       <c r="K19" s="17">
-        <v>4985.6120000000001</v>
+        <f>70826*FX!C9</f>
+        <v>9915.6400000000012</v>
       </c>
       <c r="L19" s="21">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M19" s="17">
-        <v>1179.0999999999999</v>
-      </c>
-      <c r="N19" s="17">
-        <v>967.2</v>
-      </c>
-      <c r="O19" s="21">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P19" s="21">
-        <f>+M19/K19</f>
-        <v>0.23650055399417361</v>
-      </c>
+        <f>16595*FX!C9</f>
+        <v>2323.3000000000002</v>
+      </c>
+      <c r="N19" s="17"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
       <c r="Q19" s="22">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="R19" s="22">
-        <v>19.399999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="S19" s="22"/>
       <c r="T19" s="22"/>
       <c r="U19" s="22">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="V19" s="22">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="W19" s="27"/>
       <c r="X19" s="22"/>
@@ -8721,10 +8805,10 @@
       <c r="AB19" s="17"/>
       <c r="AC19" s="17"/>
       <c r="AD19" s="5">
-        <v>1973</v>
+        <v>1991</v>
       </c>
       <c r="AE19" s="28" t="s">
-        <v>117</v>
+        <v>402</v>
       </c>
       <c r="AF19" s="2"/>
     </row>
@@ -8734,48 +8818,69 @@
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>310</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>311</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="24">
-        <f>+[15]Main!$J$2</f>
-        <v>130</v>
+        <f>+[14]Main!$M$2</f>
+        <v>103.91</v>
       </c>
       <c r="F20" s="17">
-        <f>+[15]Main!$J$4</f>
-        <v>25920.918140000002</v>
+        <f>+[14]Main!$M$4</f>
+        <v>14174.802327570002</v>
       </c>
       <c r="G20" s="17">
-        <f>+[15]Main!$J$6-[15]Main!$J$5</f>
-        <v>1227</v>
+        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
+        <v>-1602.5889999999999</v>
       </c>
       <c r="H20" s="17">
         <f>F20+G20</f>
-        <v>27147.918140000002</v>
+        <v>12572.213327570002</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>826</v>
+        <v>873</v>
       </c>
       <c r="J20" s="26">
-        <v>46331</v>
-      </c>
-      <c r="K20" s="24"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
+        <v>46317</v>
+      </c>
+      <c r="K20" s="17">
+        <v>4985.6120000000001</v>
+      </c>
+      <c r="L20" s="21">
+        <v>0.16</v>
+      </c>
+      <c r="M20" s="17">
+        <v>1179.0999999999999</v>
+      </c>
+      <c r="N20" s="17">
+        <v>967.2</v>
+      </c>
+      <c r="O20" s="21">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P20" s="21">
+        <f>+M20/K20</f>
+        <v>0.23650055399417361</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>19</v>
+      </c>
+      <c r="R20" s="22">
+        <v>19.399999999999999</v>
+      </c>
       <c r="S20" s="22"/>
       <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
+      <c r="U20" s="22">
+        <v>7.2</v>
+      </c>
+      <c r="V20" s="22">
+        <v>3.3</v>
+      </c>
       <c r="W20" s="27"/>
       <c r="X20" s="22"/>
       <c r="Y20" s="28"/>
@@ -8784,10 +8889,10 @@
       <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
       <c r="AD20" s="5">
-        <v>2000</v>
+        <v>1973</v>
       </c>
       <c r="AE20" s="28" t="s">
-        <v>401</v>
+        <v>117</v>
       </c>
       <c r="AF20" s="2"/>
     </row>
@@ -8797,43 +8902,38 @@
         <v>16</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>108</v>
+        <v>310</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>109</v>
+        <v>311</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E21" s="24">
-        <f>+[16]Main!$I$2</f>
-        <v>166.25</v>
+        <f>+[15]Main!$J$2</f>
+        <v>130</v>
       </c>
       <c r="F21" s="17">
-        <f>+[16]Main!$I$4*FX!C4</f>
-        <v>25232.110793750002</v>
+        <f>+[15]Main!$J$4</f>
+        <v>25920.918140000002</v>
       </c>
       <c r="G21" s="17">
-        <f>+([16]Main!$I$6-[16]Main!$I$5)*FX!C4</f>
-        <v>187.91</v>
+        <f>+[15]Main!$J$6-[15]Main!$J$5</f>
+        <v>1227</v>
       </c>
       <c r="H21" s="17">
-        <f t="shared" si="1"/>
-        <v>25420.020793750002</v>
+        <f>F21+G21</f>
+        <v>27147.918140000002</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>806</v>
+        <v>825</v>
       </c>
       <c r="J21" s="26">
-        <v>46289</v>
-      </c>
-      <c r="K21" s="17">
-        <f>234478*FX!C4</f>
-        <v>22275.41</v>
-      </c>
-      <c r="L21" s="21">
-        <v>-0.01</v>
-      </c>
+        <v>46331</v>
+      </c>
+      <c r="K21" s="24"/>
+      <c r="L21" s="21"/>
       <c r="M21" s="17"/>
       <c r="N21" s="24"/>
       <c r="O21" s="21"/>
@@ -8852,10 +8952,10 @@
       <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="5">
-        <v>1947</v>
+        <v>2000</v>
       </c>
       <c r="AE21" s="28" t="s">
-        <v>116</v>
+        <v>401</v>
       </c>
       <c r="AF21" s="2"/>
     </row>
@@ -8865,91 +8965,65 @@
         <v>17</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>110</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="E22" s="24">
-        <f>+[17]Main!$H$2</f>
-        <v>389.9</v>
+        <f>+[16]Main!$I$2</f>
+        <v>166.25</v>
       </c>
       <c r="F22" s="17">
-        <f>+[17]Main!$H$4</f>
-        <v>23231.114986099998</v>
+        <f>+[16]Main!$I$4*FX!C4</f>
+        <v>25232.110793750002</v>
       </c>
       <c r="G22" s="17">
-        <f>+[17]Main!$H$6-[17]Main!$H$5</f>
-        <v>-633.5</v>
+        <f>+([16]Main!$I$6-[16]Main!$I$5)*FX!C4</f>
+        <v>187.91</v>
       </c>
       <c r="H22" s="17">
-        <f>F22+G22</f>
-        <v>22597.614986099998</v>
+        <f t="shared" si="1"/>
+        <v>25420.020793750002</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>874</v>
+        <v>805</v>
       </c>
       <c r="J22" s="26">
-        <v>46331</v>
+        <v>46289</v>
       </c>
       <c r="K22" s="17">
-        <v>6631.4</v>
+        <f>234478*FX!C4</f>
+        <v>22275.41</v>
       </c>
       <c r="L22" s="21">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="M22" s="17">
-        <v>756.4</v>
-      </c>
-      <c r="N22" s="17">
-        <v>646.29999999999995</v>
-      </c>
-      <c r="O22" s="21">
-        <v>0.64</v>
-      </c>
-      <c r="P22" s="21">
-        <v>0.11</v>
-      </c>
-      <c r="Q22" s="22">
-        <v>17.3</v>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="22"/>
       <c r="R22" s="22"/>
-      <c r="S22" s="22">
-        <f>-11.2/100</f>
-        <v>-0.11199999999999999</v>
-      </c>
+      <c r="S22" s="22"/>
       <c r="T22" s="22"/>
-      <c r="U22" s="22">
-        <v>3.52</v>
-      </c>
-      <c r="V22" s="22">
-        <v>1.51</v>
-      </c>
-      <c r="W22" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="X22" s="22">
-        <v>0.75</v>
-      </c>
-      <c r="Y22" s="28">
-        <v>0.21</v>
-      </c>
-      <c r="Z22" s="28">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AA22" s="28">
-        <v>0.1</v>
-      </c>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="28"/>
+      <c r="AA22" s="28"/>
       <c r="AB22" s="17"/>
       <c r="AC22" s="17"/>
       <c r="AD22" s="5">
-        <v>1967</v>
+        <v>1947</v>
       </c>
       <c r="AE22" s="28" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="AF22" s="2"/>
     </row>
@@ -8959,60 +9033,91 @@
         <v>18</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E23" s="24">
-        <f>+[18]Main!$I$2</f>
-        <v>5281</v>
+        <f>+[17]Main!$H$2</f>
+        <v>389.9</v>
       </c>
       <c r="F23" s="17">
-        <f>+[18]Main!$I$4*FX!C5</f>
-        <v>23581.789650335701</v>
+        <f>+[17]Main!$H$4</f>
+        <v>23231.114986099998</v>
       </c>
       <c r="G23" s="17">
-        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C5</f>
-        <v>-471.03210000000001</v>
+        <f>+[17]Main!$H$6-[17]Main!$H$5</f>
+        <v>-633.5</v>
       </c>
       <c r="H23" s="17">
         <f>F23+G23</f>
-        <v>23110.7575503357</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>806</v>
+        <v>22597.614986099998</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>873</v>
       </c>
       <c r="J23" s="26">
-        <v>46337</v>
-      </c>
-      <c r="K23" s="17"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="22"/>
+        <v>46331</v>
+      </c>
+      <c r="K23" s="17">
+        <v>6631.4</v>
+      </c>
+      <c r="L23" s="21">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M23" s="17">
+        <v>756.4</v>
+      </c>
+      <c r="N23" s="17">
+        <v>646.29999999999995</v>
+      </c>
+      <c r="O23" s="21">
+        <v>0.64</v>
+      </c>
+      <c r="P23" s="21">
+        <v>0.11</v>
+      </c>
+      <c r="Q23" s="22">
+        <v>17.3</v>
+      </c>
       <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
+      <c r="S23" s="22">
+        <f>-11.2/100</f>
+        <v>-0.11199999999999999</v>
+      </c>
       <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
+      <c r="U23" s="22">
+        <v>3.52</v>
+      </c>
+      <c r="V23" s="22">
+        <v>1.51</v>
+      </c>
+      <c r="W23" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="X23" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="Y23" s="28">
+        <v>0.21</v>
+      </c>
+      <c r="Z23" s="28">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AA23" s="28">
+        <v>0.1</v>
+      </c>
       <c r="AB23" s="17"/>
       <c r="AC23" s="17"/>
       <c r="AD23" s="5">
-        <v>1949</v>
+        <v>1967</v>
       </c>
       <c r="AE23" s="28" t="s">
-        <v>402</v>
+        <v>97</v>
       </c>
       <c r="AF23" s="2"/>
     </row>
@@ -9022,40 +9127,40 @@
         <v>19</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>165</v>
+        <v>382</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="E24" s="24">
-        <f>+[19]Main!$H$2</f>
-        <v>43.26</v>
+        <f>+[18]Main!$I$2</f>
+        <v>5281</v>
       </c>
       <c r="F24" s="17">
-        <f>+[19]Main!$H$5*FX!C3</f>
-        <v>13814.701834751999</v>
+        <f>+[18]Main!$I$4*FX!C5</f>
+        <v>23581.789650335701</v>
       </c>
       <c r="G24" s="17">
-        <f>(+[19]Main!$H$7-[19]Main!$H$6)*FX!C3</f>
-        <v>727.22728000000006</v>
+        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C5</f>
+        <v>-471.03210000000001</v>
       </c>
       <c r="H24" s="17">
-        <f t="shared" si="1"/>
-        <v>14541.929114751998</v>
-      </c>
-      <c r="I24" s="25" t="s">
-        <v>806</v>
+        <f>F24+G24</f>
+        <v>23110.7575503357</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>805</v>
       </c>
       <c r="J24" s="26">
-        <v>46317</v>
-      </c>
-      <c r="K24" s="24"/>
+        <v>46337</v>
+      </c>
+      <c r="K24" s="17"/>
       <c r="L24" s="21"/>
       <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
+      <c r="N24" s="24"/>
       <c r="O24" s="21"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="22"/>
@@ -9072,10 +9177,10 @@
       <c r="AB24" s="17"/>
       <c r="AC24" s="17"/>
       <c r="AD24" s="5">
-        <v>1913</v>
+        <v>1949</v>
       </c>
       <c r="AE24" s="28" t="s">
-        <v>114</v>
+        <v>402</v>
       </c>
       <c r="AF24" s="2"/>
     </row>
@@ -9084,39 +9189,39 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>440</v>
+      <c r="B25" s="44" t="s">
+        <v>902</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>441</v>
+        <v>904</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>185</v>
+        <v>454</v>
       </c>
       <c r="E25" s="24">
-        <f>+[20]Main!$I$2</f>
-        <v>2992.7</v>
+        <f>+[80]Main!$J$2</f>
+        <v>48.5</v>
       </c>
       <c r="F25" s="17">
-        <f>+[20]Main!$I$4*FX!C12</f>
-        <v>11702.540569881699</v>
+        <f>+[80]Main!$J$5</f>
+        <v>26772.307449745003</v>
       </c>
       <c r="G25" s="17">
-        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C12</f>
-        <v>2616.768</v>
+        <f>+[80]Main!$J$7-[80]Main!$J$6</f>
+        <v>-15210</v>
       </c>
       <c r="H25" s="17">
         <f>+F25+G25</f>
-        <v>14319.308569881699</v>
+        <v>11562.307449745003</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>828</v>
-      </c>
-      <c r="J25" s="26"/>
+        <v>805</v>
+      </c>
+      <c r="J25" s="2"/>
       <c r="K25" s="24"/>
       <c r="L25" s="21"/>
       <c r="M25" s="24"/>
-      <c r="N25" s="17"/>
+      <c r="N25" s="24"/>
       <c r="O25" s="21"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="22"/>
@@ -9142,40 +9247,40 @@
         <v>21</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="D26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>165</v>
       </c>
       <c r="E26" s="24">
-        <f>+[21]Main!$H$2</f>
-        <v>47.32</v>
+        <f>+[19]Main!$H$2</f>
+        <v>43.26</v>
       </c>
       <c r="F26" s="17">
-        <f>+[21]Main!$H$4*FX!C3</f>
-        <v>13313.188044374401</v>
+        <f>+[19]Main!$H$5*FX!C3</f>
+        <v>13814.701834751999</v>
       </c>
       <c r="G26" s="17">
-        <f>+([21]Main!$H$6-[21]Main!$H$5)*FX!C3</f>
-        <v>-376.31984</v>
+        <f>(+[19]Main!$H$7-[19]Main!$H$6)*FX!C3</f>
+        <v>727.22728000000006</v>
       </c>
       <c r="H26" s="17">
         <f t="shared" si="1"/>
-        <v>12936.868204374401</v>
+        <v>14541.929114751998</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J26" s="26">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="K26" s="24"/>
       <c r="L26" s="21"/>
       <c r="M26" s="17"/>
-      <c r="N26" s="24"/>
+      <c r="N26" s="17"/>
       <c r="O26" s="21"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="22"/>
@@ -9192,10 +9297,10 @@
       <c r="AB26" s="17"/>
       <c r="AC26" s="17"/>
       <c r="AD26" s="5">
-        <v>1952</v>
+        <v>1913</v>
       </c>
       <c r="AE26" s="28" t="s">
-        <v>400</v>
+        <v>114</v>
       </c>
       <c r="AF26" s="2"/>
     </row>
@@ -9204,41 +9309,39 @@
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B27" s="31" t="s">
-        <v>306</v>
+      <c r="B27" s="23" t="s">
+        <v>440</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>309</v>
+        <v>441</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E27" s="24">
-        <f>+[22]Main!$I$2</f>
-        <v>294.94</v>
+        <f>+[20]Main!$I$2</f>
+        <v>2992.7</v>
       </c>
       <c r="F27" s="17">
-        <f>+[22]Main!$I$4</f>
-        <v>18845.486239999998</v>
+        <f>+[20]Main!$I$4*FX!C12</f>
+        <v>11702.540569881699</v>
       </c>
       <c r="G27" s="17">
-        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
-        <v>1189.8249999999998</v>
+        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C12</f>
+        <v>2616.768</v>
       </c>
       <c r="H27" s="17">
-        <f>F27+G27</f>
-        <v>20035.311239999999</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>806</v>
-      </c>
-      <c r="J27" s="26">
-        <v>46350</v>
-      </c>
+        <f>+F27+G27</f>
+        <v>14319.308569881699</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="J27" s="26"/>
       <c r="K27" s="24"/>
       <c r="L27" s="21"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="17"/>
       <c r="O27" s="21"/>
       <c r="P27" s="21"/>
       <c r="Q27" s="22"/>
@@ -9254,12 +9357,8 @@
       <c r="AA27" s="28"/>
       <c r="AB27" s="17"/>
       <c r="AC27" s="17"/>
-      <c r="AD27" s="5">
-        <v>1972</v>
-      </c>
-      <c r="AE27" s="28" t="s">
-        <v>118</v>
-      </c>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="28"/>
       <c r="AF27" s="2"/>
     </row>
     <row r="28" spans="1:32">
@@ -9267,40 +9366,40 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B28" s="31" t="s">
-        <v>307</v>
+      <c r="B28" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>308</v>
+        <v>448</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="E28" s="24">
-        <f>+[23]Main!$I$2</f>
-        <v>156</v>
+        <f>+[21]Main!$H$2</f>
+        <v>47.32</v>
       </c>
       <c r="F28" s="17">
-        <f>+[23]Main!$I$4*FX!C8</f>
-        <v>22613.136000000002</v>
+        <f>+[21]Main!$H$4*FX!C3</f>
+        <v>13313.188044374401</v>
       </c>
       <c r="G28" s="17">
-        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C8</f>
-        <v>883.74799999999993</v>
+        <f>+([21]Main!$H$6-[21]Main!$H$5)*FX!C3</f>
+        <v>-376.31984</v>
       </c>
       <c r="H28" s="17">
-        <f>F28+G28</f>
-        <v>23496.884000000002</v>
+        <f t="shared" si="1"/>
+        <v>12936.868204374401</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>422</v>
+        <v>805</v>
       </c>
       <c r="J28" s="26">
-        <v>46282</v>
+        <v>46316</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="21"/>
-      <c r="M28" s="24"/>
+      <c r="M28" s="17"/>
       <c r="N28" s="24"/>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
@@ -9318,10 +9417,10 @@
       <c r="AB28" s="17"/>
       <c r="AC28" s="17"/>
       <c r="AD28" s="5">
-        <v>1864</v>
+        <v>1952</v>
       </c>
       <c r="AE28" s="28" t="s">
-        <v>118</v>
+        <v>400</v>
       </c>
       <c r="AF28" s="2"/>
     </row>
@@ -9330,41 +9429,41 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B29" s="23" t="s">
-        <v>24</v>
+      <c r="B29" s="31" t="s">
+        <v>306</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>23</v>
+        <v>309</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="E29" s="24">
-        <f>+[24]Main!$H$2</f>
-        <v>30.85</v>
+        <f>+[22]Main!$I$2</f>
+        <v>294.94</v>
       </c>
       <c r="F29" s="17">
-        <f>+[24]Main!$H$5*FX!C7</f>
-        <v>8718.9328789276005</v>
+        <f>+[22]Main!$I$4</f>
+        <v>18845.486239999998</v>
       </c>
       <c r="G29" s="17">
-        <f>+([24]Main!$H$7-[24]Main!$H$6)*FX!C7</f>
-        <v>-1077.8880000000001</v>
+        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
+        <v>1189.8249999999998</v>
       </c>
       <c r="H29" s="17">
         <f>F29+G29</f>
-        <v>7641.0448789276006</v>
+        <v>20035.311239999999</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J29" s="26">
-        <v>46337</v>
+        <v>46350</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="21"/>
       <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
+      <c r="N29" s="24"/>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="22"/>
@@ -9381,10 +9480,10 @@
       <c r="AB29" s="17"/>
       <c r="AC29" s="17"/>
       <c r="AD29" s="5">
-        <v>2010</v>
+        <v>1972</v>
       </c>
       <c r="AE29" s="28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AF29" s="2"/>
     </row>
@@ -9393,36 +9492,36 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B30" s="23" t="s">
-        <v>418</v>
+      <c r="B30" s="31" t="s">
+        <v>307</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>419</v>
+        <v>308</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E30" s="24">
-        <f>+[25]Main!$J$2</f>
-        <v>33.79</v>
+        <f>+[23]Main!$I$2</f>
+        <v>156</v>
       </c>
       <c r="F30" s="17">
-        <f>+[25]Main!$J$4</f>
-        <v>19685.281459229998</v>
+        <f>+[23]Main!$I$4*FX!C8</f>
+        <v>22613.136000000002</v>
       </c>
       <c r="G30" s="17">
-        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
-        <v>-573</v>
+        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C8</f>
+        <v>883.74799999999993</v>
       </c>
       <c r="H30" s="17">
-        <f t="shared" si="1"/>
-        <v>19112.281459229998</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>806</v>
+        <f>F30+G30</f>
+        <v>23496.884000000002</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>422</v>
       </c>
       <c r="J30" s="26">
-        <v>46343</v>
+        <v>46282</v>
       </c>
       <c r="K30" s="24"/>
       <c r="L30" s="21"/>
@@ -9444,10 +9543,10 @@
       <c r="AB30" s="17"/>
       <c r="AC30" s="17"/>
       <c r="AD30" s="5">
-        <v>1950</v>
+        <v>1864</v>
       </c>
       <c r="AE30" s="28" t="s">
-        <v>430</v>
+        <v>118</v>
       </c>
       <c r="AF30" s="2"/>
     </row>
@@ -9457,35 +9556,35 @@
         <v>26</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>449</v>
+        <v>23</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>454</v>
+        <v>166</v>
       </c>
       <c r="E31" s="24">
-        <f>+[26]Main!$J$2</f>
-        <v>47.12</v>
+        <f>+[24]Main!$H$2</f>
+        <v>30.85</v>
       </c>
       <c r="F31" s="17">
-        <f>+[26]Main!$J$5*FX!C9</f>
-        <v>8726.4826075060482</v>
+        <f>+[24]Main!$H$5*FX!C7</f>
+        <v>8718.9328789276005</v>
       </c>
       <c r="G31" s="17">
-        <f>+([26]Main!$J$7-[26]Main!$J$6)*FX!C9</f>
-        <v>-1503.0597399999999</v>
+        <f>+([24]Main!$H$7-[24]Main!$H$6)*FX!C7</f>
+        <v>-1077.8880000000001</v>
       </c>
       <c r="H31" s="17">
-        <f t="shared" si="1"/>
-        <v>7223.4228675060485</v>
+        <f>F31+G31</f>
+        <v>7641.0448789276006</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>149</v>
+        <v>805</v>
       </c>
       <c r="J31" s="26">
-        <v>46260</v>
+        <v>46337</v>
       </c>
       <c r="K31" s="24"/>
       <c r="L31" s="21"/>
@@ -9507,10 +9606,10 @@
       <c r="AB31" s="17"/>
       <c r="AC31" s="17"/>
       <c r="AD31" s="5">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="AE31" s="28" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AF31" s="2"/>
     </row>
@@ -9520,40 +9619,40 @@
         <v>27</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>454</v>
+        <v>214</v>
       </c>
       <c r="E32" s="24">
-        <f>+[27]Main!$K$2</f>
-        <v>76.739999999999995</v>
+        <f>+[25]Main!$J$2</f>
+        <v>33.79</v>
       </c>
       <c r="F32" s="17">
-        <f>+[27]Main!$K$4*FX!C9</f>
-        <v>12537.781199999999</v>
+        <f>+[25]Main!$J$4</f>
+        <v>19685.281459229998</v>
       </c>
       <c r="G32" s="17">
-        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
-        <v>-745.22328020000009</v>
+        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
+        <v>-573</v>
       </c>
       <c r="H32" s="17">
-        <f>+G32+F32</f>
-        <v>11792.5579198</v>
+        <f t="shared" si="1"/>
+        <v>19112.281459229998</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="J32" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="K32" s="17"/>
+        <v>805</v>
+      </c>
+      <c r="J32" s="26">
+        <v>46343</v>
+      </c>
+      <c r="K32" s="24"/>
       <c r="L32" s="21"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
       <c r="O32" s="21"/>
       <c r="P32" s="21"/>
       <c r="Q32" s="22"/>
@@ -9570,10 +9669,10 @@
       <c r="AB32" s="17"/>
       <c r="AC32" s="17"/>
       <c r="AD32" s="5">
-        <v>2004</v>
+        <v>1950</v>
       </c>
       <c r="AE32" s="28" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="AF32" s="2"/>
     </row>
@@ -9583,40 +9682,40 @@
         <v>28</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="E33" s="24">
-        <f>+[28]Main!$I$2</f>
-        <v>25.27</v>
+        <f>+[26]Main!$J$2</f>
+        <v>35.46</v>
       </c>
       <c r="F33" s="17">
-        <f>+[28]Main!$I$4*FX!C3</f>
-        <v>6543.9191999999994</v>
+        <f>+[26]Main!$J$5*FX!C9</f>
+        <v>6567.085595546785</v>
       </c>
       <c r="G33" s="17">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
-        <v>-477.15199999999999</v>
+        <f>+([26]Main!$J$7-[26]Main!$J$6)*FX!C9</f>
+        <v>-3721.6155200000003</v>
       </c>
       <c r="H33" s="17">
-        <f>F33+G33</f>
-        <v>6066.7671999999993</v>
+        <f t="shared" si="1"/>
+        <v>2845.4700755467848</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J33" s="26">
-        <v>46329</v>
+        <v>46441</v>
       </c>
       <c r="K33" s="24"/>
       <c r="L33" s="21"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
       <c r="O33" s="21"/>
       <c r="P33" s="21"/>
       <c r="Q33" s="22"/>
@@ -9633,10 +9732,10 @@
       <c r="AB33" s="17"/>
       <c r="AC33" s="17"/>
       <c r="AD33" s="5">
-        <v>2008</v>
+        <v>1991</v>
       </c>
       <c r="AE33" s="28" t="s">
-        <v>415</v>
+        <v>97</v>
       </c>
       <c r="AF33" s="2"/>
     </row>
@@ -9646,35 +9745,35 @@
         <v>29</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>44</v>
+        <v>450</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E34" s="24">
-        <f>+[29]Main!$H$2</f>
-        <v>14.5</v>
+        <f>+[27]Main!$K$2</f>
+        <v>76.739999999999995</v>
       </c>
       <c r="F34" s="17">
-        <f>+[29]Main!$H$4</f>
-        <v>5700.4512649999997</v>
+        <f>+[27]Main!$K$4*FX!C9</f>
+        <v>12537.781199999999</v>
       </c>
       <c r="G34" s="17">
-        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
-        <v>2343.0419999999999</v>
+        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
+        <v>-745.22328020000009</v>
       </c>
       <c r="H34" s="17">
         <f>+G34+F34</f>
-        <v>8043.4932649999992</v>
+        <v>11792.5579198</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>873</v>
-      </c>
-      <c r="J34" s="26">
-        <v>46322</v>
+        <v>383</v>
+      </c>
+      <c r="J34" s="30" t="s">
+        <v>404</v>
       </c>
       <c r="K34" s="17"/>
       <c r="L34" s="21"/>
@@ -9696,10 +9795,10 @@
       <c r="AB34" s="17"/>
       <c r="AC34" s="17"/>
       <c r="AD34" s="5">
-        <v>1899</v>
+        <v>2004</v>
       </c>
       <c r="AE34" s="28" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="AF34" s="2"/>
     </row>
@@ -9709,40 +9808,40 @@
         <v>30</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>27</v>
+        <v>414</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E35" s="24">
-        <f>+[30]Main!$I$3</f>
-        <v>34.85</v>
+        <f>+[28]Main!$I$2</f>
+        <v>25.27</v>
       </c>
       <c r="F35" s="17">
-        <f>+[30]Main!$I$5*FX!C3</f>
-        <v>6665.4910936640008</v>
+        <f>+[28]Main!$I$4*FX!C3</f>
+        <v>6543.9191999999994</v>
       </c>
       <c r="G35" s="17">
-        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
-        <v>1033.5260000000001</v>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
+        <v>-477.15199999999999</v>
       </c>
       <c r="H35" s="17">
-        <f t="shared" si="1"/>
-        <v>7699.0170936640006</v>
-      </c>
-      <c r="I35" s="16" t="s">
-        <v>819</v>
+        <f>F35+G35</f>
+        <v>6066.7671999999993</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>805</v>
       </c>
       <c r="J35" s="26">
-        <v>46373</v>
-      </c>
-      <c r="K35" s="17"/>
+        <v>46329</v>
+      </c>
+      <c r="K35" s="24"/>
       <c r="L35" s="21"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
       <c r="O35" s="21"/>
       <c r="P35" s="21"/>
       <c r="Q35" s="22"/>
@@ -9759,10 +9858,10 @@
       <c r="AB35" s="17"/>
       <c r="AC35" s="17"/>
       <c r="AD35" s="5">
-        <v>1774</v>
+        <v>2008</v>
       </c>
       <c r="AE35" s="28" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="AF35" s="2"/>
     </row>
@@ -9772,54 +9871,42 @@
         <v>31</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>111</v>
+        <v>314</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>743</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E36" s="24">
-        <f>+[31]Main!$J$2</f>
-        <v>23.84</v>
+        <f>+[29]Main!$H$2</f>
+        <v>14.5</v>
       </c>
       <c r="F36" s="17">
-        <f>+[31]Main!$J$4</f>
-        <v>8463.2000000000007</v>
+        <f>+[29]Main!$H$4</f>
+        <v>5700.4512649999997</v>
       </c>
       <c r="G36" s="17">
-        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
-        <v>-992</v>
+        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
+        <v>2343.0419999999999</v>
       </c>
       <c r="H36" s="17">
         <f>+G36+F36</f>
-        <v>7471.2000000000007</v>
+        <v>8043.4932649999992</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>806</v>
+        <v>872</v>
       </c>
       <c r="J36" s="26">
-        <v>46345</v>
-      </c>
-      <c r="K36" s="17">
-        <v>14889</v>
-      </c>
-      <c r="L36" s="21">
-        <v>0.05</v>
-      </c>
-      <c r="M36" s="17">
-        <v>560</v>
-      </c>
-      <c r="N36" s="17">
-        <v>502</v>
-      </c>
-      <c r="O36" s="21">
-        <v>0.37</v>
-      </c>
-      <c r="P36" s="21">
-        <v>0.04</v>
-      </c>
+        <v>46322</v>
+      </c>
+      <c r="K36" s="17"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
       <c r="Q36" s="22"/>
       <c r="R36" s="22"/>
       <c r="S36" s="22"/>
@@ -9834,10 +9921,10 @@
       <c r="AB36" s="17"/>
       <c r="AC36" s="17"/>
       <c r="AD36" s="5">
-        <v>1969</v>
+        <v>1899</v>
       </c>
       <c r="AE36" s="28" t="s">
-        <v>97</v>
+        <v>406</v>
       </c>
       <c r="AF36" s="2"/>
     </row>
@@ -9847,35 +9934,35 @@
         <v>32</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E37" s="24">
-        <f>+[32]Main!$I$2</f>
-        <v>60.4</v>
+        <f>+[30]Main!$I$3</f>
+        <v>34.85</v>
       </c>
       <c r="F37" s="17">
-        <f>+[32]Main!$I$4</f>
-        <v>9118.7085583999997</v>
+        <f>+[30]Main!$I$5*FX!C3</f>
+        <v>6665.4910936640008</v>
       </c>
       <c r="G37" s="17">
-        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
-        <v>-838.96200000000022</v>
+        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
+        <v>1033.5260000000001</v>
       </c>
       <c r="H37" s="17">
-        <f t="shared" ref="H37:H59" si="3">F37+G37</f>
-        <v>8279.7465584000001</v>
+        <f t="shared" si="1"/>
+        <v>7699.0170936640006</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="J37" s="26" t="s">
-        <v>811</v>
+        <v>818</v>
+      </c>
+      <c r="J37" s="26">
+        <v>46373</v>
       </c>
       <c r="K37" s="17"/>
       <c r="L37" s="21"/>
@@ -9897,10 +9984,10 @@
       <c r="AB37" s="17"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="5">
-        <v>1992</v>
+        <v>1774</v>
       </c>
       <c r="AE37" s="28" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AF37" s="2"/>
     </row>
@@ -9910,42 +9997,54 @@
         <v>33</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>387</v>
+        <v>111</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>386</v>
+        <v>742</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="E38" s="24">
-        <f>+[33]Main!$J$2</f>
-        <v>87.92</v>
+        <f>+[31]Main!$J$2</f>
+        <v>23.84</v>
       </c>
       <c r="F38" s="17">
-        <f>+[33]Main!$J$4*FX!C3</f>
-        <v>6217.1241536768002</v>
+        <f>+[31]Main!$J$4</f>
+        <v>8463.2000000000007</v>
       </c>
       <c r="G38" s="17">
-        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
-        <v>227.71215999999995</v>
+        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
+        <v>-992</v>
       </c>
       <c r="H38" s="17">
-        <f>F38+G38</f>
-        <v>6444.8363136768003</v>
+        <f>+G38+F38</f>
+        <v>7471.2000000000007</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J38" s="26">
-        <v>46310</v>
-      </c>
-      <c r="K38" s="17"/>
-      <c r="L38" s="21"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
+        <v>46345</v>
+      </c>
+      <c r="K38" s="17">
+        <v>14889</v>
+      </c>
+      <c r="L38" s="21">
+        <v>0.05</v>
+      </c>
+      <c r="M38" s="17">
+        <v>560</v>
+      </c>
+      <c r="N38" s="17">
+        <v>502</v>
+      </c>
+      <c r="O38" s="21">
+        <v>0.37</v>
+      </c>
+      <c r="P38" s="21">
+        <v>0.04</v>
+      </c>
       <c r="Q38" s="22"/>
       <c r="R38" s="22"/>
       <c r="S38" s="22"/>
@@ -9960,10 +10059,10 @@
       <c r="AB38" s="17"/>
       <c r="AC38" s="17"/>
       <c r="AD38" s="5">
-        <v>1978</v>
+        <v>1969</v>
       </c>
       <c r="AE38" s="28" t="s">
-        <v>400</v>
+        <v>97</v>
       </c>
       <c r="AF38" s="2"/>
     </row>
@@ -9973,35 +10072,35 @@
         <v>34</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E39" s="24">
-        <f>+[34]Main!$I$2</f>
-        <v>55.89</v>
+        <f>+[32]Main!$I$2</f>
+        <v>60.4</v>
       </c>
       <c r="F39" s="17">
-        <f>+[34]Main!$I$4</f>
-        <v>10349.486639999999</v>
+        <f>+[32]Main!$I$4</f>
+        <v>9118.7085583999997</v>
       </c>
       <c r="G39" s="17">
-        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
-        <v>4262.759</v>
+        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
+        <v>-838.96200000000022</v>
       </c>
       <c r="H39" s="17">
-        <f>F39+G39</f>
-        <v>14612.245639999999</v>
+        <f t="shared" ref="H39:H61" si="3">F39+G39</f>
+        <v>8279.7465584000001</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>806</v>
-      </c>
-      <c r="J39" s="26">
-        <v>46323</v>
+        <v>337</v>
+      </c>
+      <c r="J39" s="30" t="s">
+        <v>810</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="21"/>
@@ -10023,10 +10122,10 @@
       <c r="AB39" s="17"/>
       <c r="AC39" s="17"/>
       <c r="AD39" s="5">
-        <v>1984</v>
+        <v>1992</v>
       </c>
       <c r="AE39" s="28" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AF39" s="2"/>
     </row>
@@ -10036,54 +10135,42 @@
         <v>35</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>32</v>
+        <v>386</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="E40" s="24">
-        <f>+[35]Main!$I$2</f>
-        <v>24.26</v>
+        <f>+[33]Main!$J$2</f>
+        <v>87.92</v>
       </c>
       <c r="F40" s="17">
-        <f>+[35]Main!$I$4</f>
-        <v>8463.1146341200019</v>
+        <f>+[33]Main!$J$4*FX!C3</f>
+        <v>6217.1241536768002</v>
       </c>
       <c r="G40" s="17">
-        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
-        <v>65.200000000000045</v>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
+        <v>227.71215999999995</v>
       </c>
       <c r="H40" s="17">
         <f>F40+G40</f>
-        <v>8528.3146341200027</v>
+        <v>6444.8363136768003</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J40" s="26">
-        <v>46303</v>
-      </c>
-      <c r="K40" s="17">
-        <v>6179</v>
-      </c>
-      <c r="L40" s="21">
-        <v>0</v>
-      </c>
-      <c r="M40" s="17">
-        <v>353.3</v>
-      </c>
-      <c r="N40" s="17">
-        <v>249.6</v>
-      </c>
-      <c r="O40" s="21">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P40" s="21">
-        <v>0.06</v>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="K40" s="17"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="21"/>
+      <c r="P40" s="21"/>
       <c r="Q40" s="22"/>
       <c r="R40" s="22"/>
       <c r="S40" s="22"/>
@@ -10098,10 +10185,10 @@
       <c r="AB40" s="17"/>
       <c r="AC40" s="17"/>
       <c r="AD40" s="5">
-        <v>1853</v>
+        <v>1978</v>
       </c>
       <c r="AE40" s="28" t="s">
-        <v>97</v>
+        <v>400</v>
       </c>
       <c r="AF40" s="2"/>
     </row>
@@ -10111,35 +10198,35 @@
         <v>36</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>321</v>
+        <v>38</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>322</v>
+        <v>39</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="E41" s="24">
-        <f>+[36]Main!$I$2</f>
-        <v>17550</v>
+        <f>+[34]Main!$I$2</f>
+        <v>55.89</v>
       </c>
       <c r="F41" s="17">
-        <f>+[36]Main!$I$4*FX!C11</f>
-        <v>8142.7173750000002</v>
+        <f>+[34]Main!$I$4</f>
+        <v>10349.486639999999</v>
       </c>
       <c r="G41" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
-        <v>171.25</v>
+        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
+        <v>4262.759</v>
       </c>
       <c r="H41" s="17">
-        <f>+F41+G41</f>
-        <v>8313.9673750000002</v>
+        <f>F41+G41</f>
+        <v>14612.245639999999</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>149</v>
+        <v>805</v>
       </c>
       <c r="J41" s="26">
-        <v>46002</v>
+        <v>46323</v>
       </c>
       <c r="K41" s="17"/>
       <c r="L41" s="21"/>
@@ -10160,8 +10247,12 @@
       <c r="AA41" s="28"/>
       <c r="AB41" s="17"/>
       <c r="AC41" s="17"/>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="28"/>
+      <c r="AD41" s="5">
+        <v>1984</v>
+      </c>
+      <c r="AE41" s="28" t="s">
+        <v>409</v>
+      </c>
       <c r="AF41" s="2"/>
     </row>
     <row r="42" spans="1:32">
@@ -10170,40 +10261,54 @@
         <v>37</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="3">
-        <v>600398</v>
+        <v>31</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="E42" s="24">
-        <f>+[37]Main!$J$2</f>
-        <v>8.7799999999999994</v>
+        <f>+[35]Main!$I$2</f>
+        <v>24.26</v>
       </c>
       <c r="F42" s="17">
-        <f>+[37]Main!$J$4*FX!C9</f>
-        <v>5900.1600000000008</v>
+        <f>+[35]Main!$I$4</f>
+        <v>8463.1146341200019</v>
       </c>
       <c r="G42" s="17">
-        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
-        <v>-679.00000000000011</v>
+        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
+        <v>65.200000000000045</v>
       </c>
       <c r="H42" s="17">
         <f>F42+G42</f>
-        <v>5221.1600000000008</v>
+        <v>8528.3146341200027</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="J42" s="26"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="21"/>
-      <c r="P42" s="21"/>
+        <v>805</v>
+      </c>
+      <c r="J42" s="26">
+        <v>46303</v>
+      </c>
+      <c r="K42" s="17">
+        <v>6179</v>
+      </c>
+      <c r="L42" s="21">
+        <v>0</v>
+      </c>
+      <c r="M42" s="17">
+        <v>353.3</v>
+      </c>
+      <c r="N42" s="17">
+        <v>249.6</v>
+      </c>
+      <c r="O42" s="21">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P42" s="21">
+        <v>0.06</v>
+      </c>
       <c r="Q42" s="22"/>
       <c r="R42" s="22"/>
       <c r="S42" s="22"/>
@@ -10218,9 +10323,11 @@
       <c r="AB42" s="17"/>
       <c r="AC42" s="17"/>
       <c r="AD42" s="5">
-        <v>1997</v>
-      </c>
-      <c r="AE42" s="28"/>
+        <v>1853</v>
+      </c>
+      <c r="AE42" s="28" t="s">
+        <v>97</v>
+      </c>
       <c r="AF42" s="2"/>
     </row>
     <row r="43" spans="1:32">
@@ -10229,35 +10336,35 @@
         <v>38</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="E43" s="24">
-        <f>+[38]Main!$H$2</f>
-        <v>41240</v>
+        <f>+[36]Main!$I$2</f>
+        <v>21560</v>
       </c>
       <c r="F43" s="17">
-        <f>+[38]Main!$H$4*FX!C12</f>
-        <v>5059.9509140399996</v>
+        <f>+[36]Main!$I$4*FX!C11</f>
+        <v>10018.43612</v>
       </c>
       <c r="G43" s="17">
-        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
-        <v>79.99563000000002</v>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
+        <v>295.25</v>
       </c>
       <c r="H43" s="17">
         <f>+F43+G43</f>
-        <v>5139.9465440399999</v>
+        <v>10313.68612</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>715</v>
+        <v>149</v>
       </c>
       <c r="J43" s="26">
-        <v>45975</v>
+        <v>46282</v>
       </c>
       <c r="K43" s="17"/>
       <c r="L43" s="21"/>
@@ -10288,36 +10395,34 @@
         <v>39</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="C44" s="3">
+        <v>600398</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E44" s="24">
-        <f>+[39]Main!$H$2</f>
-        <v>121.86</v>
+        <f>+[37]Main!$J$2</f>
+        <v>8.7799999999999994</v>
       </c>
       <c r="F44" s="17">
-        <f>+[39]Main!$H$4</f>
-        <v>5842.5868395000007</v>
+        <f>+[37]Main!$J$4*FX!C9</f>
+        <v>5900.1600000000008</v>
       </c>
       <c r="G44" s="17">
-        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
-        <v>1137.3819999999998</v>
+        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
+        <v>-679.00000000000011</v>
       </c>
       <c r="H44" s="17">
         <f>F44+G44</f>
-        <v>6979.9688395000003</v>
+        <v>5221.1600000000008</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>806</v>
-      </c>
-      <c r="J44" s="26">
-        <v>46324</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="J44" s="26"/>
       <c r="K44" s="17"/>
       <c r="L44" s="21"/>
       <c r="M44" s="17"/>
@@ -10338,11 +10443,9 @@
       <c r="AB44" s="17"/>
       <c r="AC44" s="17"/>
       <c r="AD44" s="5">
-        <v>2002</v>
-      </c>
-      <c r="AE44" s="28" t="s">
-        <v>408</v>
-      </c>
+        <v>1997</v>
+      </c>
+      <c r="AE44" s="28"/>
       <c r="AF44" s="2"/>
     </row>
     <row r="45" spans="1:32">
@@ -10351,35 +10454,35 @@
         <v>40</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>325</v>
+        <v>185</v>
       </c>
       <c r="E45" s="24">
-        <f>+[40]Main!$I$2</f>
-        <v>27.8</v>
+        <f>+[38]Main!$H$2</f>
+        <v>41240</v>
       </c>
       <c r="F45" s="17">
-        <f>+[40]Main!$I$4*FX!C14</f>
-        <v>5512.4063999999998</v>
+        <f>+[38]Main!$H$4*FX!C12</f>
+        <v>5059.9509140399996</v>
       </c>
       <c r="G45" s="17">
-        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
-        <v>392.36399999999998</v>
+        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
+        <v>79.99563000000002</v>
       </c>
       <c r="H45" s="17">
         <f>+F45+G45</f>
-        <v>5904.7703999999994</v>
+        <v>5139.9465440399999</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>338</v>
+        <v>715</v>
       </c>
       <c r="J45" s="26">
-        <v>45804</v>
+        <v>45975</v>
       </c>
       <c r="K45" s="17"/>
       <c r="L45" s="21"/>
@@ -10400,12 +10503,8 @@
       <c r="AA45" s="28"/>
       <c r="AB45" s="17"/>
       <c r="AC45" s="17"/>
-      <c r="AD45" s="5">
-        <v>1956</v>
-      </c>
-      <c r="AE45" s="28" t="s">
-        <v>118</v>
-      </c>
+      <c r="AD45" s="5"/>
+      <c r="AE45" s="28"/>
       <c r="AF45" s="2"/>
     </row>
     <row r="46" spans="1:32">
@@ -10413,38 +10512,38 @@
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="B46" s="31" t="s">
-        <v>312</v>
+      <c r="B46" s="23" t="s">
+        <v>33</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>313</v>
+        <v>34</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="E46" s="24">
-        <f>+[41]Main!$I$2</f>
-        <v>0.93779999999999997</v>
+        <f>+[39]Main!$H$2</f>
+        <v>121.86</v>
       </c>
       <c r="F46" s="17">
-        <f>+[41]Main!$I$4*FX!C8</f>
-        <v>5962.0447439999998</v>
+        <f>+[39]Main!$H$4</f>
+        <v>5842.5868395000007</v>
       </c>
       <c r="G46" s="17">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
-        <v>155</v>
+        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
+        <v>1137.3819999999998</v>
       </c>
       <c r="H46" s="17">
         <f>F46+G46</f>
-        <v>6117.0447439999998</v>
-      </c>
-      <c r="I46" s="25" t="s">
-        <v>806</v>
+        <v>6979.9688395000003</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>805</v>
       </c>
       <c r="J46" s="26">
-        <v>45981</v>
-      </c>
-      <c r="K46" s="24"/>
+        <v>46324</v>
+      </c>
+      <c r="K46" s="17"/>
       <c r="L46" s="21"/>
       <c r="M46" s="17"/>
       <c r="N46" s="17"/>
@@ -10464,10 +10563,10 @@
       <c r="AB46" s="17"/>
       <c r="AC46" s="17"/>
       <c r="AD46" s="5">
-        <v>1981</v>
+        <v>2002</v>
       </c>
       <c r="AE46" s="28" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AF46" s="2"/>
     </row>
@@ -10477,35 +10576,35 @@
         <v>42</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="E47" s="24">
-        <f>+[42]Main!$H$2</f>
-        <v>86.42</v>
+        <f>+[40]Main!$I$2</f>
+        <v>27.8</v>
       </c>
       <c r="F47" s="17">
-        <f>+[42]Main!$H$4*FX!C13</f>
-        <v>6825.0480185999995</v>
+        <f>+[40]Main!$I$4*FX!C14</f>
+        <v>5512.4063999999998</v>
       </c>
       <c r="G47" s="17">
-        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
-        <v>-201.90158999999997</v>
+        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
+        <v>392.36399999999998</v>
       </c>
       <c r="H47" s="17">
         <f>+F47+G47</f>
-        <v>6623.1464285999991</v>
+        <v>5904.7703999999994</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>715</v>
+        <v>338</v>
       </c>
       <c r="J47" s="26">
-        <v>45939</v>
+        <v>45804</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="21"/>
@@ -10526,8 +10625,12 @@
       <c r="AA47" s="28"/>
       <c r="AB47" s="17"/>
       <c r="AC47" s="17"/>
-      <c r="AD47" s="5"/>
-      <c r="AE47" s="28"/>
+      <c r="AD47" s="5">
+        <v>1956</v>
+      </c>
+      <c r="AE47" s="28" t="s">
+        <v>118</v>
+      </c>
       <c r="AF47" s="2"/>
     </row>
     <row r="48" spans="1:32">
@@ -10535,38 +10638,38 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="B48" s="23" t="s">
-        <v>388</v>
+      <c r="B48" s="31" t="s">
+        <v>312</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>452</v>
+        <v>313</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>454</v>
+        <v>219</v>
       </c>
       <c r="E48" s="24">
-        <f>+[43]Main!$H$2</f>
-        <v>16.02</v>
+        <f>+[41]Main!$I$2</f>
+        <v>0.93779999999999997</v>
       </c>
       <c r="F48" s="17">
-        <f>+[43]Main!$H$5*FX!C9</f>
-        <v>5313.5769879360005</v>
+        <f>+[41]Main!$I$4*FX!C8</f>
+        <v>5962.0447439999998</v>
       </c>
       <c r="G48" s="17">
-        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
-        <v>-2458.0551799999998</v>
+        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
+        <v>155</v>
       </c>
       <c r="H48" s="17">
         <f>F48+G48</f>
-        <v>2855.5218079360006</v>
-      </c>
-      <c r="I48" s="16" t="s">
-        <v>148</v>
+        <v>6117.0447439999998</v>
+      </c>
+      <c r="I48" s="25" t="s">
+        <v>805</v>
       </c>
       <c r="J48" s="26">
-        <v>45733</v>
-      </c>
-      <c r="K48" s="17"/>
+        <v>45981</v>
+      </c>
+      <c r="K48" s="24"/>
       <c r="L48" s="21"/>
       <c r="M48" s="17"/>
       <c r="N48" s="17"/>
@@ -10585,9 +10688,11 @@
       <c r="AA48" s="28"/>
       <c r="AB48" s="17"/>
       <c r="AC48" s="17"/>
-      <c r="AD48" s="5"/>
+      <c r="AD48" s="5">
+        <v>1981</v>
+      </c>
       <c r="AE48" s="28" t="s">
-        <v>115</v>
+        <v>402</v>
       </c>
       <c r="AF48" s="2"/>
     </row>
@@ -10597,34 +10702,36 @@
         <v>44</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>47</v>
+        <v>329</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>453</v>
+        <v>330</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>454</v>
+        <v>107</v>
       </c>
       <c r="E49" s="24">
-        <f>+[44]Main!$I$2</f>
-        <v>8.01</v>
+        <f>+[42]Main!$H$2</f>
+        <v>86.42</v>
       </c>
       <c r="F49" s="17">
-        <f>+[44]Main!$I$4*FX!C9</f>
-        <v>5141.5464790620008</v>
+        <f>+[42]Main!$H$4*FX!C13</f>
+        <v>6825.0480185999995</v>
       </c>
       <c r="G49" s="17">
-        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
-        <v>1697.6221653999999</v>
+        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
+        <v>-201.90158999999997</v>
       </c>
       <c r="H49" s="17">
         <f>+F49+G49</f>
-        <v>6839.1686444620009</v>
+        <v>6623.1464285999991</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="J49" s="26"/>
+        <v>715</v>
+      </c>
+      <c r="J49" s="26">
+        <v>45939</v>
+      </c>
       <c r="K49" s="17"/>
       <c r="L49" s="21"/>
       <c r="M49" s="17"/>
@@ -10654,35 +10761,35 @@
         <v>45</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>152</v>
+        <v>388</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>153</v>
+        <v>452</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E50" s="24">
-        <f>+[45]Main!$J$2</f>
-        <v>79.900000000000006</v>
+        <f>+[43]Main!$H$2</f>
+        <v>16.02</v>
       </c>
       <c r="F50" s="17">
-        <f>+[45]Main!$J$4</f>
-        <v>6842.1251993000005</v>
+        <f>+[43]Main!$H$5*FX!C9</f>
+        <v>5313.5769879360005</v>
       </c>
       <c r="G50" s="17">
-        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
-        <v>-716.12699999999995</v>
+        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
+        <v>-2458.0551799999998</v>
       </c>
       <c r="H50" s="17">
-        <f>+F50+G50</f>
-        <v>6125.9981993000001</v>
+        <f>F50+G50</f>
+        <v>2855.5218079360006</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>900</v>
+        <v>148</v>
       </c>
       <c r="J50" s="26">
-        <v>46350</v>
+        <v>45733</v>
       </c>
       <c r="K50" s="17"/>
       <c r="L50" s="21"/>
@@ -10704,7 +10811,9 @@
       <c r="AB50" s="17"/>
       <c r="AC50" s="17"/>
       <c r="AD50" s="5"/>
-      <c r="AE50" s="28"/>
+      <c r="AE50" s="28" t="s">
+        <v>115</v>
+      </c>
       <c r="AF50" s="2"/>
     </row>
     <row r="51" spans="1:32">
@@ -10713,36 +10822,34 @@
         <v>46</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>385</v>
+        <v>453</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="E51" s="24">
-        <f>+[46]Main!$I$2</f>
-        <v>25.8</v>
+        <f>+[44]Main!$I$2</f>
+        <v>8.01</v>
       </c>
       <c r="F51" s="17">
-        <f>+[46]Main!$I$4*FX!C3</f>
-        <v>3949.9093389599998</v>
+        <f>+[44]Main!$I$4*FX!C9</f>
+        <v>5141.5464790620008</v>
       </c>
       <c r="G51" s="17">
-        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
-        <v>1411.904</v>
+        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
+        <v>1697.6221653999999</v>
       </c>
       <c r="H51" s="17">
-        <f t="shared" si="3"/>
-        <v>5361.8133389599998</v>
+        <f>+F51+G51</f>
+        <v>6839.1686444620009</v>
       </c>
       <c r="I51" s="16" t="s">
-        <v>827</v>
-      </c>
-      <c r="J51" s="26">
-        <v>46325</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="J51" s="26"/>
       <c r="K51" s="17"/>
       <c r="L51" s="21"/>
       <c r="M51" s="17"/>
@@ -10762,12 +10869,8 @@
       <c r="AA51" s="28"/>
       <c r="AB51" s="17"/>
       <c r="AC51" s="17"/>
-      <c r="AD51" s="5">
-        <v>1948</v>
-      </c>
-      <c r="AE51" s="28" t="s">
-        <v>402</v>
-      </c>
+      <c r="AD51" s="5"/>
+      <c r="AE51" s="28"/>
       <c r="AF51" s="2"/>
     </row>
     <row r="52" spans="1:32">
@@ -10776,35 +10879,35 @@
         <v>47</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>390</v>
+        <v>153</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="E52" s="24">
-        <f>+[47]Main!$I$2</f>
-        <v>3.75</v>
+        <f>+[45]Main!$J$2</f>
+        <v>79.900000000000006</v>
       </c>
       <c r="F52" s="17">
-        <f>+[47]Main!$I$5*FX!C9</f>
-        <v>5271.5025720000003</v>
+        <f>+[45]Main!$J$4</f>
+        <v>6842.1251993000005</v>
       </c>
       <c r="G52" s="17">
-        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
-        <v>-653.85012000000006</v>
+        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
+        <v>-716.12699999999995</v>
       </c>
       <c r="H52" s="17">
-        <f t="shared" si="3"/>
-        <v>4617.6524520000003</v>
+        <f>+F52+G52</f>
+        <v>6125.9981993000001</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>334</v>
+        <v>899</v>
       </c>
       <c r="J52" s="26">
-        <v>45833</v>
+        <v>46350</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="21"/>
@@ -10825,12 +10928,8 @@
       <c r="AA52" s="28"/>
       <c r="AB52" s="17"/>
       <c r="AC52" s="17"/>
-      <c r="AD52" s="5">
-        <v>1976</v>
-      </c>
-      <c r="AE52" s="28" t="s">
-        <v>97</v>
-      </c>
+      <c r="AD52" s="5"/>
+      <c r="AE52" s="28"/>
       <c r="AF52" s="2"/>
     </row>
     <row r="53" spans="1:32">
@@ -10839,54 +10938,42 @@
         <v>48</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>113</v>
+        <v>385</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E53" s="24">
-        <f>+[48]Main!$I$2</f>
-        <v>148.80000000000001</v>
+        <f>+[46]Main!$I$2</f>
+        <v>25.8</v>
       </c>
       <c r="F53" s="17">
-        <f>+[48]Main!$I$4</f>
-        <v>6512.5296000000008</v>
+        <f>+[46]Main!$I$4*FX!C3</f>
+        <v>3949.9093389599998</v>
       </c>
       <c r="G53" s="17">
-        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
-        <v>-637.99900000000002</v>
+        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
+        <v>1411.904</v>
       </c>
       <c r="H53" s="17">
-        <f>F53+G53</f>
-        <v>5874.530600000001</v>
-      </c>
-      <c r="I53" s="25" t="s">
-        <v>806</v>
+        <f t="shared" si="3"/>
+        <v>5361.8133389599998</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>826</v>
       </c>
       <c r="J53" s="26">
-        <v>46350</v>
-      </c>
-      <c r="K53" s="17">
-        <v>4280.7</v>
-      </c>
-      <c r="L53" s="21">
-        <v>0.16</v>
-      </c>
-      <c r="M53" s="17">
-        <v>484.7</v>
-      </c>
-      <c r="N53" s="17">
-        <v>328.1</v>
-      </c>
-      <c r="O53" s="21">
-        <v>0.63</v>
-      </c>
-      <c r="P53" s="21">
-        <v>0.11</v>
-      </c>
+        <v>46325</v>
+      </c>
+      <c r="K53" s="17"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="21"/>
+      <c r="P53" s="21"/>
       <c r="Q53" s="22"/>
       <c r="R53" s="22"/>
       <c r="S53" s="22"/>
@@ -10901,10 +10988,10 @@
       <c r="AB53" s="17"/>
       <c r="AC53" s="17"/>
       <c r="AD53" s="5">
-        <v>1892</v>
+        <v>1948</v>
       </c>
       <c r="AE53" s="28" t="s">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="AF53" s="2"/>
     </row>
@@ -10914,35 +11001,35 @@
         <v>49</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>43</v>
+        <v>390</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="E54" s="24">
-        <f>+[49]Main!$I$2</f>
-        <v>58.06</v>
+        <f>+[47]Main!$I$2</f>
+        <v>3.75</v>
       </c>
       <c r="F54" s="17">
-        <f>+[49]Main!$I$4</f>
-        <v>2969.2344415800003</v>
+        <f>+[47]Main!$I$5*FX!C9</f>
+        <v>5271.5025720000003</v>
       </c>
       <c r="G54" s="17">
-        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
-        <v>-535.35400000000004</v>
+        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
+        <v>-653.85012000000006</v>
       </c>
       <c r="H54" s="17">
         <f t="shared" si="3"/>
-        <v>2433.8804415800005</v>
+        <v>4617.6524520000003</v>
       </c>
       <c r="I54" s="16" t="s">
-        <v>422</v>
+        <v>334</v>
       </c>
       <c r="J54" s="26">
-        <v>46233</v>
+        <v>45833</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="21"/>
@@ -10964,7 +11051,7 @@
       <c r="AB54" s="17"/>
       <c r="AC54" s="17"/>
       <c r="AD54" s="5">
-        <v>1938</v>
+        <v>1976</v>
       </c>
       <c r="AE54" s="28" t="s">
         <v>97</v>
@@ -10977,42 +11064,54 @@
         <v>50</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E55" s="24">
-        <f>+[50]Main!$J$2</f>
-        <v>77.790000000000006</v>
+        <f>+[48]Main!$I$2</f>
+        <v>148.80000000000001</v>
       </c>
       <c r="F55" s="17">
-        <f>+[50]Main!$J$4</f>
-        <v>3586.7484766800003</v>
+        <f>+[48]Main!$I$4</f>
+        <v>6512.5296000000008</v>
       </c>
       <c r="G55" s="17">
-        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
-        <v>1689.8000000000002</v>
+        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
+        <v>-637.99900000000002</v>
       </c>
       <c r="H55" s="17">
         <f>F55+G55</f>
-        <v>5276.54847668</v>
-      </c>
-      <c r="I55" s="16" t="s">
-        <v>827</v>
+        <v>5874.530600000001</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>805</v>
       </c>
       <c r="J55" s="26">
-        <v>46261</v>
-      </c>
-      <c r="K55" s="17"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="21"/>
-      <c r="P55" s="21"/>
+        <v>46350</v>
+      </c>
+      <c r="K55" s="17">
+        <v>4280.7</v>
+      </c>
+      <c r="L55" s="21">
+        <v>0.16</v>
+      </c>
+      <c r="M55" s="17">
+        <v>484.7</v>
+      </c>
+      <c r="N55" s="17">
+        <v>328.1</v>
+      </c>
+      <c r="O55" s="21">
+        <v>0.63</v>
+      </c>
+      <c r="P55" s="21">
+        <v>0.11</v>
+      </c>
       <c r="Q55" s="22"/>
       <c r="R55" s="22"/>
       <c r="S55" s="22"/>
@@ -11027,7 +11126,7 @@
       <c r="AB55" s="17"/>
       <c r="AC55" s="17"/>
       <c r="AD55" s="5">
-        <v>1881</v>
+        <v>1892</v>
       </c>
       <c r="AE55" s="28" t="s">
         <v>97</v>
@@ -11040,35 +11139,35 @@
         <v>51</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>417</v>
+        <v>43</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E56" s="24">
-        <f>+[51]Main!$I$2</f>
-        <v>2816.5</v>
+        <f>+[49]Main!$I$2</f>
+        <v>56.92</v>
       </c>
       <c r="F56" s="17">
-        <f>+[51]Main!$I$4*FX!C5</f>
-        <v>4393.7011297651507</v>
+        <f>+[49]Main!$I$4</f>
+        <v>2913.9166024800002</v>
       </c>
       <c r="G56" s="17">
-        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
-        <v>-837.64170000000001</v>
+        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
+        <v>-624.601</v>
       </c>
       <c r="H56" s="17">
-        <f>+F56+G56</f>
-        <v>3556.0594297651505</v>
+        <f t="shared" si="3"/>
+        <v>2289.3156024800001</v>
       </c>
       <c r="I56" s="16" t="s">
-        <v>338</v>
+        <v>805</v>
       </c>
       <c r="J56" s="26">
-        <v>45812</v>
+        <v>46324</v>
       </c>
       <c r="K56" s="17"/>
       <c r="L56" s="21"/>
@@ -11090,10 +11189,10 @@
       <c r="AB56" s="17"/>
       <c r="AC56" s="17"/>
       <c r="AD56" s="5">
-        <v>1985</v>
+        <v>1938</v>
       </c>
       <c r="AE56" s="28" t="s">
-        <v>431</v>
+        <v>97</v>
       </c>
       <c r="AF56" s="2"/>
     </row>
@@ -11103,34 +11202,36 @@
         <v>52</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>455</v>
+        <v>37</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="E57" s="24">
-        <f>+[52]Main!$I$2</f>
-        <v>10.93</v>
+        <f>+[50]Main!$J$2</f>
+        <v>72.459999999999994</v>
       </c>
       <c r="F57" s="17">
-        <f>+[52]Main!$I$4*FX!C3</f>
-        <v>4072.8677600000001</v>
+        <f>+[50]Main!$J$4</f>
+        <v>3343.1473791799999</v>
       </c>
       <c r="G57" s="17">
-        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
-        <v>-107.12</v>
+        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
+        <v>1270.5999999999999</v>
       </c>
       <c r="H57" s="17">
-        <f>+F57+G57</f>
-        <v>3965.7477600000002</v>
+        <f>F57+G57</f>
+        <v>4613.7473791800003</v>
       </c>
       <c r="I57" s="16" t="s">
-        <v>828</v>
-      </c>
-      <c r="J57" s="26"/>
+        <v>805</v>
+      </c>
+      <c r="J57" s="26">
+        <v>46359</v>
+      </c>
       <c r="K57" s="17"/>
       <c r="L57" s="21"/>
       <c r="M57" s="17"/>
@@ -11150,8 +11251,12 @@
       <c r="AA57" s="28"/>
       <c r="AB57" s="17"/>
       <c r="AC57" s="17"/>
-      <c r="AD57" s="5"/>
-      <c r="AE57" s="28"/>
+      <c r="AD57" s="5">
+        <v>1881</v>
+      </c>
+      <c r="AE57" s="28" t="s">
+        <v>97</v>
+      </c>
       <c r="AF57" s="2"/>
     </row>
     <row r="58" spans="1:32">
@@ -11160,35 +11265,35 @@
         <v>53</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>317</v>
+        <v>49</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>316</v>
+        <v>417</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="E58" s="24">
-        <f>+[53]Main!$I$2</f>
-        <v>165.1</v>
+        <f>+[51]Main!$I$2</f>
+        <v>2816.5</v>
       </c>
       <c r="F58" s="17">
-        <f>+[53]Main!$I$4</f>
-        <v>5044.7333572999996</v>
+        <f>+[51]Main!$I$4*FX!C5</f>
+        <v>4393.7011297651507</v>
       </c>
       <c r="G58" s="17">
-        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
-        <v>-95.319000000000003</v>
+        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
+        <v>-837.64170000000001</v>
       </c>
       <c r="H58" s="17">
-        <f t="shared" si="3"/>
-        <v>4949.4143572999992</v>
+        <f>+F58+G58</f>
+        <v>3556.0594297651505</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>806</v>
+        <v>338</v>
       </c>
       <c r="J58" s="26">
-        <v>45957</v>
+        <v>45812</v>
       </c>
       <c r="K58" s="17"/>
       <c r="L58" s="21"/>
@@ -11210,10 +11315,10 @@
       <c r="AB58" s="17"/>
       <c r="AC58" s="17"/>
       <c r="AD58" s="5">
-        <v>1978</v>
+        <v>1985</v>
       </c>
       <c r="AE58" s="28" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="AF58" s="2"/>
     </row>
@@ -11223,36 +11328,34 @@
         <v>54</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>411</v>
+        <v>48</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>318</v>
+        <v>455</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="E59" s="24">
-        <f>+[54]Main!$I$2</f>
-        <v>78.680000000000007</v>
+        <f>+[52]Main!$I$2</f>
+        <v>10.93</v>
       </c>
       <c r="F59" s="17">
-        <f>+[54]Main!$I$4</f>
-        <v>4372.5807311200006</v>
+        <f>+[52]Main!$I$4*FX!C3</f>
+        <v>4072.8677600000001</v>
       </c>
       <c r="G59" s="17">
-        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
-        <v>1259.028</v>
+        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
+        <v>-107.12</v>
       </c>
       <c r="H59" s="17">
-        <f t="shared" si="3"/>
-        <v>5631.6087311200008</v>
+        <f>+F59+G59</f>
+        <v>3965.7477600000002</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="J59" s="26">
-        <v>45960</v>
-      </c>
+        <v>827</v>
+      </c>
+      <c r="J59" s="26"/>
       <c r="K59" s="17"/>
       <c r="L59" s="21"/>
       <c r="M59" s="17"/>
@@ -11272,12 +11375,8 @@
       <c r="AA59" s="28"/>
       <c r="AB59" s="17"/>
       <c r="AC59" s="17"/>
-      <c r="AD59" s="5">
-        <v>2019</v>
-      </c>
-      <c r="AE59" s="28" t="s">
-        <v>412</v>
-      </c>
+      <c r="AD59" s="5"/>
+      <c r="AE59" s="28"/>
       <c r="AF59" s="2"/>
     </row>
     <row r="60" spans="1:32">
@@ -11286,26 +11385,40 @@
         <v>55</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>439</v>
+        <v>317</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>346</v>
+        <v>316</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E60" s="24" t="s">
-        <v>817</v>
-      </c>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="24"/>
+      <c r="E60" s="24">
+        <f>+[53]Main!$I$2</f>
+        <v>165.1</v>
+      </c>
+      <c r="F60" s="17">
+        <f>+[53]Main!$I$4</f>
+        <v>5044.7333572999996</v>
+      </c>
+      <c r="G60" s="17">
+        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
+        <v>-95.319000000000003</v>
+      </c>
+      <c r="H60" s="17">
+        <f t="shared" si="3"/>
+        <v>4949.4143572999992</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="J60" s="26">
+        <v>45957</v>
+      </c>
+      <c r="K60" s="17"/>
       <c r="L60" s="21"/>
-      <c r="M60" s="24"/>
-      <c r="N60" s="24"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
       <c r="O60" s="21"/>
       <c r="P60" s="21"/>
       <c r="Q60" s="22"/>
@@ -11321,9 +11434,11 @@
       <c r="AA60" s="28"/>
       <c r="AB60" s="17"/>
       <c r="AC60" s="17"/>
-      <c r="AD60" s="5"/>
+      <c r="AD60" s="5">
+        <v>1978</v>
+      </c>
       <c r="AE60" s="28" t="s">
-        <v>118</v>
+        <v>410</v>
       </c>
       <c r="AF60" s="2"/>
     </row>
@@ -11333,34 +11448,36 @@
         <v>56</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>50</v>
+        <v>411</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>456</v>
+        <v>318</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>433</v>
+        <v>21</v>
       </c>
       <c r="E61" s="24">
-        <f>+[55]Main!$J$2</f>
-        <v>132.5</v>
+        <f>+[54]Main!$I$2</f>
+        <v>78.680000000000007</v>
       </c>
       <c r="F61" s="17">
-        <f>+[55]Main!$J$4*FX!C15</f>
-        <v>3925.244925</v>
+        <f>+[54]Main!$I$4</f>
+        <v>4372.5807311200006</v>
       </c>
       <c r="G61" s="17">
-        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
-        <v>122.75229000000002</v>
+        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
+        <v>1259.028</v>
       </c>
       <c r="H61" s="17">
-        <f>+F61+G61</f>
-        <v>4047.9972149999999</v>
+        <f t="shared" si="3"/>
+        <v>5631.6087311200008</v>
       </c>
       <c r="I61" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="J61" s="26"/>
+        <v>149</v>
+      </c>
+      <c r="J61" s="26">
+        <v>45960</v>
+      </c>
       <c r="K61" s="17"/>
       <c r="L61" s="21"/>
       <c r="M61" s="17"/>
@@ -11380,8 +11497,12 @@
       <c r="AA61" s="28"/>
       <c r="AB61" s="17"/>
       <c r="AC61" s="17"/>
-      <c r="AD61" s="5"/>
-      <c r="AE61" s="28"/>
+      <c r="AD61" s="5">
+        <v>2019</v>
+      </c>
+      <c r="AE61" s="28" t="s">
+        <v>412</v>
+      </c>
       <c r="AF61" s="2"/>
     </row>
     <row r="62" spans="1:32">
@@ -11390,40 +11511,26 @@
         <v>57</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>150</v>
+        <v>439</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>151</v>
+        <v>346</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="24">
-        <f>+[56]Main!$J$2</f>
-        <v>161.28</v>
-      </c>
-      <c r="F62" s="17">
-        <f>+[56]Main!$J$4</f>
-        <v>2990.6024601600002</v>
-      </c>
-      <c r="G62" s="17">
-        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
-        <v>-211.91</v>
-      </c>
-      <c r="H62" s="17">
-        <f>+F62+G62</f>
-        <v>2778.6924601600003</v>
-      </c>
-      <c r="I62" s="16" t="s">
-        <v>812</v>
-      </c>
-      <c r="J62" s="26">
-        <v>45952</v>
-      </c>
-      <c r="K62" s="17"/>
+      <c r="E62" s="24" t="s">
+        <v>816</v>
+      </c>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="24"/>
       <c r="L62" s="21"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
+      <c r="M62" s="24"/>
+      <c r="N62" s="24"/>
       <c r="O62" s="21"/>
       <c r="P62" s="21"/>
       <c r="Q62" s="22"/>
@@ -11440,7 +11547,9 @@
       <c r="AB62" s="17"/>
       <c r="AC62" s="17"/>
       <c r="AD62" s="5"/>
-      <c r="AE62" s="28"/>
+      <c r="AE62" s="28" t="s">
+        <v>118</v>
+      </c>
       <c r="AF62" s="2"/>
     </row>
     <row r="63" spans="1:32">
@@ -11449,36 +11558,34 @@
         <v>58</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>696</v>
+        <v>456</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="E63" s="24">
-        <f>+[57]Main!$J$2</f>
-        <v>37.94</v>
+        <f>+[55]Main!$J$2</f>
+        <v>132.5</v>
       </c>
       <c r="F63" s="17">
-        <f>+[57]Main!$J$4*FX!C3</f>
-        <v>2723.2123110191997</v>
+        <f>+[55]Main!$J$4*FX!C15</f>
+        <v>3925.244925</v>
       </c>
       <c r="G63" s="17">
-        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
-        <v>-54.08</v>
+        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
+        <v>122.75229000000002</v>
       </c>
       <c r="H63" s="17">
         <f>+F63+G63</f>
-        <v>2669.1323110191997</v>
+        <v>4047.9972149999999</v>
       </c>
       <c r="I63" s="16" t="s">
-        <v>806</v>
-      </c>
-      <c r="J63" s="26">
-        <v>46329</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="J63" s="26"/>
       <c r="K63" s="17"/>
       <c r="L63" s="21"/>
       <c r="M63" s="17"/>
@@ -11508,35 +11615,35 @@
         <v>59</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="24">
-        <f>+[58]Main!$I$2</f>
-        <v>5.53</v>
+        <f>+[56]Main!$J$2</f>
+        <v>161.28</v>
       </c>
       <c r="F64" s="17">
-        <f>+[58]Main!$I$4</f>
-        <v>1932.9868362000002</v>
+        <f>+[56]Main!$J$4</f>
+        <v>2990.6024601600002</v>
       </c>
       <c r="G64" s="17">
-        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
-        <v>195.17700000000002</v>
+        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
+        <v>-211.91</v>
       </c>
       <c r="H64" s="17">
         <f>+F64+G64</f>
-        <v>2128.1638362000003</v>
+        <v>2778.6924601600003</v>
       </c>
       <c r="I64" s="16" t="s">
-        <v>874</v>
+        <v>811</v>
       </c>
       <c r="J64" s="26">
-        <v>46331</v>
+        <v>45952</v>
       </c>
       <c r="K64" s="17"/>
       <c r="L64" s="21"/>
@@ -11567,35 +11674,35 @@
         <v>60</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>327</v>
+        <v>53</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>328</v>
+        <v>696</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E65" s="24">
-        <f>+[59]Main!$I$2</f>
-        <v>14.35</v>
+        <f>+[57]Main!$J$2</f>
+        <v>37.94</v>
       </c>
       <c r="F65" s="17">
-        <f>+[59]Main!$I$4</f>
-        <v>2756.6605860499999</v>
+        <f>+[57]Main!$J$4*FX!C3</f>
+        <v>2723.2123110191997</v>
       </c>
       <c r="G65" s="17">
-        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
-        <v>-160.19499999999999</v>
+        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
+        <v>-54.08</v>
       </c>
       <c r="H65" s="17">
-        <f t="shared" ref="H65:H71" si="4">+F65+G65</f>
-        <v>2596.4655860499997</v>
+        <f>+F65+G65</f>
+        <v>2669.1323110191997</v>
       </c>
       <c r="I65" s="16" t="s">
-        <v>337</v>
+        <v>805</v>
       </c>
       <c r="J65" s="26">
-        <v>45723</v>
+        <v>46329</v>
       </c>
       <c r="K65" s="17"/>
       <c r="L65" s="21"/>
@@ -11626,34 +11733,36 @@
         <v>61</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>332</v>
+        <v>58</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>333</v>
+        <v>60</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E66" s="24">
-        <f>+[60]Main!$I$2</f>
-        <v>263.45</v>
+        <f>+[58]Main!$I$2</f>
+        <v>5.53</v>
       </c>
       <c r="F66" s="17">
-        <f>+[60]Main!$I$4*FX!C12</f>
-        <v>2976.4027894628493</v>
+        <f>+[58]Main!$I$4</f>
+        <v>1932.9868362000002</v>
       </c>
       <c r="G66" s="17">
-        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
-        <v>26.92503</v>
+        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
+        <v>195.17700000000002</v>
       </c>
       <c r="H66" s="17">
-        <f t="shared" si="4"/>
-        <v>3003.3278194628492</v>
+        <f>+F66+G66</f>
+        <v>2128.1638362000003</v>
       </c>
       <c r="I66" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="J66" s="26"/>
+        <v>873</v>
+      </c>
+      <c r="J66" s="26">
+        <v>46331</v>
+      </c>
       <c r="K66" s="17"/>
       <c r="L66" s="21"/>
       <c r="M66" s="17"/>
@@ -11682,41 +11791,39 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="B67" s="44" t="s">
-        <v>161</v>
+      <c r="B67" s="23" t="s">
+        <v>327</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>897</v>
+        <v>328</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E67" s="24">
-        <f>+[61]Main!$I$2</f>
-        <v>74.900000000000006</v>
+        <f>+[59]Main!$I$2</f>
+        <v>17.37</v>
       </c>
       <c r="F67" s="17">
-        <f>+[61]Main!$I$4</f>
-        <v>5953.9305021000009</v>
+        <f>+[59]Main!$I$4</f>
+        <v>2910.7487942100001</v>
       </c>
       <c r="G67" s="17">
-        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
-        <v>783</v>
+        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
+        <v>-18.286000000000001</v>
       </c>
       <c r="H67" s="17">
-        <f>F67+G67</f>
-        <v>6736.9305021000009</v>
-      </c>
-      <c r="I67" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="J67" s="26">
-        <v>46261</v>
-      </c>
-      <c r="K67" s="24"/>
+        <f t="shared" ref="H67:H73" si="4">+F67+G67</f>
+        <v>2892.4627942100001</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="J67" s="26"/>
+      <c r="K67" s="17"/>
       <c r="L67" s="21"/>
-      <c r="M67" s="24"/>
-      <c r="N67" s="24"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
       <c r="O67" s="21"/>
       <c r="P67" s="21"/>
       <c r="Q67" s="22"/>
@@ -11732,12 +11839,8 @@
       <c r="AA67" s="28"/>
       <c r="AB67" s="17"/>
       <c r="AC67" s="17"/>
-      <c r="AD67" s="5">
-        <v>1977</v>
-      </c>
-      <c r="AE67" s="28" t="s">
-        <v>118</v>
-      </c>
+      <c r="AD67" s="5"/>
+      <c r="AE67" s="28"/>
       <c r="AF67" s="2"/>
     </row>
     <row r="68" spans="1:32">
@@ -11746,36 +11849,34 @@
         <v>63</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>55</v>
+        <v>332</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E68" s="24">
-        <f>+[62]Main!$H$2</f>
-        <v>44.03</v>
+        <f>+[60]Main!$I$2</f>
+        <v>263.45</v>
       </c>
       <c r="F68" s="17">
-        <f>+[62]Main!$H$4</f>
-        <v>3217.9517470800001</v>
+        <f>+[60]Main!$I$4*FX!C12</f>
+        <v>2976.4027894628493</v>
       </c>
       <c r="G68" s="17">
-        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
-        <v>209.34100000000001</v>
+        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
+        <v>26.92503</v>
       </c>
       <c r="H68" s="17">
-        <f>+F68+G68</f>
-        <v>3427.29274708</v>
+        <f t="shared" si="4"/>
+        <v>3003.3278194628492</v>
       </c>
       <c r="I68" s="16" t="s">
-        <v>827</v>
-      </c>
-      <c r="J68" s="26">
-        <v>46232</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="J68" s="26"/>
       <c r="K68" s="17"/>
       <c r="L68" s="21"/>
       <c r="M68" s="17"/>
@@ -11804,41 +11905,41 @@
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="B69" s="23" t="s">
-        <v>319</v>
+      <c r="B69" s="44" t="s">
+        <v>161</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>320</v>
+        <v>896</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="E69" s="24">
-        <f>+[63]Main!$I$2</f>
-        <v>18.14</v>
+        <f>+[61]Main!$I$2</f>
+        <v>73.62</v>
       </c>
       <c r="F69" s="17">
-        <f>+[63]Main!$I$4</f>
-        <v>2154.9996926600002</v>
+        <f>+[61]Main!$I$4</f>
+        <v>5852.1810889800008</v>
       </c>
       <c r="G69" s="17">
-        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
-        <v>222</v>
+        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
+        <v>783</v>
       </c>
       <c r="H69" s="17">
-        <f>+F69+G69</f>
-        <v>2376.9996926600002</v>
-      </c>
-      <c r="I69" s="16" t="s">
-        <v>826</v>
+        <f>F69+G69</f>
+        <v>6635.1810889800008</v>
+      </c>
+      <c r="I69" s="25" t="s">
+        <v>805</v>
       </c>
       <c r="J69" s="26">
-        <v>46239</v>
-      </c>
-      <c r="K69" s="17"/>
+        <v>46360</v>
+      </c>
+      <c r="K69" s="24"/>
       <c r="L69" s="21"/>
-      <c r="M69" s="17"/>
-      <c r="N69" s="17"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="24"/>
       <c r="O69" s="21"/>
       <c r="P69" s="21"/>
       <c r="Q69" s="22"/>
@@ -11855,10 +11956,10 @@
       <c r="AB69" s="17"/>
       <c r="AC69" s="17"/>
       <c r="AD69" s="5">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="AE69" s="28" t="s">
-        <v>413</v>
+        <v>118</v>
       </c>
       <c r="AF69" s="2"/>
     </row>
@@ -11868,35 +11969,35 @@
         <v>65</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="E70" s="24">
-        <f>+[64]Main!$J$2</f>
-        <v>10.61</v>
+        <f>+[62]Main!$H$2</f>
+        <v>44.03</v>
       </c>
       <c r="F70" s="17">
-        <f>+[64]Main!$J$4*FX!C3</f>
-        <v>2791.9657083759998</v>
+        <f>+[62]Main!$H$4</f>
+        <v>3217.9517470800001</v>
       </c>
       <c r="G70" s="17">
-        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
-        <v>-53.418560000000006</v>
+        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
+        <v>209.34100000000001</v>
       </c>
       <c r="H70" s="17">
         <f>+F70+G70</f>
-        <v>2738.5471483759998</v>
+        <v>3427.29274708</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>422</v>
+        <v>826</v>
       </c>
       <c r="J70" s="26">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="21"/>
@@ -11927,35 +12028,35 @@
         <v>66</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>416</v>
+        <v>319</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E71" s="24">
-        <f>+[65]Main!$J$2</f>
-        <v>828.4</v>
+        <f>+[63]Main!$I$2</f>
+        <v>18.14</v>
       </c>
       <c r="F71" s="17">
-        <f>+[65]Main!$J$4*FX!C12</f>
-        <v>2214.6636811287999</v>
+        <f>+[63]Main!$I$4</f>
+        <v>2154.9996926600002</v>
       </c>
       <c r="G71" s="17">
-        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
-        <v>-1.8833099999999996</v>
+        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
+        <v>222</v>
       </c>
       <c r="H71" s="17">
-        <f t="shared" si="4"/>
-        <v>2212.7803711287997</v>
+        <f>+F71+G71</f>
+        <v>2376.9996926600002</v>
       </c>
       <c r="I71" s="16" t="s">
-        <v>380</v>
+        <v>825</v>
       </c>
       <c r="J71" s="26">
-        <v>45776</v>
+        <v>46239</v>
       </c>
       <c r="K71" s="17"/>
       <c r="L71" s="21"/>
@@ -11976,8 +12077,12 @@
       <c r="AA71" s="28"/>
       <c r="AB71" s="17"/>
       <c r="AC71" s="17"/>
-      <c r="AD71" s="5"/>
-      <c r="AE71" s="28"/>
+      <c r="AD71" s="5">
+        <v>1981</v>
+      </c>
+      <c r="AE71" s="28" t="s">
+        <v>413</v>
+      </c>
       <c r="AF71" s="2"/>
     </row>
     <row r="72" spans="1:32">
@@ -11985,19 +12090,37 @@
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C72" s="3">
-        <v>7453</v>
-      </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="16"/>
-      <c r="J72" s="26"/>
+      <c r="B72" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" s="24">
+        <f>+[64]Main!$J$2</f>
+        <v>11.0596</v>
+      </c>
+      <c r="F72" s="17">
+        <f>+[64]Main!$J$4*FX!C3</f>
+        <v>2910.2755841993599</v>
+      </c>
+      <c r="G72" s="17">
+        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
+        <v>-1.9947199999999772</v>
+      </c>
+      <c r="H72" s="17">
+        <f>+F72+G72</f>
+        <v>2908.2808641993597</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="J72" s="26">
+        <v>46317</v>
+      </c>
       <c r="K72" s="17"/>
       <c r="L72" s="21"/>
       <c r="M72" s="17"/>
@@ -12023,22 +12146,40 @@
     </row>
     <row r="73" spans="1:32">
       <c r="A73" s="15">
-        <f t="shared" ref="A73:A136" si="5">+A72+1</f>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C73" s="3">
-        <v>1467</v>
-      </c>
-      <c r="D73" s="2"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="16"/>
-      <c r="J73" s="26"/>
+      <c r="B73" s="23" t="s">
+        <v>416</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E73" s="24">
+        <f>+[65]Main!$J$2</f>
+        <v>828.4</v>
+      </c>
+      <c r="F73" s="17">
+        <f>+[65]Main!$J$4*FX!C12</f>
+        <v>2214.6636811287999</v>
+      </c>
+      <c r="G73" s="17">
+        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
+        <v>-1.8833099999999996</v>
+      </c>
+      <c r="H73" s="17">
+        <f t="shared" si="4"/>
+        <v>2212.7803711287997</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="J73" s="26">
+        <v>45776</v>
+      </c>
       <c r="K73" s="17"/>
       <c r="L73" s="21"/>
       <c r="M73" s="17"/>
@@ -12064,14 +12205,14 @@
     </row>
     <row r="74" spans="1:32">
       <c r="A74" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C74" s="3">
-        <v>9904</v>
+        <v>7453</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="24"/>
@@ -12105,14 +12246,14 @@
     </row>
     <row r="75" spans="1:32">
       <c r="A75" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A75:A139" si="5">+A74+1</f>
         <v>70</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1467</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="24"/>
@@ -12150,10 +12291,10 @@
         <v>71</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C76" s="3">
-        <v>551</v>
+        <v>9904</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="24"/>
@@ -12191,10 +12332,10 @@
         <v>72</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C77" s="3">
-        <v>1477</v>
+        <v>57</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="24"/>
@@ -12232,10 +12373,10 @@
         <v>73</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C78" s="3">
-        <v>8111</v>
+        <v>551</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="24"/>
@@ -12273,10 +12414,10 @@
         <v>74</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C79" s="32" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="C79" s="3">
+        <v>1477</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="24"/>
@@ -12314,10 +12455,10 @@
         <v>75</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C80" s="32" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="C80" s="3">
+        <v>8111</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="24"/>
@@ -12355,10 +12496,10 @@
         <v>76</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="24"/>
@@ -12396,10 +12537,10 @@
         <v>77</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>67</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="24"/>
@@ -12436,34 +12577,18 @@
         <f t="shared" si="5"/>
         <v>78</v>
       </c>
-      <c r="B83" s="23" t="s">
-        <v>75</v>
+      <c r="B83" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E83" s="24">
-        <f>+[66]Main!$I$2</f>
-        <v>5.82</v>
-      </c>
-      <c r="F83" s="17">
-        <f>+[66]Main!$I$4</f>
-        <v>2055.0937514400002</v>
-      </c>
-      <c r="G83" s="17">
-        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
-        <v>1971.2029999999997</v>
-      </c>
-      <c r="H83" s="17">
-        <f>+F83+G83</f>
-        <v>4026.2967514399998</v>
-      </c>
-      <c r="I83" s="16" t="s">
-        <v>338</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="24"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="16"/>
       <c r="J83" s="26"/>
       <c r="K83" s="17"/>
       <c r="L83" s="21"/>
@@ -12494,10 +12619,10 @@
         <v>79</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C84" s="3">
-        <v>382220</v>
+        <v>69</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="24"/>
@@ -12534,18 +12659,34 @@
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C85" s="3">
-        <v>1368</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="17"/>
-      <c r="G85" s="17"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="16"/>
+      <c r="B85" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E85" s="24">
+        <f>+[66]Main!$I$2</f>
+        <v>5.82</v>
+      </c>
+      <c r="F85" s="17">
+        <f>+[66]Main!$I$4</f>
+        <v>2055.0937514400002</v>
+      </c>
+      <c r="G85" s="17">
+        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
+        <v>1971.2029999999997</v>
+      </c>
+      <c r="H85" s="17">
+        <f>+F85+G85</f>
+        <v>4026.2967514399998</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>338</v>
+      </c>
       <c r="J85" s="26"/>
       <c r="K85" s="17"/>
       <c r="L85" s="21"/>
@@ -12576,14 +12717,12 @@
         <v>81</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>156</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C86" s="3">
+        <v>382220</v>
+      </c>
+      <c r="D86" s="2"/>
       <c r="E86" s="24"/>
       <c r="F86" s="17"/>
       <c r="G86" s="17"/>
@@ -12619,14 +12758,12 @@
         <v>82</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>159</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C87" s="3">
+        <v>1368</v>
+      </c>
+      <c r="D87" s="2"/>
       <c r="E87" s="24"/>
       <c r="F87" s="17"/>
       <c r="G87" s="17"/>
@@ -12662,13 +12799,13 @@
         <v>83</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>454</v>
+        <v>156</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="17"/>
@@ -12704,34 +12841,20 @@
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
-      <c r="B89" s="23" t="s">
-        <v>163</v>
+      <c r="B89" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E89" s="24">
-        <f>+[67]Main!$H$2</f>
-        <v>41.42</v>
-      </c>
-      <c r="F89" s="17">
-        <f>+[67]Main!$H$4</f>
-        <v>1491.5652650000002</v>
-      </c>
-      <c r="G89" s="17">
-        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
-        <v>85.194000000000017</v>
-      </c>
-      <c r="H89" s="17">
-        <f>+F89+G89</f>
-        <v>1576.7592650000001</v>
-      </c>
-      <c r="I89" s="16" t="s">
-        <v>338</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E89" s="24"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="17"/>
+      <c r="I89" s="16"/>
       <c r="J89" s="26"/>
       <c r="K89" s="17"/>
       <c r="L89" s="21"/>
@@ -12761,34 +12884,20 @@
         <f t="shared" si="5"/>
         <v>85</v>
       </c>
-      <c r="B90" s="23" t="s">
-        <v>167</v>
+      <c r="B90" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90" s="24">
-        <f>+[68]Main!$I$2</f>
-        <v>38.119999999999997</v>
-      </c>
-      <c r="F90" s="17">
-        <f>+[68]Main!$I$4</f>
-        <v>1935.4971035199997</v>
-      </c>
-      <c r="G90" s="17">
-        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
-        <v>-325.44000000000005</v>
-      </c>
-      <c r="H90" s="17">
-        <f>+F90+G90</f>
-        <v>1610.0571035199996</v>
-      </c>
-      <c r="I90" s="16" t="s">
-        <v>337</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="E90" s="24"/>
+      <c r="F90" s="17"/>
+      <c r="G90" s="17"/>
+      <c r="H90" s="17"/>
+      <c r="I90" s="16"/>
       <c r="J90" s="26"/>
       <c r="K90" s="17"/>
       <c r="L90" s="21"/>
@@ -12819,29 +12928,29 @@
         <v>86</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E91" s="24">
-        <f>+[69]Main!$I$2</f>
-        <v>24.73</v>
+        <f>+[67]Main!$H$2</f>
+        <v>41.42</v>
       </c>
       <c r="F91" s="17">
-        <f>+[69]Main!$I$4</f>
-        <v>1761.5194085300002</v>
+        <f>+[67]Main!$H$4</f>
+        <v>1491.5652650000002</v>
       </c>
       <c r="G91" s="17">
-        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
-        <v>-256.60000000000002</v>
+        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
+        <v>85.194000000000017</v>
       </c>
       <c r="H91" s="17">
         <f>+F91+G91</f>
-        <v>1504.9194085300001</v>
+        <v>1576.7592650000001</v>
       </c>
       <c r="I91" s="16" t="s">
         <v>338</v>
@@ -12866,12 +12975,8 @@
       <c r="AA91" s="28"/>
       <c r="AB91" s="17"/>
       <c r="AC91" s="17"/>
-      <c r="AD91" s="5">
-        <v>2003</v>
-      </c>
-      <c r="AE91" s="28" t="s">
-        <v>118</v>
-      </c>
+      <c r="AD91" s="5"/>
+      <c r="AE91" s="28"/>
       <c r="AF91" s="2"/>
     </row>
     <row r="92" spans="1:32">
@@ -12879,20 +12984,34 @@
         <f t="shared" si="5"/>
         <v>87</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>171</v>
+      <c r="B92" s="23" t="s">
+        <v>167</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="17"/>
-      <c r="G92" s="17"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E92" s="24">
+        <f>+[68]Main!$I$2</f>
+        <v>38.119999999999997</v>
+      </c>
+      <c r="F92" s="17">
+        <f>+[68]Main!$I$4</f>
+        <v>1935.4971035199997</v>
+      </c>
+      <c r="G92" s="17">
+        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
+        <v>-325.44000000000005</v>
+      </c>
+      <c r="H92" s="17">
+        <f>+F92+G92</f>
+        <v>1610.0571035199996</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>337</v>
+      </c>
       <c r="J92" s="26"/>
       <c r="K92" s="17"/>
       <c r="L92" s="21"/>
@@ -12922,20 +13041,34 @@
         <f t="shared" si="5"/>
         <v>88</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C93" s="32" t="s">
-        <v>175</v>
+      <c r="B93" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="17"/>
-      <c r="G93" s="17"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E93" s="24">
+        <f>+[69]Main!$I$2</f>
+        <v>24.73</v>
+      </c>
+      <c r="F93" s="17">
+        <f>+[69]Main!$I$4</f>
+        <v>1761.5194085300002</v>
+      </c>
+      <c r="G93" s="17">
+        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
+        <v>-256.60000000000002</v>
+      </c>
+      <c r="H93" s="17">
+        <f>+F93+G93</f>
+        <v>1504.9194085300001</v>
+      </c>
+      <c r="I93" s="16" t="s">
+        <v>338</v>
+      </c>
       <c r="J93" s="26"/>
       <c r="K93" s="17"/>
       <c r="L93" s="21"/>
@@ -12956,8 +13089,12 @@
       <c r="AA93" s="28"/>
       <c r="AB93" s="17"/>
       <c r="AC93" s="17"/>
-      <c r="AD93" s="5"/>
-      <c r="AE93" s="28"/>
+      <c r="AD93" s="5">
+        <v>2003</v>
+      </c>
+      <c r="AE93" s="28" t="s">
+        <v>118</v>
+      </c>
       <c r="AF93" s="2"/>
     </row>
     <row r="94" spans="1:32">
@@ -12966,13 +13103,13 @@
         <v>89</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="17"/>
@@ -13009,38 +13146,40 @@
         <v>90</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>178</v>
+        <v>479</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>179</v>
+        <v>480</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E95" s="24">
-        <f>+[70]Main!$I$2</f>
-        <v>27.07</v>
+        <f>+[79]Main!$J$2</f>
+        <v>19.989999999999998</v>
       </c>
       <c r="F95" s="17">
-        <f>+[70]Main!$I$4</f>
-        <v>1188.01315849</v>
+        <f>+[79]Main!$J$4</f>
+        <v>1640.5061166099999</v>
       </c>
       <c r="G95" s="17">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
-        <v>119.48899999999998</v>
+        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
+        <v>388.6</v>
       </c>
       <c r="H95" s="17">
         <f>+F95+G95</f>
-        <v>1307.5021584900001</v>
+        <v>2029.1061166099998</v>
       </c>
       <c r="I95" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="J95" s="26"/>
-      <c r="K95" s="17"/>
+        <v>422</v>
+      </c>
+      <c r="J95" s="26">
+        <v>46149</v>
+      </c>
+      <c r="K95" s="24"/>
       <c r="L95" s="21"/>
-      <c r="M95" s="17"/>
-      <c r="N95" s="17"/>
+      <c r="M95" s="24"/>
+      <c r="N95" s="24"/>
       <c r="O95" s="21"/>
       <c r="P95" s="21"/>
       <c r="Q95" s="22"/>
@@ -13065,34 +13204,20 @@
         <f t="shared" si="5"/>
         <v>91</v>
       </c>
-      <c r="B96" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>181</v>
+      <c r="B96" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C96" s="32" t="s">
+        <v>175</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E96" s="24">
-        <f>+[71]Main!$I$2</f>
-        <v>59.85</v>
-      </c>
-      <c r="F96" s="17">
-        <f>+[71]Main!$I$4</f>
-        <v>939.70682505000002</v>
-      </c>
-      <c r="G96" s="17">
-        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
-        <v>50.789000000000001</v>
-      </c>
-      <c r="H96" s="17">
-        <f>+F96+G96</f>
-        <v>990.49582505000001</v>
-      </c>
-      <c r="I96" s="16" t="s">
-        <v>337</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E96" s="24"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="16"/>
       <c r="J96" s="26"/>
       <c r="K96" s="17"/>
       <c r="L96" s="21"/>
@@ -13122,37 +13247,21 @@
         <f t="shared" si="5"/>
         <v>92</v>
       </c>
-      <c r="B97" s="23" t="s">
-        <v>395</v>
+      <c r="B97" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E97" s="24">
-        <f>+[72]Main!$J$2</f>
-        <v>12.17</v>
-      </c>
-      <c r="F97" s="17">
-        <f>+[72]Main!$J$4*FX!C13</f>
-        <v>817.17420560790003</v>
-      </c>
-      <c r="G97" s="17">
-        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
-        <v>158.286</v>
-      </c>
-      <c r="H97" s="17">
-        <f>+F97+G97</f>
-        <v>975.46020560789998</v>
-      </c>
-      <c r="I97" s="16" t="s">
-        <v>873</v>
-      </c>
-      <c r="J97" s="26">
-        <v>46331</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="17"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="26"/>
       <c r="K97" s="17"/>
       <c r="L97" s="21"/>
       <c r="M97" s="17"/>
@@ -13181,20 +13290,34 @@
         <f t="shared" si="5"/>
         <v>93</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>183</v>
+      <c r="B98" s="23" t="s">
+        <v>178</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="17"/>
-      <c r="G98" s="17"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E98" s="24">
+        <f>+[70]Main!$I$2</f>
+        <v>27.07</v>
+      </c>
+      <c r="F98" s="17">
+        <f>+[70]Main!$I$4</f>
+        <v>1188.01315849</v>
+      </c>
+      <c r="G98" s="17">
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <v>119.48899999999998</v>
+      </c>
+      <c r="H98" s="17">
+        <f>+F98+G98</f>
+        <v>1307.5021584900001</v>
+      </c>
+      <c r="I98" s="16" t="s">
+        <v>337</v>
+      </c>
       <c r="J98" s="26"/>
       <c r="K98" s="17"/>
       <c r="L98" s="21"/>
@@ -13224,20 +13347,34 @@
         <f t="shared" si="5"/>
         <v>94</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>186</v>
+      <c r="B99" s="23" t="s">
+        <v>180</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="17"/>
-      <c r="G99" s="17"/>
-      <c r="H99" s="17"/>
-      <c r="I99" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E99" s="24">
+        <f>+[71]Main!$I$2</f>
+        <v>59.85</v>
+      </c>
+      <c r="F99" s="17">
+        <f>+[71]Main!$I$4</f>
+        <v>939.70682505000002</v>
+      </c>
+      <c r="G99" s="17">
+        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
+        <v>50.789000000000001</v>
+      </c>
+      <c r="H99" s="17">
+        <f>+F99+G99</f>
+        <v>990.49582505000001</v>
+      </c>
+      <c r="I99" s="16" t="s">
+        <v>337</v>
+      </c>
       <c r="J99" s="26"/>
       <c r="K99" s="17"/>
       <c r="L99" s="21"/>
@@ -13268,34 +13405,36 @@
         <v>95</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>189</v>
+        <v>395</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E100" s="24">
-        <f>+[73]Main!$I$2</f>
-        <v>4.53</v>
+        <f>+[72]Main!$J$2</f>
+        <v>12.17</v>
       </c>
       <c r="F100" s="17">
-        <f>+[73]Main!$I$4</f>
-        <v>736.21656488999997</v>
+        <f>+[72]Main!$J$4*FX!C13</f>
+        <v>817.17420560790003</v>
       </c>
       <c r="G100" s="17">
-        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
-        <v>-235.51</v>
+        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
+        <v>158.286</v>
       </c>
       <c r="H100" s="17">
         <f>+F100+G100</f>
-        <v>500.70656488999998</v>
+        <v>975.46020560789998</v>
       </c>
       <c r="I100" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="J100" s="26"/>
+        <v>872</v>
+      </c>
+      <c r="J100" s="26">
+        <v>46331</v>
+      </c>
       <c r="K100" s="17"/>
       <c r="L100" s="21"/>
       <c r="M100" s="17"/>
@@ -13324,34 +13463,20 @@
         <f t="shared" si="5"/>
         <v>96</v>
       </c>
-      <c r="B101" s="23" t="s">
-        <v>191</v>
+      <c r="B101" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E101" s="24">
-        <f>+[74]Main!$I$2</f>
-        <v>16.75</v>
-      </c>
-      <c r="F101" s="17">
-        <f>+[74]Main!$I$4</f>
-        <v>872.38125524999998</v>
-      </c>
-      <c r="G101" s="17">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
-        <v>434.077</v>
-      </c>
-      <c r="H101" s="17">
-        <f>+F101+G101</f>
-        <v>1306.4582552500001</v>
-      </c>
-      <c r="I101" s="16" t="s">
-        <v>149</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="E101" s="24"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="17"/>
+      <c r="H101" s="17"/>
+      <c r="I101" s="16"/>
       <c r="J101" s="26"/>
       <c r="K101" s="17"/>
       <c r="L101" s="21"/>
@@ -13382,10 +13507,10 @@
         <v>97</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>188</v>
@@ -13424,20 +13549,34 @@
         <f t="shared" si="5"/>
         <v>98</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>195</v>
+      <c r="B103" s="23" t="s">
+        <v>189</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E103" s="24"/>
-      <c r="F103" s="17"/>
-      <c r="G103" s="17"/>
-      <c r="H103" s="17"/>
-      <c r="I103" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E103" s="24">
+        <f>+[73]Main!$I$2</f>
+        <v>4.53</v>
+      </c>
+      <c r="F103" s="17">
+        <f>+[73]Main!$I$4</f>
+        <v>736.21656488999997</v>
+      </c>
+      <c r="G103" s="17">
+        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
+        <v>-235.51</v>
+      </c>
+      <c r="H103" s="17">
+        <f>+F103+G103</f>
+        <v>500.70656488999998</v>
+      </c>
+      <c r="I103" s="16" t="s">
+        <v>338</v>
+      </c>
       <c r="J103" s="26"/>
       <c r="K103" s="17"/>
       <c r="L103" s="21"/>
@@ -13467,20 +13606,34 @@
         <f t="shared" si="5"/>
         <v>99</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>198</v>
+      <c r="B104" s="23" t="s">
+        <v>191</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E104" s="24"/>
-      <c r="F104" s="17"/>
-      <c r="G104" s="17"/>
-      <c r="H104" s="17"/>
-      <c r="I104" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E104" s="24">
+        <f>+[74]Main!$I$2</f>
+        <v>16.75</v>
+      </c>
+      <c r="F104" s="17">
+        <f>+[74]Main!$I$4</f>
+        <v>872.38125524999998</v>
+      </c>
+      <c r="G104" s="17">
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <v>434.077</v>
+      </c>
+      <c r="H104" s="17">
+        <f>+F104+G104</f>
+        <v>1306.4582552500001</v>
+      </c>
+      <c r="I104" s="16" t="s">
+        <v>149</v>
+      </c>
       <c r="J104" s="26"/>
       <c r="K104" s="17"/>
       <c r="L104" s="21"/>
@@ -13511,13 +13664,13 @@
         <v>100</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="17"/>
@@ -13554,13 +13707,13 @@
         <v>101</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="17"/>
@@ -13597,13 +13750,13 @@
         <v>102</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="17"/>
@@ -13640,13 +13793,13 @@
         <v>103</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>109</v>
+        <v>185</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="17"/>
@@ -13683,13 +13836,13 @@
         <v>104</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="17"/>
@@ -13726,13 +13879,13 @@
         <v>105</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="17"/>
@@ -13769,13 +13922,13 @@
         <v>106</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="17"/>
@@ -13812,13 +13965,13 @@
         <v>107</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="17"/>
@@ -13855,13 +14008,13 @@
         <v>108</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="17"/>
@@ -13898,13 +14051,13 @@
         <v>109</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="17"/>
@@ -13941,13 +14094,13 @@
         <v>110</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="17"/>
@@ -13983,39 +14136,25 @@
         <f t="shared" si="5"/>
         <v>111</v>
       </c>
-      <c r="B116" s="23" t="s">
-        <v>212</v>
+      <c r="B116" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>335</v>
+        <v>220</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E116" s="24">
-        <f>+'[75]Main '!$F$2</f>
-        <v>2.4350000000000001</v>
-      </c>
-      <c r="F116" s="17">
-        <f>+'[75]Main '!$F$4*FX!C8</f>
-        <v>360.19879762439996</v>
-      </c>
-      <c r="G116" s="17">
-        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
-        <v>229.02800000000005</v>
-      </c>
-      <c r="H116" s="17">
-        <f>+F116+G116</f>
-        <v>589.22679762439998</v>
-      </c>
-      <c r="I116" s="16" t="s">
-        <v>422</v>
-      </c>
+      <c r="E116" s="24"/>
+      <c r="F116" s="17"/>
+      <c r="G116" s="17"/>
+      <c r="H116" s="17"/>
+      <c r="I116" s="16"/>
       <c r="J116" s="26"/>
-      <c r="K116" s="24"/>
+      <c r="K116" s="17"/>
       <c r="L116" s="21"/>
-      <c r="M116" s="24"/>
-      <c r="N116" s="24"/>
+      <c r="M116" s="17"/>
+      <c r="N116" s="17"/>
       <c r="O116" s="21"/>
       <c r="P116" s="21"/>
       <c r="Q116" s="22"/>
@@ -14041,13 +14180,13 @@
         <v>112</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="17"/>
@@ -14084,13 +14223,13 @@
         <v>113</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="17"/>
@@ -14126,25 +14265,39 @@
         <f t="shared" si="5"/>
         <v>114</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>230</v>
+      <c r="B119" s="23" t="s">
+        <v>212</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>231</v>
+        <v>335</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E119" s="24"/>
-      <c r="F119" s="17"/>
-      <c r="G119" s="17"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="16"/>
+        <v>219</v>
+      </c>
+      <c r="E119" s="24">
+        <f>+'[75]Main '!$F$2</f>
+        <v>2.4350000000000001</v>
+      </c>
+      <c r="F119" s="17">
+        <f>+'[75]Main '!$F$4*FX!C8</f>
+        <v>360.19879762439996</v>
+      </c>
+      <c r="G119" s="17">
+        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
+        <v>229.02800000000005</v>
+      </c>
+      <c r="H119" s="17">
+        <f>+F119+G119</f>
+        <v>589.22679762439998</v>
+      </c>
+      <c r="I119" s="16" t="s">
+        <v>422</v>
+      </c>
       <c r="J119" s="26"/>
-      <c r="K119" s="17"/>
+      <c r="K119" s="24"/>
       <c r="L119" s="21"/>
-      <c r="M119" s="17"/>
-      <c r="N119" s="17"/>
+      <c r="M119" s="24"/>
+      <c r="N119" s="24"/>
       <c r="O119" s="21"/>
       <c r="P119" s="21"/>
       <c r="Q119" s="22"/>
@@ -14170,13 +14323,13 @@
         <v>115</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="17"/>
@@ -14213,13 +14366,13 @@
         <v>116</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="17"/>
@@ -14256,10 +14409,10 @@
         <v>117</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>185</v>
@@ -14298,34 +14451,20 @@
         <f t="shared" si="5"/>
         <v>118</v>
       </c>
-      <c r="B123" s="23" t="s">
-        <v>242</v>
+      <c r="B123" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E123" s="24">
-        <f>+[76]Main!$H$2</f>
-        <v>0.98</v>
-      </c>
-      <c r="F123" s="17">
-        <f>+[76]Main!$H$4</f>
-        <v>97.21301296</v>
-      </c>
-      <c r="G123" s="17">
-        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
-        <v>274.101</v>
-      </c>
-      <c r="H123" s="17">
-        <f>+F123+G123</f>
-        <v>371.31401296000001</v>
-      </c>
-      <c r="I123" s="16" t="s">
-        <v>812</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E123" s="24"/>
+      <c r="F123" s="17"/>
+      <c r="G123" s="17"/>
+      <c r="H123" s="17"/>
+      <c r="I123" s="16"/>
       <c r="J123" s="26"/>
       <c r="K123" s="17"/>
       <c r="L123" s="21"/>
@@ -14356,13 +14495,13 @@
         <v>119</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="17"/>
@@ -14398,34 +14537,20 @@
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="B125" s="44" t="s">
-        <v>246</v>
+      <c r="B125" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E125" s="24">
-        <f>+[77]Main!$I$2</f>
-        <v>17.79</v>
-      </c>
-      <c r="F125" s="17">
-        <f>+[77]Main!$I$4</f>
-        <v>270.90115659000003</v>
-      </c>
-      <c r="G125" s="17">
-        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
-        <v>24.493000000000002</v>
-      </c>
-      <c r="H125" s="17">
-        <f>+F125+G125</f>
-        <v>295.39415659000002</v>
-      </c>
-      <c r="I125" s="16" t="s">
-        <v>149</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="E125" s="24"/>
+      <c r="F125" s="17"/>
+      <c r="G125" s="17"/>
+      <c r="H125" s="17"/>
+      <c r="I125" s="16"/>
       <c r="J125" s="26"/>
       <c r="K125" s="17"/>
       <c r="L125" s="21"/>
@@ -14455,20 +14580,34 @@
         <f t="shared" si="5"/>
         <v>121</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>248</v>
+      <c r="B126" s="23" t="s">
+        <v>242</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E126" s="24"/>
-      <c r="F126" s="17"/>
-      <c r="G126" s="17"/>
-      <c r="H126" s="17"/>
-      <c r="I126" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E126" s="24">
+        <f>+[76]Main!$H$2</f>
+        <v>0.98</v>
+      </c>
+      <c r="F126" s="17">
+        <f>+[76]Main!$H$4</f>
+        <v>97.21301296</v>
+      </c>
+      <c r="G126" s="17">
+        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
+        <v>274.101</v>
+      </c>
+      <c r="H126" s="17">
+        <f>+F126+G126</f>
+        <v>371.31401296000001</v>
+      </c>
+      <c r="I126" s="16" t="s">
+        <v>811</v>
+      </c>
       <c r="J126" s="26"/>
       <c r="K126" s="17"/>
       <c r="L126" s="21"/>
@@ -14499,13 +14638,13 @@
         <v>122</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="17"/>
@@ -14541,20 +14680,34 @@
         <f t="shared" si="5"/>
         <v>123</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C128" s="32" t="s">
-        <v>253</v>
+      <c r="B128" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="17"/>
-      <c r="G128" s="17"/>
-      <c r="H128" s="17"/>
-      <c r="I128" s="16"/>
+        <v>21</v>
+      </c>
+      <c r="E128" s="24">
+        <f>+[77]Main!$I$2</f>
+        <v>17.79</v>
+      </c>
+      <c r="F128" s="17">
+        <f>+[77]Main!$I$4</f>
+        <v>270.90115659000003</v>
+      </c>
+      <c r="G128" s="17">
+        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
+        <v>24.493000000000002</v>
+      </c>
+      <c r="H128" s="17">
+        <f>+F128+G128</f>
+        <v>295.39415659000002</v>
+      </c>
+      <c r="I128" s="16" t="s">
+        <v>149</v>
+      </c>
       <c r="J128" s="26"/>
       <c r="K128" s="17"/>
       <c r="L128" s="21"/>
@@ -14585,13 +14738,13 @@
         <v>124</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="17"/>
@@ -14628,10 +14781,10 @@
         <v>125</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>21</v>
@@ -14642,10 +14795,10 @@
       <c r="H130" s="17"/>
       <c r="I130" s="16"/>
       <c r="J130" s="26"/>
-      <c r="K130" s="24"/>
+      <c r="K130" s="17"/>
       <c r="L130" s="21"/>
-      <c r="M130" s="24"/>
-      <c r="N130" s="24"/>
+      <c r="M130" s="17"/>
+      <c r="N130" s="17"/>
       <c r="O130" s="21"/>
       <c r="P130" s="21"/>
       <c r="Q130" s="22"/>
@@ -14671,13 +14824,13 @@
         <v>126</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
+      </c>
+      <c r="C131" s="32" t="s">
+        <v>253</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="17"/>
@@ -14714,13 +14867,13 @@
         <v>127</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="17"/>
@@ -14757,13 +14910,13 @@
         <v>128</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="17"/>
@@ -14771,10 +14924,10 @@
       <c r="H133" s="17"/>
       <c r="I133" s="16"/>
       <c r="J133" s="26"/>
-      <c r="K133" s="17"/>
+      <c r="K133" s="24"/>
       <c r="L133" s="21"/>
-      <c r="M133" s="17"/>
-      <c r="N133" s="17"/>
+      <c r="M133" s="24"/>
+      <c r="N133" s="24"/>
       <c r="O133" s="21"/>
       <c r="P133" s="21"/>
       <c r="Q133" s="22"/>
@@ -14800,13 +14953,13 @@
         <v>129</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="17"/>
@@ -14843,13 +14996,13 @@
         <v>130</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="17"/>
@@ -14886,13 +15039,13 @@
         <v>131</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>269</v>
+        <v>166</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="17"/>
@@ -14925,17 +15078,17 @@
     </row>
     <row r="137" spans="1:32">
       <c r="A137" s="15">
-        <f t="shared" ref="A137:A181" si="6">+A136+1</f>
+        <f t="shared" si="5"/>
         <v>132</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="17"/>
@@ -14943,10 +15096,10 @@
       <c r="H137" s="17"/>
       <c r="I137" s="16"/>
       <c r="J137" s="26"/>
-      <c r="K137" s="24"/>
+      <c r="K137" s="17"/>
       <c r="L137" s="21"/>
-      <c r="M137" s="24"/>
-      <c r="N137" s="24"/>
+      <c r="M137" s="17"/>
+      <c r="N137" s="17"/>
       <c r="O137" s="21"/>
       <c r="P137" s="21"/>
       <c r="Q137" s="22"/>
@@ -14968,17 +15121,17 @@
     </row>
     <row r="138" spans="1:32">
       <c r="A138" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>133</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="17"/>
@@ -15011,17 +15164,17 @@
     </row>
     <row r="139" spans="1:32">
       <c r="A139" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>134</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>21</v>
+        <v>269</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="17"/>
@@ -15054,17 +15207,17 @@
     </row>
     <row r="140" spans="1:32">
       <c r="A140" s="15">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A140:A183" si="6">+A139+1</f>
         <v>135</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C140" s="32" t="s">
-        <v>277</v>
+        <v>265</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="17"/>
@@ -15072,10 +15225,10 @@
       <c r="H140" s="17"/>
       <c r="I140" s="16"/>
       <c r="J140" s="26"/>
-      <c r="K140" s="17"/>
+      <c r="K140" s="24"/>
       <c r="L140" s="21"/>
-      <c r="M140" s="17"/>
-      <c r="N140" s="17"/>
+      <c r="M140" s="24"/>
+      <c r="N140" s="24"/>
       <c r="O140" s="21"/>
       <c r="P140" s="21"/>
       <c r="Q140" s="22"/>
@@ -15101,13 +15254,13 @@
         <v>136</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="17"/>
@@ -15144,13 +15297,13 @@
         <v>137</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="17"/>
@@ -15187,13 +15340,13 @@
         <v>138</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
+      </c>
+      <c r="C143" s="32" t="s">
+        <v>277</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="17"/>
@@ -15230,13 +15383,13 @@
         <v>139</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="17"/>
@@ -15273,13 +15426,13 @@
         <v>140</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="17"/>
@@ -15316,10 +15469,10 @@
         <v>141</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>21</v>
@@ -15330,7 +15483,7 @@
       <c r="H146" s="17"/>
       <c r="I146" s="16"/>
       <c r="J146" s="26"/>
-      <c r="K146" s="24"/>
+      <c r="K146" s="17"/>
       <c r="L146" s="21"/>
       <c r="M146" s="17"/>
       <c r="N146" s="17"/>
@@ -15359,13 +15512,13 @@
         <v>142</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="17"/>
@@ -15373,10 +15526,10 @@
       <c r="H147" s="17"/>
       <c r="I147" s="16"/>
       <c r="J147" s="26"/>
-      <c r="K147" s="24"/>
+      <c r="K147" s="17"/>
       <c r="L147" s="21"/>
-      <c r="M147" s="24"/>
-      <c r="N147" s="24"/>
+      <c r="M147" s="17"/>
+      <c r="N147" s="17"/>
       <c r="O147" s="21"/>
       <c r="P147" s="21"/>
       <c r="Q147" s="22"/>
@@ -15402,13 +15555,13 @@
         <v>143</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="17"/>
@@ -15416,10 +15569,10 @@
       <c r="H148" s="17"/>
       <c r="I148" s="16"/>
       <c r="J148" s="26"/>
-      <c r="K148" s="24"/>
+      <c r="K148" s="17"/>
       <c r="L148" s="21"/>
-      <c r="M148" s="24"/>
-      <c r="N148" s="24"/>
+      <c r="M148" s="17"/>
+      <c r="N148" s="17"/>
       <c r="O148" s="21"/>
       <c r="P148" s="21"/>
       <c r="Q148" s="22"/>
@@ -15445,10 +15598,10 @@
         <v>144</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>21</v>
@@ -15461,8 +15614,8 @@
       <c r="J149" s="26"/>
       <c r="K149" s="24"/>
       <c r="L149" s="21"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
+      <c r="M149" s="17"/>
+      <c r="N149" s="17"/>
       <c r="O149" s="21"/>
       <c r="P149" s="21"/>
       <c r="Q149" s="22"/>
@@ -15488,13 +15641,13 @@
         <v>145</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="17"/>
@@ -15531,13 +15684,13 @@
         <v>146</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>21</v>
+        <v>294</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="17"/>
@@ -15574,10 +15727,10 @@
         <v>147</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>21</v>
@@ -15617,13 +15770,13 @@
         <v>148</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="17"/>
@@ -15659,34 +15812,20 @@
         <f t="shared" si="6"/>
         <v>149</v>
       </c>
-      <c r="B154" s="23" t="s">
-        <v>477</v>
+      <c r="B154" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>478</v>
+        <v>298</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E154" s="24">
-        <f>+[78]Main!$I$2</f>
-        <v>2540</v>
-      </c>
-      <c r="F154" s="17">
-        <f>+[78]Main!$I$4*FX!C5</f>
-        <v>409.27593709799999</v>
-      </c>
-      <c r="G154" s="17">
-        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
-        <v>-123.31619999999999</v>
-      </c>
-      <c r="H154" s="17">
-        <f>+F154+G154</f>
-        <v>285.95973709800001</v>
-      </c>
-      <c r="I154" s="16" t="s">
-        <v>337</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E154" s="24"/>
+      <c r="F154" s="17"/>
+      <c r="G154" s="17"/>
+      <c r="H154" s="17"/>
+      <c r="I154" s="16"/>
       <c r="J154" s="26"/>
       <c r="K154" s="24"/>
       <c r="L154" s="21"/>
@@ -15716,37 +15855,21 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="B155" s="23" t="s">
-        <v>479</v>
+      <c r="B155" s="2" t="s">
+        <v>301</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>480</v>
+        <v>302</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E155" s="24">
-        <f>+[79]Main!$J$2</f>
-        <v>19.989999999999998</v>
-      </c>
-      <c r="F155" s="17">
-        <f>+[79]Main!$J$4</f>
-        <v>1640.5061166099999</v>
-      </c>
-      <c r="G155" s="17">
-        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
-        <v>388.6</v>
-      </c>
-      <c r="H155" s="17">
-        <f>+F155+G155</f>
-        <v>2029.1061166099998</v>
-      </c>
-      <c r="I155" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="J155" s="26">
-        <v>46149</v>
-      </c>
+      <c r="E155" s="24"/>
+      <c r="F155" s="17"/>
+      <c r="G155" s="17"/>
+      <c r="H155" s="17"/>
+      <c r="I155" s="16"/>
+      <c r="J155" s="26"/>
       <c r="K155" s="24"/>
       <c r="L155" s="21"/>
       <c r="M155" s="24"/>
@@ -15776,13 +15899,13 @@
         <v>151</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>482</v>
+        <v>305</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>481</v>
+        <v>304</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>124</v>
+        <v>303</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="17"/>
@@ -15818,20 +15941,34 @@
         <f t="shared" si="6"/>
         <v>152</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>483</v>
+      <c r="B157" s="23" t="s">
+        <v>477</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="17"/>
-      <c r="G157" s="17"/>
-      <c r="H157" s="17"/>
-      <c r="I157" s="16"/>
+        <v>124</v>
+      </c>
+      <c r="E157" s="24">
+        <f>+[78]Main!$I$2</f>
+        <v>2540</v>
+      </c>
+      <c r="F157" s="17">
+        <f>+[78]Main!$I$4*FX!C5</f>
+        <v>409.27593709799999</v>
+      </c>
+      <c r="G157" s="17">
+        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
+        <v>-123.31619999999999</v>
+      </c>
+      <c r="H157" s="17">
+        <f>+F157+G157</f>
+        <v>285.95973709800001</v>
+      </c>
+      <c r="I157" s="16" t="s">
+        <v>337</v>
+      </c>
       <c r="J157" s="26"/>
       <c r="K157" s="24"/>
       <c r="L157" s="21"/>
@@ -15862,10 +15999,10 @@
         <v>153</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>124</v>
@@ -15905,10 +16042,10 @@
         <v>154</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>21</v>
@@ -15948,13 +16085,13 @@
         <v>155</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>294</v>
+        <v>124</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="17"/>
@@ -15991,13 +16128,13 @@
         <v>156</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="17"/>
@@ -16034,13 +16171,13 @@
         <v>157</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="17"/>
@@ -16077,13 +16214,13 @@
         <v>158</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="17"/>
@@ -16120,13 +16257,13 @@
         <v>159</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E164" s="24"/>
       <c r="F164" s="17"/>
@@ -16163,13 +16300,13 @@
         <v>160</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E165" s="24"/>
       <c r="F165" s="17"/>
@@ -16206,13 +16343,13 @@
         <v>161</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="E166" s="24"/>
       <c r="F166" s="17"/>
@@ -16249,13 +16386,13 @@
         <v>162</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E167" s="24"/>
       <c r="F167" s="17"/>
@@ -16292,13 +16429,13 @@
         <v>163</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>378</v>
+        <v>504</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>506</v>
+        <v>352</v>
       </c>
       <c r="E168" s="24"/>
       <c r="F168" s="17"/>
@@ -16335,10 +16472,10 @@
         <v>164</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>21</v>
@@ -16378,13 +16515,13 @@
         <v>165</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>510</v>
+        <v>378</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>21</v>
+        <v>506</v>
       </c>
       <c r="E170" s="24"/>
       <c r="F170" s="17"/>
@@ -16421,13 +16558,13 @@
         <v>166</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="E171" s="24"/>
       <c r="F171" s="17"/>
@@ -16464,13 +16601,13 @@
         <v>167</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E172" s="24"/>
       <c r="F172" s="17"/>
@@ -16507,13 +16644,13 @@
         <v>168</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="E173" s="24"/>
       <c r="F173" s="17"/>
@@ -16550,13 +16687,13 @@
         <v>169</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="E174" s="24"/>
       <c r="F174" s="17"/>
@@ -16593,10 +16730,10 @@
         <v>170</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>21</v>
@@ -16636,10 +16773,10 @@
         <v>171</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>21</v>
@@ -16679,10 +16816,10 @@
         <v>172</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>21</v>
@@ -16722,13 +16859,13 @@
         <v>173</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>526</v>
+        <v>21</v>
       </c>
       <c r="E178" s="24"/>
       <c r="F178" s="17"/>
@@ -16765,10 +16902,10 @@
         <v>174</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>21</v>
@@ -16808,13 +16945,13 @@
         <v>175</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>672</v>
+        <v>527</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="E180" s="24"/>
       <c r="F180" s="17"/>
@@ -16851,10 +16988,10 @@
         <v>176</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>673</v>
+        <v>529</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>21</v>
@@ -16889,16 +17026,25 @@
       <c r="AF181" s="2"/>
     </row>
     <row r="182" spans="1:32">
-      <c r="A182" s="15"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="3"/>
-      <c r="D182" s="2"/>
+      <c r="A182" s="15">
+        <f t="shared" si="6"/>
+        <v>177</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="E182" s="24"/>
       <c r="F182" s="17"/>
       <c r="G182" s="17"/>
       <c r="H182" s="17"/>
       <c r="I182" s="16"/>
-      <c r="J182" s="2"/>
+      <c r="J182" s="26"/>
       <c r="K182" s="24"/>
       <c r="L182" s="21"/>
       <c r="M182" s="24"/>
@@ -16923,16 +17069,25 @@
       <c r="AF182" s="2"/>
     </row>
     <row r="183" spans="1:32">
-      <c r="A183" s="15"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="3"/>
-      <c r="D183" s="2"/>
+      <c r="A183" s="15">
+        <f t="shared" si="6"/>
+        <v>178</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="E183" s="24"/>
-      <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-      <c r="H183" s="2"/>
+      <c r="F183" s="17"/>
+      <c r="G183" s="17"/>
+      <c r="H183" s="17"/>
       <c r="I183" s="16"/>
-      <c r="J183" s="2"/>
+      <c r="J183" s="26"/>
       <c r="K183" s="24"/>
       <c r="L183" s="21"/>
       <c r="M183" s="24"/>
@@ -16962,9 +17117,9 @@
       <c r="C184" s="3"/>
       <c r="D184" s="2"/>
       <c r="E184" s="24"/>
-      <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
+      <c r="F184" s="17"/>
+      <c r="G184" s="17"/>
+      <c r="H184" s="17"/>
       <c r="I184" s="16"/>
       <c r="J184" s="2"/>
       <c r="K184" s="24"/>
@@ -17000,9 +17155,9 @@
       <c r="C185" s="3"/>
       <c r="D185" s="2"/>
       <c r="E185" s="24"/>
-      <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="2"/>
+      <c r="F185" s="17"/>
+      <c r="G185" s="17"/>
+      <c r="H185" s="17"/>
       <c r="I185" s="16"/>
       <c r="J185" s="2"/>
       <c r="K185" s="24"/>
@@ -17034,9 +17189,9 @@
       <c r="C186" s="3"/>
       <c r="D186" s="2"/>
       <c r="E186" s="24"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="2"/>
+      <c r="F186" s="17"/>
+      <c r="G186" s="17"/>
+      <c r="H186" s="17"/>
       <c r="I186" s="16"/>
       <c r="J186" s="2"/>
       <c r="K186" s="24"/>
@@ -17068,9 +17223,9 @@
       <c r="C187" s="3"/>
       <c r="D187" s="2"/>
       <c r="E187" s="24"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="2"/>
+      <c r="F187" s="17"/>
+      <c r="G187" s="17"/>
+      <c r="H187" s="17"/>
       <c r="I187" s="16"/>
       <c r="J187" s="2"/>
       <c r="K187" s="24"/>
@@ -17102,9 +17257,9 @@
       <c r="C188" s="3"/>
       <c r="D188" s="2"/>
       <c r="E188" s="24"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-      <c r="H188" s="2"/>
+      <c r="F188" s="17"/>
+      <c r="G188" s="17"/>
+      <c r="H188" s="17"/>
       <c r="I188" s="16"/>
       <c r="J188" s="2"/>
       <c r="K188" s="24"/>
@@ -17136,9 +17291,9 @@
       <c r="C189" s="3"/>
       <c r="D189" s="2"/>
       <c r="E189" s="24"/>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-      <c r="H189" s="2"/>
+      <c r="F189" s="17"/>
+      <c r="G189" s="17"/>
+      <c r="H189" s="17"/>
       <c r="I189" s="16"/>
       <c r="J189" s="26"/>
       <c r="K189" s="24"/>
@@ -17170,9 +17325,9 @@
       <c r="C190" s="3"/>
       <c r="D190" s="2"/>
       <c r="E190" s="24"/>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-      <c r="H190" s="2"/>
+      <c r="F190" s="17"/>
+      <c r="G190" s="17"/>
+      <c r="H190" s="17"/>
       <c r="I190" s="16"/>
       <c r="J190" s="26"/>
       <c r="K190" s="24"/>
@@ -17204,9 +17359,9 @@
       <c r="C191" s="3"/>
       <c r="D191" s="2"/>
       <c r="E191" s="24"/>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-      <c r="H191" s="2"/>
+      <c r="F191" s="17"/>
+      <c r="G191" s="17"/>
+      <c r="H191" s="17"/>
       <c r="I191" s="16"/>
       <c r="J191" s="26"/>
       <c r="K191" s="24"/>
@@ -17238,9 +17393,9 @@
       <c r="C192" s="3"/>
       <c r="D192" s="2"/>
       <c r="E192" s="24"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-      <c r="H192" s="2"/>
+      <c r="F192" s="17"/>
+      <c r="G192" s="17"/>
+      <c r="H192" s="17"/>
       <c r="I192" s="16"/>
       <c r="J192" s="2"/>
       <c r="K192" s="24"/>
@@ -17272,9 +17427,9 @@
       <c r="C193" s="3"/>
       <c r="D193" s="2"/>
       <c r="E193" s="24"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-      <c r="H193" s="2"/>
+      <c r="F193" s="17"/>
+      <c r="G193" s="17"/>
+      <c r="H193" s="17"/>
       <c r="I193" s="16"/>
       <c r="J193" s="2"/>
       <c r="K193" s="24"/>
@@ -17306,9 +17461,9 @@
       <c r="C194" s="3"/>
       <c r="D194" s="2"/>
       <c r="E194" s="24"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-      <c r="H194" s="2"/>
+      <c r="F194" s="17"/>
+      <c r="G194" s="17"/>
+      <c r="H194" s="17"/>
       <c r="I194" s="16"/>
       <c r="J194" s="2"/>
       <c r="K194" s="24"/>
@@ -17340,9 +17495,9 @@
       <c r="C195" s="3"/>
       <c r="D195" s="2"/>
       <c r="E195" s="24"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
+      <c r="F195" s="17"/>
+      <c r="G195" s="17"/>
+      <c r="H195" s="17"/>
       <c r="I195" s="16"/>
       <c r="J195" s="2"/>
       <c r="K195" s="24"/>
@@ -17374,9 +17529,9 @@
       <c r="C196" s="3"/>
       <c r="D196" s="2"/>
       <c r="E196" s="24"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
+      <c r="F196" s="17"/>
+      <c r="G196" s="17"/>
+      <c r="H196" s="17"/>
       <c r="I196" s="16"/>
       <c r="J196" s="2"/>
       <c r="K196" s="24"/>
@@ -17408,9 +17563,9 @@
       <c r="C197" s="3"/>
       <c r="D197" s="2"/>
       <c r="E197" s="24"/>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
+      <c r="F197" s="17"/>
+      <c r="G197" s="17"/>
+      <c r="H197" s="17"/>
       <c r="I197" s="16"/>
       <c r="J197" s="2"/>
       <c r="K197" s="24"/>
@@ -17442,9 +17597,9 @@
       <c r="C198" s="3"/>
       <c r="D198" s="2"/>
       <c r="E198" s="24"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-      <c r="H198" s="2"/>
+      <c r="F198" s="17"/>
+      <c r="G198" s="17"/>
+      <c r="H198" s="17"/>
       <c r="I198" s="16"/>
       <c r="J198" s="2"/>
       <c r="K198" s="24"/>
@@ -17758,102 +17913,104 @@
       <c r="AE212" s="40"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE181" xr:uid="{87FBAEA3-CFE3-4821-A533-830373FE4419}"/>
+  <autoFilter ref="A1:AE183" xr:uid="{87FBAEA3-CFE3-4821-A533-830373FE4419}"/>
   <dataConsolidate function="varp"/>
   <conditionalFormatting sqref="J1:J1048576">
     <cfRule type="containsBlanks" priority="1" stopIfTrue="1">
       <formula>LEN(TRIM(J1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J181">
+  <conditionalFormatting sqref="J6:J183">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B22" r:id="rId1" xr:uid="{02A4F589-028F-4FB5-99AC-E90D661BE402}"/>
+    <hyperlink ref="B23" r:id="rId1" xr:uid="{02A4F589-028F-4FB5-99AC-E90D661BE402}"/>
     <hyperlink ref="B7" r:id="rId2" xr:uid="{DA1AA612-FC13-4B8F-91DB-8176F965797C}"/>
     <hyperlink ref="B11" r:id="rId3" xr:uid="{91FAA1A1-E352-4FDE-B643-6A57A69F937B}"/>
-    <hyperlink ref="B19" r:id="rId4" xr:uid="{2BBDF59A-9C71-40A3-80BB-A2879EADA016}"/>
+    <hyperlink ref="B20" r:id="rId4" xr:uid="{2BBDF59A-9C71-40A3-80BB-A2879EADA016}"/>
     <hyperlink ref="B8" r:id="rId5" xr:uid="{4AE9E397-5013-4F4B-9E72-DC4EEAFDDCA9}"/>
     <hyperlink ref="B6" r:id="rId6" xr:uid="{708A6D55-5F0B-4113-9678-05E38D6E6AD0}"/>
-    <hyperlink ref="B21" r:id="rId7" xr:uid="{07D1BA71-B6C8-469E-89BF-859A429F549B}"/>
+    <hyperlink ref="B22" r:id="rId7" xr:uid="{07D1BA71-B6C8-469E-89BF-859A429F549B}"/>
     <hyperlink ref="B16" r:id="rId8" xr:uid="{AFEB9FCD-7E7F-40CD-AC8F-A74D174AEFB7}"/>
     <hyperlink ref="B9" r:id="rId9" xr:uid="{D6690880-A2F1-4D6A-A3AE-CD9AEE2C6469}"/>
     <hyperlink ref="B15" r:id="rId10" xr:uid="{D0AC59F5-1338-40A1-B1F0-BACE833D397F}"/>
     <hyperlink ref="B10" r:id="rId11" xr:uid="{BCE06377-B4D2-4BEB-ACF5-3D9E592BB39F}"/>
-    <hyperlink ref="B26" r:id="rId12" xr:uid="{E0507867-6D69-402B-B198-3C0969661ECB}"/>
-    <hyperlink ref="B18" r:id="rId13" xr:uid="{A8B7CF06-D912-447E-8B65-51DA1BB2A12F}"/>
-    <hyperlink ref="B17" r:id="rId14" xr:uid="{65DC1C50-10A9-4D75-A4EE-346DCA4BD9D0}"/>
-    <hyperlink ref="B36" r:id="rId15" xr:uid="{30E4AC6D-BFF7-4ED3-BEF6-68D15E596103}"/>
+    <hyperlink ref="B28" r:id="rId12" xr:uid="{E0507867-6D69-402B-B198-3C0969661ECB}"/>
+    <hyperlink ref="B19" r:id="rId13" xr:uid="{A8B7CF06-D912-447E-8B65-51DA1BB2A12F}"/>
+    <hyperlink ref="B18" r:id="rId14" xr:uid="{65DC1C50-10A9-4D75-A4EE-346DCA4BD9D0}"/>
+    <hyperlink ref="B38" r:id="rId15" xr:uid="{30E4AC6D-BFF7-4ED3-BEF6-68D15E596103}"/>
     <hyperlink ref="B12" r:id="rId16" xr:uid="{13799701-6CC0-4C2D-8B02-BE133CF59D1D}"/>
     <hyperlink ref="B14" r:id="rId17" xr:uid="{C18D7EBB-E67A-46B1-9D43-883D23AF16BA}"/>
-    <hyperlink ref="B37" r:id="rId18" xr:uid="{F78AF2CB-A23C-4A06-B6FD-9AF083489B77}"/>
+    <hyperlink ref="B39" r:id="rId18" xr:uid="{F78AF2CB-A23C-4A06-B6FD-9AF083489B77}"/>
     <hyperlink ref="B13" r:id="rId19" xr:uid="{E53E4761-94E2-48A9-8FE1-83DB075778F5}"/>
-    <hyperlink ref="B40" r:id="rId20" xr:uid="{D076FDB6-042E-45AE-80AB-84C2AF7BFD24}"/>
-    <hyperlink ref="B44" r:id="rId21" xr:uid="{BEA60493-DB25-49CC-9617-7BC147DE6046}"/>
-    <hyperlink ref="B29" r:id="rId22" xr:uid="{A5F3C5DD-C50A-461E-A802-901C30FC4AED}"/>
-    <hyperlink ref="B31" r:id="rId23" xr:uid="{6C4E7FEA-B06B-4D33-A6EC-DAA26CF99103}"/>
-    <hyperlink ref="B69" r:id="rId24" xr:uid="{E1E5057A-FB94-4EE8-8C2D-49C785E4A80C}"/>
-    <hyperlink ref="B123" r:id="rId25" xr:uid="{E92A3788-94AD-417E-8776-3F0F8AC77A42}"/>
-    <hyperlink ref="B116" r:id="rId26" xr:uid="{A7CE59DA-3463-404A-A8C2-238D8E927C0C}"/>
-    <hyperlink ref="B27" r:id="rId27" xr:uid="{2DD5D1C5-CFA9-4E46-8DE3-9BB27A9D2F4F}"/>
-    <hyperlink ref="B20" r:id="rId28" xr:uid="{36C6C067-6005-47A5-BA2E-0017E9C49A7E}"/>
-    <hyperlink ref="B46" r:id="rId29" xr:uid="{F19D427D-4B33-4DA0-BCE1-89FD4C6A45EC}"/>
-    <hyperlink ref="B35" r:id="rId30" xr:uid="{5C245786-AA85-4953-851D-06DA1FA10587}"/>
-    <hyperlink ref="B34" r:id="rId31" xr:uid="{AD18BB1C-58BD-4F47-892B-ADA4BA01E802}"/>
-    <hyperlink ref="B23" r:id="rId32" xr:uid="{EB7B0C3D-3EDD-4CAB-B153-20C5E95CE006}"/>
-    <hyperlink ref="B32" r:id="rId33" xr:uid="{CD0D820D-0833-4D39-A05F-97E7FFD504B7}"/>
-    <hyperlink ref="B51" r:id="rId34" xr:uid="{E9F9E6EF-3847-43CC-8B5C-2BC41A0CC07E}"/>
-    <hyperlink ref="B38" r:id="rId35" xr:uid="{D8956061-AB17-4B6B-803A-64172A05FE3A}"/>
-    <hyperlink ref="B55" r:id="rId36" xr:uid="{24CAB4D1-71F3-4368-A959-9C0632EC3D9A}"/>
-    <hyperlink ref="B48" r:id="rId37" xr:uid="{029D5307-8102-4CB6-B35D-B4F46F774686}"/>
-    <hyperlink ref="B39" r:id="rId38" xr:uid="{8A883763-542F-442E-A4F4-1A077BBCCEDE}"/>
-    <hyperlink ref="B52" r:id="rId39" xr:uid="{E3DA2CA9-AF5D-4261-9FE3-E067CCF082BD}"/>
-    <hyperlink ref="B42" r:id="rId40" xr:uid="{33E2B044-5D50-4F04-961F-525520CFC949}"/>
-    <hyperlink ref="B54" r:id="rId41" xr:uid="{8E09D427-792A-4FC3-B3DF-CB26E0CA0BC3}"/>
-    <hyperlink ref="B58" r:id="rId42" xr:uid="{B092C32F-2D89-459B-A708-B04AD2F01D4C}"/>
-    <hyperlink ref="B59" r:id="rId43" xr:uid="{01A62E6A-E7FD-4CB9-82F5-EB6FC8005F2E}"/>
-    <hyperlink ref="B41" r:id="rId44" xr:uid="{2FE4F564-45B9-4F43-A3C0-CBB7F12E0E2B}"/>
-    <hyperlink ref="B70" r:id="rId45" xr:uid="{A6631746-D2F5-429D-B430-F960719F4B1B}"/>
-    <hyperlink ref="B57" r:id="rId46" xr:uid="{12FCC991-7F5A-4354-9FC3-18FDDDD8CE6C}"/>
-    <hyperlink ref="B43" r:id="rId47" xr:uid="{3678BBCA-4E85-489B-84A4-A96D66BD4DB7}"/>
-    <hyperlink ref="B65" r:id="rId48" xr:uid="{16947ACE-701E-44C1-AF75-3EA38C4C5B8C}"/>
-    <hyperlink ref="B67" r:id="rId49" xr:uid="{D3C0B1DE-A1B6-46E3-96D4-776763C4C12C}"/>
-    <hyperlink ref="B97" r:id="rId50" xr:uid="{5116DC3D-2E22-4FD5-87CC-672F34607BD0}"/>
-    <hyperlink ref="B63" r:id="rId51" xr:uid="{08D98261-5571-4864-9733-0D7138EAA897}"/>
-    <hyperlink ref="B64" r:id="rId52" xr:uid="{D7E79091-C7A2-45DE-916D-56A0FD914013}"/>
-    <hyperlink ref="B68" r:id="rId53" xr:uid="{EF2F445E-1926-4AB0-A70B-B691FAE11F60}"/>
-    <hyperlink ref="B45" r:id="rId54" xr:uid="{6D063377-AAF9-420D-9153-AAB05E2306AF}"/>
-    <hyperlink ref="B47" r:id="rId55" xr:uid="{8E113288-22BB-4688-9859-D8FC8E4CA92E}"/>
-    <hyperlink ref="B66" r:id="rId56" xr:uid="{B4CF0632-88BC-4F9A-9B0A-5DED84CE4631}"/>
-    <hyperlink ref="B50" r:id="rId57" xr:uid="{F8EA7F1A-44B5-4295-A6F1-AD2B31F3F1B4}"/>
-    <hyperlink ref="B28" r:id="rId58" xr:uid="{14D7DA13-D196-4716-BFA5-90CAA4803DBF}"/>
-    <hyperlink ref="B33" r:id="rId59" xr:uid="{E164BA59-FE82-4D86-AC56-85FCE19DCEF3}"/>
-    <hyperlink ref="B71" r:id="rId60" xr:uid="{12C906AB-4ECE-448C-A0C8-D125C0FDC483}"/>
-    <hyperlink ref="B49" r:id="rId61" xr:uid="{5CFFEEDA-443B-4241-9004-46F04203EB5D}"/>
-    <hyperlink ref="B101" r:id="rId62" xr:uid="{4862BAA8-03CD-461A-86AA-BFE03BD16FE8}"/>
-    <hyperlink ref="B30" r:id="rId63" xr:uid="{D9574424-1E4D-4274-B909-7AF308B1F5D0}"/>
-    <hyperlink ref="B95" r:id="rId64" xr:uid="{3CB2341C-EF0A-41F5-A91F-BAD5318AEFE8}"/>
-    <hyperlink ref="B24" r:id="rId65" xr:uid="{B9FBA509-EC12-4F94-ADD9-B5D8B5212EBC}"/>
-    <hyperlink ref="B91" r:id="rId66" xr:uid="{821D9FDF-A581-40A7-B11E-05093F625ED5}"/>
-    <hyperlink ref="B53" r:id="rId67" xr:uid="{811F7861-4819-4F4D-8210-313978606080}"/>
-    <hyperlink ref="B56" r:id="rId68" xr:uid="{F91FADA3-ABFA-40CE-92D9-B80EB489FD9E}"/>
-    <hyperlink ref="B62" r:id="rId69" xr:uid="{C4A97CFD-0C0F-40B8-A24A-A8248374855D}"/>
-    <hyperlink ref="B61" r:id="rId70" xr:uid="{B3CD1BD6-9FE2-4DA0-A1EE-6BD10B95B9DE}"/>
-    <hyperlink ref="B83" r:id="rId71" xr:uid="{3AC13755-9832-40EC-9F0A-53A8EFCB9DB1}"/>
-    <hyperlink ref="B96" r:id="rId72" xr:uid="{ECB85E2C-A720-4B5A-9287-9CA9D3D2C9C4}"/>
-    <hyperlink ref="B89" r:id="rId73" xr:uid="{CAAC2080-5FBE-44CA-808F-4B541C1D2CCF}"/>
-    <hyperlink ref="B90" r:id="rId74" xr:uid="{1395A0AA-7229-4956-8971-93FF745372A8}"/>
-    <hyperlink ref="B100" r:id="rId75" xr:uid="{6F78A718-A38C-4547-82E0-BC3AA6087414}"/>
-    <hyperlink ref="B60" r:id="rId76" xr:uid="{A69FE8E2-231D-48F0-A835-078603A9B766}"/>
-    <hyperlink ref="B25" r:id="rId77" xr:uid="{568F05A9-6D0C-4F83-9B4F-EADBE5B3D36E}"/>
-    <hyperlink ref="B155" r:id="rId78" xr:uid="{9178234D-93D7-4722-B414-1ED85B69D113}"/>
-    <hyperlink ref="B154" r:id="rId79" xr:uid="{5AF15AA0-C03A-41B5-87FB-E2EC2E8EDE78}"/>
-    <hyperlink ref="B125" r:id="rId80" xr:uid="{3E3906F5-51B3-405C-ACE3-A12F1DE77816}"/>
+    <hyperlink ref="B42" r:id="rId20" xr:uid="{D076FDB6-042E-45AE-80AB-84C2AF7BFD24}"/>
+    <hyperlink ref="B46" r:id="rId21" xr:uid="{BEA60493-DB25-49CC-9617-7BC147DE6046}"/>
+    <hyperlink ref="B31" r:id="rId22" xr:uid="{A5F3C5DD-C50A-461E-A802-901C30FC4AED}"/>
+    <hyperlink ref="B33" r:id="rId23" xr:uid="{6C4E7FEA-B06B-4D33-A6EC-DAA26CF99103}"/>
+    <hyperlink ref="B71" r:id="rId24" xr:uid="{E1E5057A-FB94-4EE8-8C2D-49C785E4A80C}"/>
+    <hyperlink ref="B126" r:id="rId25" xr:uid="{E92A3788-94AD-417E-8776-3F0F8AC77A42}"/>
+    <hyperlink ref="B119" r:id="rId26" xr:uid="{A7CE59DA-3463-404A-A8C2-238D8E927C0C}"/>
+    <hyperlink ref="B29" r:id="rId27" xr:uid="{2DD5D1C5-CFA9-4E46-8DE3-9BB27A9D2F4F}"/>
+    <hyperlink ref="B21" r:id="rId28" xr:uid="{36C6C067-6005-47A5-BA2E-0017E9C49A7E}"/>
+    <hyperlink ref="B48" r:id="rId29" xr:uid="{F19D427D-4B33-4DA0-BCE1-89FD4C6A45EC}"/>
+    <hyperlink ref="B37" r:id="rId30" xr:uid="{5C245786-AA85-4953-851D-06DA1FA10587}"/>
+    <hyperlink ref="B36" r:id="rId31" xr:uid="{AD18BB1C-58BD-4F47-892B-ADA4BA01E802}"/>
+    <hyperlink ref="B24" r:id="rId32" xr:uid="{EB7B0C3D-3EDD-4CAB-B153-20C5E95CE006}"/>
+    <hyperlink ref="B34" r:id="rId33" xr:uid="{CD0D820D-0833-4D39-A05F-97E7FFD504B7}"/>
+    <hyperlink ref="B53" r:id="rId34" xr:uid="{E9F9E6EF-3847-43CC-8B5C-2BC41A0CC07E}"/>
+    <hyperlink ref="B40" r:id="rId35" xr:uid="{D8956061-AB17-4B6B-803A-64172A05FE3A}"/>
+    <hyperlink ref="B57" r:id="rId36" xr:uid="{24CAB4D1-71F3-4368-A959-9C0632EC3D9A}"/>
+    <hyperlink ref="B50" r:id="rId37" xr:uid="{029D5307-8102-4CB6-B35D-B4F46F774686}"/>
+    <hyperlink ref="B41" r:id="rId38" xr:uid="{8A883763-542F-442E-A4F4-1A077BBCCEDE}"/>
+    <hyperlink ref="B54" r:id="rId39" xr:uid="{E3DA2CA9-AF5D-4261-9FE3-E067CCF082BD}"/>
+    <hyperlink ref="B44" r:id="rId40" xr:uid="{33E2B044-5D50-4F04-961F-525520CFC949}"/>
+    <hyperlink ref="B56" r:id="rId41" xr:uid="{8E09D427-792A-4FC3-B3DF-CB26E0CA0BC3}"/>
+    <hyperlink ref="B60" r:id="rId42" xr:uid="{B092C32F-2D89-459B-A708-B04AD2F01D4C}"/>
+    <hyperlink ref="B61" r:id="rId43" xr:uid="{01A62E6A-E7FD-4CB9-82F5-EB6FC8005F2E}"/>
+    <hyperlink ref="B43" r:id="rId44" xr:uid="{2FE4F564-45B9-4F43-A3C0-CBB7F12E0E2B}"/>
+    <hyperlink ref="B72" r:id="rId45" xr:uid="{A6631746-D2F5-429D-B430-F960719F4B1B}"/>
+    <hyperlink ref="B59" r:id="rId46" xr:uid="{12FCC991-7F5A-4354-9FC3-18FDDDD8CE6C}"/>
+    <hyperlink ref="B45" r:id="rId47" xr:uid="{3678BBCA-4E85-489B-84A4-A96D66BD4DB7}"/>
+    <hyperlink ref="B67" r:id="rId48" xr:uid="{16947ACE-701E-44C1-AF75-3EA38C4C5B8C}"/>
+    <hyperlink ref="B69" r:id="rId49" xr:uid="{D3C0B1DE-A1B6-46E3-96D4-776763C4C12C}"/>
+    <hyperlink ref="B100" r:id="rId50" xr:uid="{5116DC3D-2E22-4FD5-87CC-672F34607BD0}"/>
+    <hyperlink ref="B65" r:id="rId51" xr:uid="{08D98261-5571-4864-9733-0D7138EAA897}"/>
+    <hyperlink ref="B66" r:id="rId52" xr:uid="{D7E79091-C7A2-45DE-916D-56A0FD914013}"/>
+    <hyperlink ref="B70" r:id="rId53" xr:uid="{EF2F445E-1926-4AB0-A70B-B691FAE11F60}"/>
+    <hyperlink ref="B47" r:id="rId54" xr:uid="{6D063377-AAF9-420D-9153-AAB05E2306AF}"/>
+    <hyperlink ref="B49" r:id="rId55" xr:uid="{8E113288-22BB-4688-9859-D8FC8E4CA92E}"/>
+    <hyperlink ref="B68" r:id="rId56" xr:uid="{B4CF0632-88BC-4F9A-9B0A-5DED84CE4631}"/>
+    <hyperlink ref="B52" r:id="rId57" xr:uid="{F8EA7F1A-44B5-4295-A6F1-AD2B31F3F1B4}"/>
+    <hyperlink ref="B30" r:id="rId58" xr:uid="{14D7DA13-D196-4716-BFA5-90CAA4803DBF}"/>
+    <hyperlink ref="B35" r:id="rId59" xr:uid="{E164BA59-FE82-4D86-AC56-85FCE19DCEF3}"/>
+    <hyperlink ref="B73" r:id="rId60" xr:uid="{12C906AB-4ECE-448C-A0C8-D125C0FDC483}"/>
+    <hyperlink ref="B51" r:id="rId61" xr:uid="{5CFFEEDA-443B-4241-9004-46F04203EB5D}"/>
+    <hyperlink ref="B104" r:id="rId62" xr:uid="{4862BAA8-03CD-461A-86AA-BFE03BD16FE8}"/>
+    <hyperlink ref="B32" r:id="rId63" xr:uid="{D9574424-1E4D-4274-B909-7AF308B1F5D0}"/>
+    <hyperlink ref="B98" r:id="rId64" xr:uid="{3CB2341C-EF0A-41F5-A91F-BAD5318AEFE8}"/>
+    <hyperlink ref="B26" r:id="rId65" xr:uid="{B9FBA509-EC12-4F94-ADD9-B5D8B5212EBC}"/>
+    <hyperlink ref="B93" r:id="rId66" xr:uid="{821D9FDF-A581-40A7-B11E-05093F625ED5}"/>
+    <hyperlink ref="B55" r:id="rId67" xr:uid="{811F7861-4819-4F4D-8210-313978606080}"/>
+    <hyperlink ref="B58" r:id="rId68" xr:uid="{F91FADA3-ABFA-40CE-92D9-B80EB489FD9E}"/>
+    <hyperlink ref="B64" r:id="rId69" xr:uid="{C4A97CFD-0C0F-40B8-A24A-A8248374855D}"/>
+    <hyperlink ref="B63" r:id="rId70" xr:uid="{B3CD1BD6-9FE2-4DA0-A1EE-6BD10B95B9DE}"/>
+    <hyperlink ref="B85" r:id="rId71" xr:uid="{3AC13755-9832-40EC-9F0A-53A8EFCB9DB1}"/>
+    <hyperlink ref="B99" r:id="rId72" xr:uid="{ECB85E2C-A720-4B5A-9287-9CA9D3D2C9C4}"/>
+    <hyperlink ref="B91" r:id="rId73" xr:uid="{CAAC2080-5FBE-44CA-808F-4B541C1D2CCF}"/>
+    <hyperlink ref="B92" r:id="rId74" xr:uid="{1395A0AA-7229-4956-8971-93FF745372A8}"/>
+    <hyperlink ref="B103" r:id="rId75" xr:uid="{6F78A718-A38C-4547-82E0-BC3AA6087414}"/>
+    <hyperlink ref="B62" r:id="rId76" xr:uid="{A69FE8E2-231D-48F0-A835-078603A9B766}"/>
+    <hyperlink ref="B27" r:id="rId77" xr:uid="{568F05A9-6D0C-4F83-9B4F-EADBE5B3D36E}"/>
+    <hyperlink ref="B95" r:id="rId78" xr:uid="{9178234D-93D7-4722-B414-1ED85B69D113}"/>
+    <hyperlink ref="B157" r:id="rId79" xr:uid="{5AF15AA0-C03A-41B5-87FB-E2EC2E8EDE78}"/>
+    <hyperlink ref="B128" r:id="rId80" xr:uid="{3E3906F5-51B3-405C-ACE3-A12F1DE77816}"/>
+    <hyperlink ref="B17" r:id="rId81" xr:uid="{73D6E50C-5D52-419E-82FE-D7DAAEB42DF0}"/>
+    <hyperlink ref="B25" r:id="rId82" xr:uid="{6ECF4226-5DF1-4CDC-B19B-57E970B24289}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
+  <pageSetup orientation="portrait" r:id="rId83"/>
 </worksheet>
 </file>
 
@@ -17880,19 +18037,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D2" s="74" t="s">
+        <v>716</v>
+      </c>
+      <c r="E2" s="74" t="s">
         <v>717</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>718</v>
       </c>
       <c r="F2" s="75" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="75" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2" s="75" t="s">
         <v>126</v>
@@ -17900,13 +18057,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="B3" s="95" t="s">
+        <v>718</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>719</v>
       </c>
-      <c r="C3" s="44" t="s">
-        <v>720</v>
-      </c>
       <c r="D3" s="95" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E3" s="96">
         <v>45757</v>
@@ -17926,19 +18083,19 @@
         <v>692</v>
       </c>
       <c r="D4" s="95" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E4" s="96">
         <v>45782</v>
       </c>
       <c r="F4" s="98" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G4" s="99">
         <v>9420</v>
       </c>
       <c r="H4" s="95" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -17949,7 +18106,7 @@
         <v>128</v>
       </c>
       <c r="D5" s="95" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E5" s="96">
         <v>45637</v>
@@ -17963,13 +18120,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="95" t="s">
+        <v>729</v>
+      </c>
+      <c r="C6" s="95" t="s">
+        <v>729</v>
+      </c>
+      <c r="D6" s="95" t="s">
         <v>730</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>730</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>731</v>
       </c>
       <c r="E6" s="96">
         <v>45669</v>
@@ -17981,7 +18138,7 @@
         <v>2200</v>
       </c>
       <c r="H6" s="95" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -18001,10 +18158,10 @@
         <v>16.75</v>
       </c>
       <c r="G7" s="95" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H7" s="95" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -18015,7 +18172,7 @@
         <v>476</v>
       </c>
       <c r="D8" s="95" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E8" s="96">
         <v>45322</v>
@@ -18024,15 +18181,15 @@
         <v>500</v>
       </c>
       <c r="H8" s="95" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="95" t="s">
+        <v>806</v>
+      </c>
+      <c r="C9" s="95" t="s">
         <v>807</v>
-      </c>
-      <c r="C9" s="95" t="s">
-        <v>808</v>
       </c>
       <c r="D9" s="95" t="s">
         <v>689</v>
@@ -18046,13 +18203,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="95" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C10" s="95" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D10" s="95" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E10" s="96">
         <v>46112</v>
@@ -18066,13 +18223,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="95" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C11" s="95" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="95" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E11" s="96">
         <v>46156</v>
@@ -18086,13 +18243,13 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="95" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C12" s="95" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D12" s="95" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E12" s="96">
         <v>46160</v>
@@ -18154,13 +18311,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>720</v>
+      </c>
+      <c r="D2" s="45" t="s">
         <v>721</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="E2" s="45" t="s">
         <v>722</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>723</v>
       </c>
       <c r="F2" s="45" t="s">
         <v>126</v>
@@ -18179,16 +18336,16 @@
     <row r="3" spans="1:16">
       <c r="A3" s="45"/>
       <c r="B3" s="45" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
@@ -18205,16 +18362,16 @@
     <row r="4" spans="1:16">
       <c r="A4" s="45"/>
       <c r="B4" s="45" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D4" s="45" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F4" s="45"/>
       <c r="G4" s="45"/>
@@ -18231,19 +18388,19 @@
     <row r="5" spans="1:16">
       <c r="A5" s="45"/>
       <c r="B5" s="45" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D5" s="45" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F5" s="45" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G5" s="45"/>
       <c r="H5" s="45"/>
@@ -18259,16 +18416,16 @@
     <row r="6" spans="1:16">
       <c r="A6" s="45"/>
       <c r="B6" s="45" t="s">
+        <v>739</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>740</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>741</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
@@ -18285,19 +18442,19 @@
     <row r="7" spans="1:16">
       <c r="A7" s="45"/>
       <c r="B7" s="45" t="s">
+        <v>743</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>744</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>745</v>
       </c>
       <c r="D7" s="45" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G7" s="45"/>
       <c r="H7" s="45"/>
@@ -18316,16 +18473,16 @@
         <v>135</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>135</v>
       </c>
       <c r="E8" s="45" t="s">
+        <v>747</v>
+      </c>
+      <c r="F8" s="45" t="s">
         <v>748</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>749</v>
       </c>
       <c r="G8" s="45"/>
       <c r="H8" s="45"/>
@@ -18341,19 +18498,19 @@
     <row r="9" spans="1:16">
       <c r="A9" s="45"/>
       <c r="B9" s="45" t="s">
+        <v>749</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>750</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>751</v>
       </c>
       <c r="D9" s="45" t="s">
         <v>682</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F9" s="45" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
@@ -18369,19 +18526,19 @@
     <row r="10" spans="1:16">
       <c r="A10" s="45"/>
       <c r="B10" s="45" t="s">
+        <v>752</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>753</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="45" t="s">
         <v>754</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="E10" s="45" t="s">
+        <v>748</v>
+      </c>
+      <c r="F10" s="45" t="s">
         <v>755</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>749</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>756</v>
       </c>
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
@@ -18397,19 +18554,19 @@
     <row r="11" spans="1:16">
       <c r="A11" s="45"/>
       <c r="B11" s="45" t="s">
+        <v>757</v>
+      </c>
+      <c r="C11" s="45" t="s">
         <v>758</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>759</v>
       </c>
       <c r="D11" s="45" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G11" s="45"/>
       <c r="H11" s="45"/>
@@ -18425,19 +18582,19 @@
     <row r="12" spans="1:16">
       <c r="A12" s="45"/>
       <c r="B12" s="45" t="s">
+        <v>760</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>761</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>762</v>
       </c>
       <c r="D12" s="45" t="s">
         <v>123</v>
       </c>
       <c r="E12" s="45" t="s">
+        <v>763</v>
+      </c>
+      <c r="F12" s="45" t="s">
         <v>764</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>765</v>
       </c>
       <c r="G12" s="45"/>
       <c r="H12" s="45"/>
@@ -18453,16 +18610,16 @@
     <row r="13" spans="1:16">
       <c r="A13" s="45"/>
       <c r="B13" s="45" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D13" s="45" t="s">
         <v>135</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="45"/>
@@ -18479,16 +18636,16 @@
     <row r="14" spans="1:16">
       <c r="A14" s="45"/>
       <c r="B14" s="45" t="s">
+        <v>767</v>
+      </c>
+      <c r="C14" s="45" t="s">
         <v>768</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>769</v>
       </c>
       <c r="D14" s="45" t="s">
         <v>677</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45"/>
@@ -18505,16 +18662,16 @@
     <row r="15" spans="1:16">
       <c r="A15" s="45"/>
       <c r="B15" s="45" t="s">
+        <v>769</v>
+      </c>
+      <c r="C15" s="45" t="s">
         <v>770</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="D15" s="45" t="s">
         <v>771</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="E15" s="45" t="s">
         <v>772</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>773</v>
       </c>
       <c r="F15" s="45"/>
       <c r="G15" s="45"/>
@@ -18531,19 +18688,19 @@
     <row r="16" spans="1:16">
       <c r="A16" s="45"/>
       <c r="B16" s="45" t="s">
+        <v>774</v>
+      </c>
+      <c r="C16" s="45" t="s">
         <v>775</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="D16" s="45" t="s">
         <v>776</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="E16" s="45" t="s">
         <v>777</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="F16" s="45" t="s">
         <v>778</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>779</v>
       </c>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -18559,16 +18716,16 @@
     <row r="17" spans="1:16">
       <c r="A17" s="45"/>
       <c r="B17" s="45" t="s">
+        <v>779</v>
+      </c>
+      <c r="C17" s="45" t="s">
         <v>780</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="D17" s="45" t="s">
         <v>781</v>
       </c>
-      <c r="D17" s="45" t="s">
-        <v>782</v>
-      </c>
       <c r="E17" s="45" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45"/>
@@ -18620,7 +18777,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="B20" s="74" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="45"/>
@@ -18640,16 +18797,16 @@
     <row r="21" spans="1:16">
       <c r="A21" s="45"/>
       <c r="B21" s="89" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D21" s="77" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E21" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
@@ -18666,13 +18823,13 @@
     <row r="22" spans="1:16">
       <c r="A22" s="45"/>
       <c r="B22" s="45" t="s">
+        <v>783</v>
+      </c>
+      <c r="C22" s="45" t="s">
         <v>784</v>
       </c>
-      <c r="C22" s="45" t="s">
-        <v>785</v>
-      </c>
       <c r="D22" s="77" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
@@ -18690,16 +18847,16 @@
     <row r="23" spans="1:16">
       <c r="A23" s="45"/>
       <c r="B23" s="45" t="s">
+        <v>785</v>
+      </c>
+      <c r="C23" s="45" t="s">
         <v>786</v>
       </c>
-      <c r="C23" s="45" t="s">
-        <v>787</v>
-      </c>
       <c r="D23" s="77" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E23" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
@@ -18716,16 +18873,16 @@
     <row r="24" spans="1:16">
       <c r="A24" s="45"/>
       <c r="B24" s="45" t="s">
+        <v>787</v>
+      </c>
+      <c r="C24" s="45" t="s">
         <v>788</v>
       </c>
-      <c r="C24" s="45" t="s">
-        <v>789</v>
-      </c>
       <c r="D24" s="77" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E24" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F24" s="45"/>
       <c r="G24" s="45"/>
@@ -18745,13 +18902,13 @@
         <v>98</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D25" s="77" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
@@ -18768,16 +18925,16 @@
     <row r="26" spans="1:16">
       <c r="A26" s="45"/>
       <c r="B26" s="45" t="s">
+        <v>790</v>
+      </c>
+      <c r="C26" s="45" t="s">
         <v>791</v>
       </c>
-      <c r="C26" s="45" t="s">
-        <v>792</v>
-      </c>
       <c r="D26" s="77" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E26" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F26" s="45"/>
       <c r="G26" s="45"/>
@@ -18794,16 +18951,16 @@
     <row r="27" spans="1:16">
       <c r="A27" s="45"/>
       <c r="B27" s="45" t="s">
+        <v>792</v>
+      </c>
+      <c r="C27" s="45" t="s">
         <v>793</v>
       </c>
-      <c r="C27" s="45" t="s">
-        <v>794</v>
-      </c>
       <c r="D27" s="77" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E27" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
@@ -18820,16 +18977,16 @@
     <row r="28" spans="1:16">
       <c r="A28" s="45"/>
       <c r="B28" s="45" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D28" s="77" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E28" s="77" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F28" s="45"/>
       <c r="G28" s="45"/>
@@ -18849,7 +19006,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="89" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D29" s="45"/>
       <c r="E29" s="45"/>
@@ -18906,67 +19063,67 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" s="90" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="44" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>
@@ -19031,7 +19188,7 @@
     <row r="3" spans="1:17">
       <c r="A3" s="45"/>
       <c r="B3" s="72" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C3" s="57"/>
       <c r="D3" s="45"/>
@@ -19051,11 +19208,11 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="45"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>716</v>
+      <c r="C4" s="110" t="s">
+        <v>903</v>
       </c>
       <c r="D4" s="45"/>
       <c r="E4" s="58"/>
@@ -19291,10 +19448,10 @@
     <row r="15" spans="1:17">
       <c r="A15" s="45"/>
       <c r="B15" s="92" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D15" s="45"/>
       <c r="E15" s="58"/>
@@ -19377,14 +19534,14 @@
     <row r="19" spans="1:17">
       <c r="A19" s="45"/>
       <c r="B19" s="89" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D19" s="45"/>
       <c r="E19" s="58" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F19" s="56"/>
       <c r="G19" s="56"/>
@@ -19421,7 +19578,7 @@
     <row r="21" spans="1:17">
       <c r="A21" s="45"/>
       <c r="B21" s="77" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="45"/>
@@ -19442,10 +19599,10 @@
     <row r="22" spans="1:17">
       <c r="A22" s="45"/>
       <c r="B22" s="77" t="s">
+        <v>820</v>
+      </c>
+      <c r="C22" s="77" t="s">
         <v>821</v>
-      </c>
-      <c r="C22" s="77" t="s">
-        <v>822</v>
       </c>
       <c r="D22" s="45"/>
       <c r="E22" s="58"/>
@@ -20471,7 +20628,7 @@
         <v>2029.1061166099998</v>
       </c>
       <c r="I19" s="106" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J19" s="105"/>
       <c r="K19" s="45"/>
@@ -20518,15 +20675,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="45">
-        <f>+[80]Main!$J$2</f>
+        <f>+[81]Main!$J$2</f>
         <v>127.52</v>
       </c>
       <c r="F20" s="56">
-        <f>+[80]Main!$J$4</f>
+        <f>+[81]Main!$J$4</f>
         <v>11289.983199999999</v>
       </c>
       <c r="G20" s="56">
-        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
+        <f>+[81]Main!$J$6-[81]Main!$J$5</f>
         <v>992.61199999999997</v>
       </c>
       <c r="H20" s="56">
@@ -20534,7 +20691,7 @@
         <v>12282.595199999998</v>
       </c>
       <c r="I20" s="108" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J20" s="60">
         <v>46350</v>
@@ -39240,15 +39397,15 @@
         <v>20</v>
       </c>
       <c r="E4" s="58">
-        <f>+[81]Main!$I$2</f>
+        <f>+[82]Main!$I$2</f>
         <v>165.3</v>
       </c>
       <c r="F4" s="56">
-        <f>+[81]Main!$I$4*FX!C3</f>
+        <f>+[82]Main!$I$4*FX!C3</f>
         <v>78910.853010912018</v>
       </c>
       <c r="G4" s="56">
-        <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
+        <f>+([82]Main!$I$6-[82]Main!$I$5)*FX!C3</f>
         <v>9857.1200000000008</v>
       </c>
       <c r="H4" s="56">
@@ -39256,7 +39413,7 @@
         <v>88767.973010912014</v>
       </c>
       <c r="I4" s="104" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="J4" s="60">
         <v>46315</v>
@@ -39306,15 +39463,15 @@
         <v>85</v>
       </c>
       <c r="E5" s="58">
-        <f>+[82]Main!$J$2</f>
+        <f>+[83]Main!$J$2</f>
         <v>157.35</v>
       </c>
       <c r="F5" s="56">
-        <f>+[82]Main!$J$5*FX!C7</f>
+        <f>+[83]Main!$J$5*FX!C7</f>
         <v>109823.20036800001</v>
       </c>
       <c r="G5" s="56">
-        <f>+([82]Main!$J$7-[82]Main!$J$6)*FX!C7</f>
+        <f>+([83]Main!$J$7-[83]Main!$J$6)*FX!C7</f>
         <v>243.04000000000002</v>
       </c>
       <c r="H5" s="56">
@@ -39322,7 +39479,7 @@
         <v>110066.240368</v>
       </c>
       <c r="I5" s="103" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="J5" s="102">
         <v>46339</v>
@@ -39372,15 +39529,15 @@
         <v>21</v>
       </c>
       <c r="E6" s="58">
-        <f>+[83]Main!$K$2</f>
+        <f>+[84]Main!$K$2</f>
         <v>80.58</v>
       </c>
       <c r="F6" s="56">
-        <f>+[83]Main!$K$4</f>
+        <f>+[84]Main!$K$4</f>
         <v>29153.4342507</v>
       </c>
       <c r="G6" s="56">
-        <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
+        <f>+([84]Main!$K$6-[84]Main!$K$5)</f>
         <v>4186</v>
       </c>
       <c r="H6" s="56">
@@ -39388,7 +39545,7 @@
         <v>33339.434250699996</v>
       </c>
       <c r="I6" s="94" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J6" s="60"/>
       <c r="K6" s="58"/>
@@ -39436,15 +39593,15 @@
         <v>85</v>
       </c>
       <c r="E7" s="58">
-        <f>+[84]Main!$I$3</f>
+        <f>+[85]Main!$I$3</f>
         <v>177.95</v>
       </c>
       <c r="F7" s="56">
-        <f>+[84]Main!$I$5*FX!C7</f>
+        <f>+[85]Main!$I$5*FX!C7</f>
         <v>10344.705947284801</v>
       </c>
       <c r="G7" s="56">
-        <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
+        <f>+([85]Main!$I$7-[85]Main!$I$6)*FX!C7</f>
         <v>-1336.16</v>
       </c>
       <c r="H7" s="56">
@@ -42469,7 +42626,7 @@
         <v>458</v>
       </c>
       <c r="K3" s="67" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L3" s="70"/>
       <c r="M3" s="67"/>
@@ -42501,7 +42658,7 @@
       <c r="I4" s="45"/>
       <c r="J4" s="45"/>
       <c r="K4" s="89" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L4" s="45"/>
       <c r="M4" s="45"/>
@@ -42521,7 +42678,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D5" s="89" t="s">
         <v>20</v>
@@ -42533,7 +42690,7 @@
       <c r="I5" s="45"/>
       <c r="J5" s="45"/>
       <c r="K5" s="89" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L5" s="45"/>
       <c r="M5" s="45"/>
@@ -42550,7 +42707,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C6" s="89" t="s">
         <v>139</v>
@@ -42565,7 +42722,7 @@
       <c r="I6" s="45"/>
       <c r="J6" s="45"/>
       <c r="K6" s="89" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
@@ -42597,7 +42754,7 @@
       <c r="I7" s="45"/>
       <c r="J7" s="45"/>
       <c r="K7" s="89" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="L7" s="45"/>
       <c r="M7" s="45"/>
@@ -42629,7 +42786,7 @@
       <c r="I8" s="45"/>
       <c r="J8" s="45"/>
       <c r="K8" s="89" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L8" s="45"/>
       <c r="M8" s="45"/>
@@ -42661,7 +42818,7 @@
       <c r="I9" s="45"/>
       <c r="J9" s="45"/>
       <c r="K9" s="89" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="L9" s="45"/>
       <c r="M9" s="45"/>
@@ -42693,7 +42850,7 @@
       <c r="I10" s="45"/>
       <c r="J10" s="45"/>
       <c r="K10" s="89" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L10" s="45"/>
       <c r="M10" s="45"/>
@@ -42725,7 +42882,7 @@
       <c r="I11" s="45"/>
       <c r="J11" s="45"/>
       <c r="K11" s="89" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="L11" s="45"/>
       <c r="M11" s="45"/>
@@ -42787,7 +42944,7 @@
       <c r="I13" s="45"/>
       <c r="J13" s="45"/>
       <c r="K13" s="89" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="L13" s="45"/>
       <c r="M13" s="45"/>
@@ -42819,7 +42976,7 @@
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
       <c r="K14" s="89" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="L14" s="45"/>
       <c r="M14" s="45"/>
@@ -42836,10 +42993,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="89" t="s">
+        <v>830</v>
+      </c>
+      <c r="C15" s="89" t="s">
         <v>831</v>
-      </c>
-      <c r="C15" s="89" t="s">
-        <v>832</v>
       </c>
       <c r="D15" s="89" t="s">
         <v>143</v>
@@ -42866,7 +43023,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C16" s="89" t="s">
         <v>455</v>
@@ -42881,7 +43038,7 @@
       <c r="I16" s="45"/>
       <c r="J16" s="45"/>
       <c r="K16" s="89" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="L16" s="45"/>
       <c r="M16" s="45"/>
@@ -42898,7 +43055,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="89" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C17" s="89" t="s">
         <v>349</v>
@@ -42928,7 +43085,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="89" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C18" s="89" t="s">
         <v>46</v>
@@ -42973,7 +43130,7 @@
       <c r="I19" s="45"/>
       <c r="J19" s="45"/>
       <c r="K19" s="89" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="L19" s="45"/>
       <c r="M19" s="45"/>
@@ -42990,10 +43147,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="89" t="s">
+        <v>835</v>
+      </c>
+      <c r="C20" s="89" t="s">
         <v>836</v>
-      </c>
-      <c r="C20" s="89" t="s">
-        <v>837</v>
       </c>
       <c r="D20" s="89" t="s">
         <v>21</v>
@@ -43026,7 +43183,7 @@
         <v>351</v>
       </c>
       <c r="D21" s="89" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
@@ -43053,7 +43210,7 @@
         <v>532</v>
       </c>
       <c r="C22" s="89" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D22" s="89" t="s">
         <v>219</v>
@@ -43110,7 +43267,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="89" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C24" s="89" t="s">
         <v>357</v>
@@ -43170,7 +43327,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="89" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C26" s="89" t="s">
         <v>699</v>
@@ -50799,7 +50956,7 @@
     </row>
     <row r="19" spans="2:34">
       <c r="B19" s="77" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C19" s="77"/>
       <c r="D19" s="77"/>
@@ -50942,7 +51099,7 @@
         <v>463</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D8" s="45"/>
       <c r="E8" s="45"/>
@@ -50958,7 +51115,7 @@
         <v>464</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
@@ -51019,10 +51176,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="76" t="s">
+        <v>814</v>
+      </c>
+      <c r="C13" s="76" t="s">
         <v>815</v>
-      </c>
-      <c r="C13" s="76" t="s">
-        <v>816</v>
       </c>
       <c r="D13" s="45"/>
       <c r="E13" s="45"/>
@@ -51035,34 +51192,34 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="101" t="s">
+        <v>874</v>
+      </c>
+      <c r="C14" s="101" t="s">
         <v>875</v>
-      </c>
-      <c r="C14" s="101" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="101" t="s">
+        <v>876</v>
+      </c>
+      <c r="C15" s="101" t="s">
         <v>877</v>
-      </c>
-      <c r="C15" s="101" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="16" spans="2:11">
       <c r="B16" s="101" t="s">
+        <v>878</v>
+      </c>
+      <c r="C16" s="101" t="s">
         <v>879</v>
-      </c>
-      <c r="C16" s="101" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="101" t="s">
+        <v>880</v>
+      </c>
+      <c r="C17" s="101" t="s">
         <v>881</v>
-      </c>
-      <c r="C17" s="101" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="18" spans="2:3">
@@ -51070,60 +51227,60 @@
         <v>116</v>
       </c>
       <c r="C18" s="101" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="101" t="s">
+        <v>883</v>
+      </c>
+      <c r="C19" s="101" t="s">
         <v>884</v>
-      </c>
-      <c r="C19" s="101" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="101" t="s">
+        <v>885</v>
+      </c>
+      <c r="C20" s="101" t="s">
         <v>886</v>
-      </c>
-      <c r="C20" s="101" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="101" t="s">
+        <v>887</v>
+      </c>
+      <c r="C21" s="101" t="s">
         <v>888</v>
-      </c>
-      <c r="C21" s="101" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="101" t="s">
+        <v>889</v>
+      </c>
+      <c r="C22" s="101" t="s">
         <v>890</v>
-      </c>
-      <c r="C22" s="101" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="101" t="s">
+        <v>891</v>
+      </c>
+      <c r="C23" s="101" t="s">
         <v>892</v>
-      </c>
-      <c r="C23" s="101" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" s="101" t="s">
+        <v>893</v>
+      </c>
+      <c r="C24" s="101" t="s">
         <v>894</v>
-      </c>
-      <c r="C24" s="101" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" s="44" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E85F0DD-A13F-4980-9D95-EA0AAD49D306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0481FB07-2EA9-4DEF-8FF4-0775C56FED68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="991">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -1465,9 +1465,6 @@
     <t>TWN</t>
   </si>
   <si>
-    <t xml:space="preserve">SHEIN </t>
-  </si>
-  <si>
     <t>Stores</t>
   </si>
   <si>
@@ -1588,9 +1585,6 @@
     <t>n.a.</t>
   </si>
   <si>
-    <t>Brands: Fred Perry</t>
-  </si>
-  <si>
     <t>FTCH</t>
   </si>
   <si>
@@ -2224,9 +2218,6 @@
     <t>Calzedonia</t>
   </si>
   <si>
-    <t>Dolce &amp; Gabbana</t>
-  </si>
-  <si>
     <t>Lululemon</t>
   </si>
   <si>
@@ -2758,9 +2749,6 @@
     <t>Allbirds</t>
   </si>
   <si>
-    <t>Brands: Ed Hardy, Allbirds etc.</t>
-  </si>
-  <si>
     <t>Marc Jacob</t>
   </si>
   <si>
@@ -2872,10 +2860,280 @@
     <t>Shein</t>
   </si>
   <si>
-    <t xml:space="preserve">IPO on </t>
-  </si>
-  <si>
     <t>0625.HK</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>MF Brands Group</t>
+  </si>
+  <si>
+    <t>Lacoste, Gant, Aigle</t>
+  </si>
+  <si>
+    <t>Brands</t>
+  </si>
+  <si>
+    <t>Chopard</t>
+  </si>
+  <si>
+    <t>SUI</t>
+  </si>
+  <si>
+    <t>Chopard, L.U.C, Happy Diamonds, Alpine Eagle</t>
+  </si>
+  <si>
+    <t>Breitling</t>
+  </si>
+  <si>
+    <t>Richard Mille</t>
+  </si>
+  <si>
+    <t>Swarovski</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>Graff</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>Valentino</t>
+  </si>
+  <si>
+    <t>Valentino, Valentino Garavani</t>
+  </si>
+  <si>
+    <t>Max Mara</t>
+  </si>
+  <si>
+    <t>Max Mara, Weekend Max Mara, Sportmax, Marina Rinaldi, Marella, Pennyblack</t>
+  </si>
+  <si>
+    <t>OTB Group</t>
+  </si>
+  <si>
+    <t>Diesel, Maison Margiela, Marni, Jil Sander, Viktor&amp;Rolf</t>
+  </si>
+  <si>
+    <t>Benetton Group</t>
+  </si>
+  <si>
+    <t>United Colors of Benetton, Sisley</t>
+  </si>
+  <si>
+    <t>Missoni</t>
+  </si>
+  <si>
+    <t>Etro</t>
+  </si>
+  <si>
+    <t>Furla</t>
+  </si>
+  <si>
+    <t>Golden Goose</t>
+  </si>
+  <si>
+    <t>Canali</t>
+  </si>
+  <si>
+    <t>Herno</t>
+  </si>
+  <si>
+    <t>Bally</t>
+  </si>
+  <si>
+    <t>Goyard</t>
+  </si>
+  <si>
+    <t>Longchamp</t>
+  </si>
+  <si>
+    <t>Comme des Garçons</t>
+  </si>
+  <si>
+    <t>Junya Watanabe, Play, Dover Street Market</t>
+  </si>
+  <si>
+    <t>Decathlon</t>
+  </si>
+  <si>
+    <t>Kalenji, Quechua, Domyos, Kipsta, Forclaz</t>
+  </si>
+  <si>
+    <t>Kiabi</t>
+  </si>
+  <si>
+    <t>Hummel</t>
+  </si>
+  <si>
+    <t>Ecco</t>
+  </si>
+  <si>
+    <t>Bestseller</t>
+  </si>
+  <si>
+    <t>Jack &amp; Jones, Vero Moda, Only, Selected, Vila, Pieces, Name It</t>
+  </si>
+  <si>
+    <t>Gymshark</t>
+  </si>
+  <si>
+    <t>Barbour</t>
+  </si>
+  <si>
+    <t>Clarks</t>
+  </si>
+  <si>
+    <t>Clarks Originals</t>
+  </si>
+  <si>
+    <t>Palace</t>
+  </si>
+  <si>
+    <t>Fenix Outdoor</t>
+  </si>
+  <si>
+    <t>Fjällräven, Primus, Tierra, Hanwag</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>Violeta</t>
+  </si>
+  <si>
+    <t>Desigual</t>
+  </si>
+  <si>
+    <t>G-Star Raw</t>
+  </si>
+  <si>
+    <t>NED</t>
+  </si>
+  <si>
+    <t>Deichmann</t>
+  </si>
+  <si>
+    <t>Rack Room Shoes, Ochsner Shoes</t>
+  </si>
+  <si>
+    <t>Otto Group</t>
+  </si>
+  <si>
+    <t>Bonprix, Crate &amp; Barrel</t>
+  </si>
+  <si>
+    <t>s.Oliver</t>
+  </si>
+  <si>
+    <t>comma, Q/S designed by</t>
+  </si>
+  <si>
+    <t>Bogner</t>
+  </si>
+  <si>
+    <t>Fire+Ice</t>
+  </si>
+  <si>
+    <t>Falke</t>
+  </si>
+  <si>
+    <t>Burlington</t>
+  </si>
+  <si>
+    <t>Peek &amp; Cloppenburg</t>
+  </si>
+  <si>
+    <t>Breuninger</t>
+  </si>
+  <si>
+    <t>Takko</t>
+  </si>
+  <si>
+    <t>Kik</t>
+  </si>
+  <si>
+    <t>Triumph International</t>
+  </si>
+  <si>
+    <t>Sloggi, Maison Lejaby</t>
+  </si>
+  <si>
+    <t>Vinted</t>
+  </si>
+  <si>
+    <t>LTU</t>
+  </si>
+  <si>
+    <t>Vestiaire Collective</t>
+  </si>
+  <si>
+    <t>StockX</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Skims</t>
+  </si>
+  <si>
+    <t>Alo Yoga</t>
+  </si>
+  <si>
+    <t>Vuori</t>
+  </si>
+  <si>
+    <t>Carhartt</t>
+  </si>
+  <si>
+    <t>Patagonia</t>
+  </si>
+  <si>
+    <t>Stüssy</t>
+  </si>
+  <si>
+    <t>Fashion Nova</t>
+  </si>
+  <si>
+    <t>J.Crew Group</t>
+  </si>
+  <si>
+    <t>J.Crew, Madewell</t>
+  </si>
+  <si>
+    <t>Musinsa</t>
+  </si>
+  <si>
+    <t>Ed Hardy, Allbirds etc.</t>
+  </si>
+  <si>
+    <t>Fred Perry, Lavenham</t>
+  </si>
+  <si>
+    <t>Rolex</t>
+  </si>
+  <si>
+    <t>Reebok, Champion, Quicksilver</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>Patek</t>
+  </si>
+  <si>
+    <t>NB</t>
+  </si>
+  <si>
+    <t>Shoes</t>
   </si>
 </sst>
 </file>
@@ -2889,7 +3147,7 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3056,13 +3314,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3138,7 +3389,7 @@
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3316,9 +3567,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3352,9 +3600,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3525,6 +3781,46 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>14.68</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>26409.32</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6110</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2603</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
       <sheetName val="Brands"/>
       <sheetName val="Macro"/>
       <sheetName val="Model"/>
@@ -3570,7 +3866,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3610,7 +3906,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3650,7 +3946,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3690,7 +3986,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3705,17 +4001,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>166.25</v>
+            <v>161.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>265601.16625000001</v>
+            <v>257415.14625000002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>18697</v>
+            <v>26507</v>
           </cell>
         </row>
         <row r="6">
@@ -3724,13 +4020,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3772,7 +4068,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3807,54 +4103,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="WACC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>43.26</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>13283.367148799998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1020.558</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1719.8150000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3915,6 +4163,94 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Modle"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>48.5</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>26772.307449745003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>15210</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="WACC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>43.26</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>13283.367148799998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1020.558</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>1719.8150000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
@@ -3946,7 +4282,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3988,7 +4324,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4028,7 +4364,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4068,7 +4404,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4114,7 +4450,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4154,7 +4490,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4188,13 +4524,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4227,86 +4563,6 @@
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>25.27</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>6292.23</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1397.8</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>939</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>14.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>5700.4512649999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>670.06299999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>3013.105</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4369,6 +4625,86 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>25.27</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>6292.23</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1397.8</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>939</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>14.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>5700.4512649999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>670.06299999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>3013.105</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
             <v>34.85</v>
@@ -4396,7 +4732,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4436,7 +4772,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4476,7 +4812,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4516,7 +4852,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4556,7 +4892,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4596,7 +4932,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4630,13 +4966,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4671,94 +5007,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41240</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>459995.53764</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>45360.78</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>52633.11</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="Coc"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>121.86</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>5842.5868395000007</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>170.27600000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1307.6579999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4822,6 +5070,94 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="H2">
+            <v>41240</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>459995.53764</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>45360.78</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>52633.11</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="Coc"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>121.86</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>5842.5868395000007</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>170.27600000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1307.6579999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="I2">
             <v>27.8</v>
           </cell>
@@ -4848,7 +5184,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4888,7 +5224,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4928,7 +5264,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4968,7 +5304,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5006,7 +5342,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5046,7 +5382,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5086,7 +5422,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5121,92 +5457,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="WACC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>148.80000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>6512.5296000000008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>637.99900000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>56.92</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2913.9166024800002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>624.601</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5262,6 +5512,92 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>148.80000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>6512.5296000000008</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>637.99900000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>56.92</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2913.9166024800002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>624.601</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5292,7 +5628,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5330,7 +5666,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5370,7 +5706,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5410,7 +5746,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5450,7 +5786,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5490,7 +5826,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5530,7 +5866,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5561,86 +5897,6 @@
         <row r="6">
           <cell r="J6">
             <v>179</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5.53</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1932.9868362000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>395.98099999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>591.15800000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17.37</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2910.7487942100001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>103.286</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>85</v>
           </cell>
         </row>
       </sheetData>
@@ -5705,6 +5961,86 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5.53</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1932.9868362000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>395.98099999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>591.15800000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17.37</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2910.7487942100001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>103.286</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>85</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5734,7 +6070,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5774,7 +6110,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5814,7 +6150,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5854,7 +6190,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5894,7 +6230,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5934,7 +6270,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5974,7 +6310,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6005,86 +6341,6 @@
         <row r="6">
           <cell r="H6">
             <v>498.12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>38.119999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1935.4971035199997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>325.44000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>24.73</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1761.5194085300002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>256.60000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -6164,6 +6420,126 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
+            <v>38.119999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1935.4971035199997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>325.44000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>24.73</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1761.5194085300002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>256.60000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>19.989999999999998</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1640.5061166099999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>158.5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>547.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
             <v>27.07</v>
           </cell>
         </row>
@@ -6189,7 +6565,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6229,7 +6605,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6269,7 +6645,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6309,7 +6685,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6349,7 +6725,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6389,7 +6765,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6420,126 +6796,6 @@
         <row r="6">
           <cell r="H6">
             <v>291.31400000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17.79</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270.90115659000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>45.523000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>70.016000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2540</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>64964.434459999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>33044</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>13470</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>19.989999999999998</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1640.5061166099999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>158.5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>547.1</v>
           </cell>
         </row>
       </sheetData>
@@ -6598,28 +6854,28 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Modle"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="J2">
-            <v>48.5</v>
+          <cell r="I2">
+            <v>17.79</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270.90115659000003</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>26772.307449745003</v>
+          <cell r="I5">
+            <v>45.523000000000003</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>15210</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>0</v>
+          <cell r="I6">
+            <v>70.016000000000005</v>
           </cell>
         </row>
       </sheetData>
@@ -6630,6 +6886,46 @@
 </file>
 
 <file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2540</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>64964.434459999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>33044</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>13470</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6669,7 +6965,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6711,7 +7007,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6753,7 +7049,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6793,7 +7089,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6824,46 +7120,6 @@
         <row r="7">
           <cell r="I7">
             <v>38</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>22.51</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>40518</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>6030</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1533</v>
           </cell>
         </row>
       </sheetData>
@@ -7295,7 +7551,7 @@
     </row>
     <row r="2" spans="1:34">
       <c r="A2" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -7355,10 +7611,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>442</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>443</v>
       </c>
       <c r="K3" s="10" t="s">
         <v>147</v>
@@ -7367,10 +7623,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>89</v>
@@ -7412,10 +7668,10 @@
         <v>79</v>
       </c>
       <c r="AB3" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC3" s="8" t="s">
         <v>435</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>436</v>
       </c>
       <c r="AD3" s="12" t="s">
         <v>398</v>
@@ -7445,25 +7701,25 @@
         <v>32</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F156)</f>
-        <v>1834524.3301594281</v>
+        <v>1819637.9782594282</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G156)</f>
-        <v>-8675.0033961999943</v>
+        <v>-8426.9533961999987</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H156)</f>
-        <v>1825849.3267632276</v>
+        <v>1811211.0248632277</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="K4" s="17">
         <f>SUM(K6:K156)</f>
@@ -7508,32 +7764,32 @@
         <v>88</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D5" s="82" t="str" cm="1">
         <f t="array" ref="D5">_xlfn.LET(_xlpm.rng,D6:D183,INDEX(_xlpm.rng,MATCH(MAX(COUNTIF(_xlpm.rng,_xlpm.rng)),COUNTIF(_xlpm.rng,_xlpm.rng),0)))</f>
         <v>US</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F183)</f>
-        <v>22653.501309833657</v>
+        <v>22469.719187611434</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G156)</f>
-        <v>-108.43754245249993</v>
+        <v>-105.33691745249999</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H156)</f>
-        <v>22823.116584540345</v>
+        <v>22640.137810790347</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="K5" s="83">
         <f>AVERAGE(K6:K156)</f>
@@ -7641,7 +7897,7 @@
         <v>250961.22150112005</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J6" s="26">
         <v>46308</v>
@@ -7744,7 +8000,7 @@
         <v>156456.45617367997</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J7" s="26">
         <v>46318</v>
@@ -7825,7 +8081,7 @@
         <v>99</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>100</v>
@@ -7847,7 +8103,7 @@
         <v>166930.70827071602</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J8" s="26">
         <v>46358</v>
@@ -7947,7 +8203,7 @@
         <v>154576.23000000001</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="J9" s="26">
         <v>46344</v>
@@ -8045,7 +8301,7 @@
         <v>338</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K10" s="17">
         <v>86153</v>
@@ -8117,7 +8373,7 @@
         <v>64263.117867149995</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="J11" s="26">
         <v>46294</v>
@@ -8214,7 +8470,7 @@
         <v>160183.89110417402</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="J12" s="26">
         <v>46303</v>
@@ -8302,7 +8558,7 @@
         <v>84285.862482079989</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="J13" s="26">
         <v>46288</v>
@@ -8381,7 +8637,7 @@
         <v>76050.478160000013</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="J14" s="26">
         <v>46345</v>
@@ -8456,7 +8712,7 @@
         <v>10332.711477600002</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J15" s="26">
         <v>46366</v>
@@ -8531,7 +8787,7 @@
         <v>31132.194425488</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J16" s="26">
         <v>46324</v>
@@ -8584,34 +8840,36 @@
         <v>12</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="E17" s="24">
-        <f>+[86]Main!$I$2</f>
-        <v>22.51</v>
+        <f>+[12]Main!$I$2</f>
+        <v>14.68</v>
       </c>
       <c r="F17" s="17">
-        <f>+[86]Main!$I$4</f>
-        <v>40518</v>
+        <f>+[12]Main!$I$4</f>
+        <v>26409.32</v>
       </c>
       <c r="G17" s="17">
-        <f>+[86]Main!$I$6-[86]Main!$I$5</f>
-        <v>-4497</v>
+        <f>+[12]Main!$I$6-[12]Main!$I$5</f>
+        <v>-3507</v>
       </c>
       <c r="H17" s="17">
         <f>+F17+G17</f>
-        <v>36021</v>
+        <v>22902.32</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="J17" s="2"/>
+        <v>802</v>
+      </c>
+      <c r="J17" s="26">
+        <v>46329</v>
+      </c>
       <c r="K17" s="24"/>
       <c r="L17" s="21"/>
       <c r="M17" s="24"/>
@@ -8644,21 +8902,21 @@
         <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="24">
-        <f>+[12]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>250.5</v>
       </c>
       <c r="F18" s="17">
-        <f>+[12]Main!$H$4*FX!C3</f>
+        <f>+[13]Main!$H$4*FX!C3</f>
         <v>31944.883201920002</v>
       </c>
       <c r="G18" s="17">
-        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
+        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C3</f>
         <v>3456.96</v>
       </c>
       <c r="H18" s="17">
@@ -8666,7 +8924,7 @@
         <v>35401.843201920005</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J18" s="26">
         <v>46316</v>
@@ -8744,21 +9002,21 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E19" s="24">
-        <f>+[13]Main!$H$2</f>
+        <f>+[14]Main!$H$2</f>
         <v>78.75</v>
       </c>
       <c r="F19" s="17">
-        <f>+[13]Main!$H$5*FX!C9</f>
+        <f>+[14]Main!$H$5*FX!C9</f>
         <v>28408.679775000001</v>
       </c>
       <c r="G19" s="17">
-        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
+        <f>+([14]Main!$H$7-[14]Main!$H$6)*FX!C9</f>
         <v>-2787.26</v>
       </c>
       <c r="H19" s="17">
@@ -8766,9 +9024,11 @@
         <v>25621.419775000002</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="J19" s="26"/>
+        <v>802</v>
+      </c>
+      <c r="J19" s="26">
+        <v>46352</v>
+      </c>
       <c r="K19" s="17">
         <f>70826*FX!C9</f>
         <v>9915.6400000000012</v>
@@ -8827,15 +9087,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="24">
-        <f>+[14]Main!$M$2</f>
+        <f>+[15]Main!$M$2</f>
         <v>103.91</v>
       </c>
       <c r="F20" s="17">
-        <f>+[14]Main!$M$4</f>
+        <f>+[15]Main!$M$4</f>
         <v>14174.802327570002</v>
       </c>
       <c r="G20" s="17">
-        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
+        <f>+[15]Main!$M$6-[15]Main!$M$5</f>
         <v>-1602.5889999999999</v>
       </c>
       <c r="H20" s="17">
@@ -8843,7 +9103,7 @@
         <v>12572.213327570002</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="J20" s="26">
         <v>46317</v>
@@ -8911,15 +9171,15 @@
         <v>21</v>
       </c>
       <c r="E21" s="24">
-        <f>+[15]Main!$J$2</f>
+        <f>+[16]Main!$J$2</f>
         <v>130</v>
       </c>
       <c r="F21" s="17">
-        <f>+[15]Main!$J$4</f>
+        <f>+[16]Main!$J$4</f>
         <v>25920.918140000002</v>
       </c>
       <c r="G21" s="17">
-        <f>+[15]Main!$J$6-[15]Main!$J$5</f>
+        <f>+[16]Main!$J$6-[16]Main!$J$5</f>
         <v>1227</v>
       </c>
       <c r="H21" s="17">
@@ -8927,7 +9187,7 @@
         <v>27147.918140000002</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="J21" s="26">
         <v>46331</v>
@@ -8974,26 +9234,26 @@
         <v>109</v>
       </c>
       <c r="E22" s="24">
-        <f>+[16]Main!$I$2</f>
-        <v>166.25</v>
+        <f>+[17]Main!$I$2</f>
+        <v>161.25</v>
       </c>
       <c r="F22" s="17">
-        <f>+[16]Main!$I$4*FX!C4</f>
-        <v>25232.110793750002</v>
+        <f>+[17]Main!$I$4*FX!C4</f>
+        <v>24454.438893750001</v>
       </c>
       <c r="G22" s="17">
-        <f>+([16]Main!$I$6-[16]Main!$I$5)*FX!C4</f>
-        <v>187.91</v>
+        <f>+([17]Main!$I$6-[17]Main!$I$5)*FX!C4</f>
+        <v>-554.04</v>
       </c>
       <c r="H22" s="17">
         <f t="shared" si="1"/>
-        <v>25420.020793750002</v>
+        <v>23900.39889375</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="J22" s="26">
-        <v>46289</v>
+        <v>46415</v>
       </c>
       <c r="K22" s="17">
         <f>234478*FX!C4</f>
@@ -9036,21 +9296,21 @@
         <v>25</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="24">
-        <f>+[17]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>389.9</v>
       </c>
       <c r="F23" s="17">
-        <f>+[17]Main!$H$4</f>
+        <f>+[18]Main!$H$4</f>
         <v>23231.114986099998</v>
       </c>
       <c r="G23" s="17">
-        <f>+[17]Main!$H$6-[17]Main!$H$5</f>
+        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
         <v>-633.5</v>
       </c>
       <c r="H23" s="17">
@@ -9058,7 +9318,7 @@
         <v>22597.614986099998</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="J23" s="26">
         <v>46331</v>
@@ -9136,15 +9396,15 @@
         <v>124</v>
       </c>
       <c r="E24" s="24">
-        <f>+[18]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>5281</v>
       </c>
       <c r="F24" s="17">
-        <f>+[18]Main!$I$4*FX!C5</f>
+        <f>+[19]Main!$I$4*FX!C5</f>
         <v>23581.789650335701</v>
       </c>
       <c r="G24" s="17">
-        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C5</f>
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C5</f>
         <v>-471.03210000000001</v>
       </c>
       <c r="H24" s="17">
@@ -9152,7 +9412,7 @@
         <v>23110.7575503357</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J24" s="26">
         <v>46337</v>
@@ -9190,24 +9450,24 @@
         <v>20</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E25" s="24">
-        <f>+[80]Main!$J$2</f>
+        <f>+[20]Main!$J$2</f>
         <v>48.5</v>
       </c>
       <c r="F25" s="17">
-        <f>+[80]Main!$J$5</f>
+        <f>+[20]Main!$J$5</f>
         <v>26772.307449745003</v>
       </c>
       <c r="G25" s="17">
-        <f>+[80]Main!$J$7-[80]Main!$J$6</f>
+        <f>+[20]Main!$J$7-[20]Main!$J$6</f>
         <v>-15210</v>
       </c>
       <c r="H25" s="17">
@@ -9215,9 +9475,11 @@
         <v>11562.307449745003</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>805</v>
-      </c>
-      <c r="J25" s="2"/>
+        <v>802</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>900</v>
+      </c>
       <c r="K25" s="24"/>
       <c r="L25" s="21"/>
       <c r="M25" s="24"/>
@@ -9256,15 +9518,15 @@
         <v>165</v>
       </c>
       <c r="E26" s="24">
-        <f>+[19]Main!$H$2</f>
+        <f>+[21]Main!$H$2</f>
         <v>43.26</v>
       </c>
       <c r="F26" s="17">
-        <f>+[19]Main!$H$5*FX!C3</f>
+        <f>+[21]Main!$H$5*FX!C3</f>
         <v>13814.701834751999</v>
       </c>
       <c r="G26" s="17">
-        <f>(+[19]Main!$H$7-[19]Main!$H$6)*FX!C3</f>
+        <f>(+[21]Main!$H$7-[21]Main!$H$6)*FX!C3</f>
         <v>727.22728000000006</v>
       </c>
       <c r="H26" s="17">
@@ -9272,7 +9534,7 @@
         <v>14541.929114751998</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J26" s="26">
         <v>46317</v>
@@ -9310,24 +9572,24 @@
         <v>22</v>
       </c>
       <c r="B27" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E27" s="24">
-        <f>+[20]Main!$I$2</f>
+        <f>+[22]Main!$I$2</f>
         <v>2992.7</v>
       </c>
       <c r="F27" s="17">
-        <f>+[20]Main!$I$4*FX!C12</f>
+        <f>+[22]Main!$I$4*FX!C12</f>
         <v>11702.540569881699</v>
       </c>
       <c r="G27" s="17">
-        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C12</f>
+        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C12</f>
         <v>2616.768</v>
       </c>
       <c r="H27" s="17">
@@ -9335,7 +9597,7 @@
         <v>14319.308569881699</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="J27" s="26"/>
       <c r="K27" s="24"/>
@@ -9370,21 +9632,21 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>165</v>
       </c>
       <c r="E28" s="24">
-        <f>+[21]Main!$H$2</f>
+        <f>+[23]Main!$H$2</f>
         <v>47.32</v>
       </c>
       <c r="F28" s="17">
-        <f>+[21]Main!$H$4*FX!C3</f>
+        <f>+[23]Main!$H$4*FX!C3</f>
         <v>13313.188044374401</v>
       </c>
       <c r="G28" s="17">
-        <f>+([21]Main!$H$6-[21]Main!$H$5)*FX!C3</f>
+        <f>+([23]Main!$H$6-[23]Main!$H$5)*FX!C3</f>
         <v>-376.31984</v>
       </c>
       <c r="H28" s="17">
@@ -9392,7 +9654,7 @@
         <v>12936.868204374401</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J28" s="26">
         <v>46316</v>
@@ -9439,15 +9701,15 @@
         <v>21</v>
       </c>
       <c r="E29" s="24">
-        <f>+[22]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>294.94</v>
       </c>
       <c r="F29" s="17">
-        <f>+[22]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>18845.486239999998</v>
       </c>
       <c r="G29" s="17">
-        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>1189.8249999999998</v>
       </c>
       <c r="H29" s="17">
@@ -9455,7 +9717,7 @@
         <v>20035.311239999999</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J29" s="26">
         <v>46350</v>
@@ -9502,15 +9764,15 @@
         <v>219</v>
       </c>
       <c r="E30" s="24">
-        <f>+[23]Main!$I$2</f>
+        <f>+[25]Main!$I$2</f>
         <v>156</v>
       </c>
       <c r="F30" s="17">
-        <f>+[23]Main!$I$4*FX!C8</f>
+        <f>+[25]Main!$I$4*FX!C8</f>
         <v>22613.136000000002</v>
       </c>
       <c r="G30" s="17">
-        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C8</f>
+        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C8</f>
         <v>883.74799999999993</v>
       </c>
       <c r="H30" s="17">
@@ -9565,15 +9827,15 @@
         <v>166</v>
       </c>
       <c r="E31" s="24">
-        <f>+[24]Main!$H$2</f>
+        <f>+[26]Main!$H$2</f>
         <v>30.85</v>
       </c>
       <c r="F31" s="17">
-        <f>+[24]Main!$H$5*FX!C7</f>
+        <f>+[26]Main!$H$5*FX!C7</f>
         <v>8718.9328789276005</v>
       </c>
       <c r="G31" s="17">
-        <f>+([24]Main!$H$7-[24]Main!$H$6)*FX!C7</f>
+        <f>+([26]Main!$H$7-[26]Main!$H$6)*FX!C7</f>
         <v>-1077.8880000000001</v>
       </c>
       <c r="H31" s="17">
@@ -9581,7 +9843,7 @@
         <v>7641.0448789276006</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J31" s="26">
         <v>46337</v>
@@ -9628,15 +9890,15 @@
         <v>214</v>
       </c>
       <c r="E32" s="24">
-        <f>+[25]Main!$J$2</f>
+        <f>+[27]Main!$J$2</f>
         <v>33.79</v>
       </c>
       <c r="F32" s="17">
-        <f>+[25]Main!$J$4</f>
+        <f>+[27]Main!$J$4</f>
         <v>19685.281459229998</v>
       </c>
       <c r="G32" s="17">
-        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
+        <f>+[27]Main!$J$6-[27]Main!$J$5</f>
         <v>-573</v>
       </c>
       <c r="H32" s="17">
@@ -9644,7 +9906,7 @@
         <v>19112.281459229998</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J32" s="26">
         <v>46343</v>
@@ -9685,21 +9947,21 @@
         <v>22</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E33" s="24">
-        <f>+[26]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>35.46</v>
       </c>
       <c r="F33" s="17">
-        <f>+[26]Main!$J$5*FX!C9</f>
+        <f>+[28]Main!$J$5*FX!C9</f>
         <v>6567.085595546785</v>
       </c>
       <c r="G33" s="17">
-        <f>+([26]Main!$J$7-[26]Main!$J$6)*FX!C9</f>
+        <f>+([28]Main!$J$7-[28]Main!$J$6)*FX!C9</f>
         <v>-3721.6155200000003</v>
       </c>
       <c r="H33" s="17">
@@ -9707,7 +9969,7 @@
         <v>2845.4700755467848</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J33" s="26">
         <v>46441</v>
@@ -9748,21 +10010,21 @@
         <v>381</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E34" s="24">
-        <f>+[27]Main!$K$2</f>
+        <f>+[29]Main!$K$2</f>
         <v>76.739999999999995</v>
       </c>
       <c r="F34" s="17">
-        <f>+[27]Main!$K$4*FX!C9</f>
+        <f>+[29]Main!$K$4*FX!C9</f>
         <v>12537.781199999999</v>
       </c>
       <c r="G34" s="17">
-        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
+        <f>+([29]Main!$K$6-[29]Main!$K$5)*FX!C9</f>
         <v>-745.22328020000009</v>
       </c>
       <c r="H34" s="17">
@@ -9817,15 +10079,15 @@
         <v>82</v>
       </c>
       <c r="E35" s="24">
-        <f>+[28]Main!$I$2</f>
+        <f>+[30]Main!$I$2</f>
         <v>25.27</v>
       </c>
       <c r="F35" s="17">
-        <f>+[28]Main!$I$4*FX!C3</f>
+        <f>+[30]Main!$I$4*FX!C3</f>
         <v>6543.9191999999994</v>
       </c>
       <c r="G35" s="17">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
+        <f>+([30]Main!$I$6-[30]Main!$I$5)*FX!C3</f>
         <v>-477.15199999999999</v>
       </c>
       <c r="H35" s="17">
@@ -9833,7 +10095,7 @@
         <v>6066.7671999999993</v>
       </c>
       <c r="I35" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J35" s="26">
         <v>46329</v>
@@ -9880,15 +10142,15 @@
         <v>21</v>
       </c>
       <c r="E36" s="24">
-        <f>+[29]Main!$H$2</f>
+        <f>+[31]Main!$H$2</f>
         <v>14.5</v>
       </c>
       <c r="F36" s="17">
-        <f>+[29]Main!$H$4</f>
+        <f>+[31]Main!$H$4</f>
         <v>5700.4512649999997</v>
       </c>
       <c r="G36" s="17">
-        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
+        <f>+[31]Main!$H$6-[31]Main!$H$5</f>
         <v>2343.0419999999999</v>
       </c>
       <c r="H36" s="17">
@@ -9896,7 +10158,7 @@
         <v>8043.4932649999992</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="J36" s="26">
         <v>46322</v>
@@ -9943,15 +10205,15 @@
         <v>82</v>
       </c>
       <c r="E37" s="24">
-        <f>+[30]Main!$I$3</f>
+        <f>+[32]Main!$I$3</f>
         <v>34.85</v>
       </c>
       <c r="F37" s="17">
-        <f>+[30]Main!$I$5*FX!C3</f>
+        <f>+[32]Main!$I$5*FX!C3</f>
         <v>6665.4910936640008</v>
       </c>
       <c r="G37" s="17">
-        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
+        <f>+([32]Main!$I$7-[32]Main!$I$6)*FX!C3</f>
         <v>1033.5260000000001</v>
       </c>
       <c r="H37" s="17">
@@ -9959,7 +10221,7 @@
         <v>7699.0170936640006</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="J37" s="26">
         <v>46373</v>
@@ -10000,21 +10262,21 @@
         <v>111</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="24">
-        <f>+[31]Main!$J$2</f>
+        <f>+[33]Main!$J$2</f>
         <v>23.84</v>
       </c>
       <c r="F38" s="17">
-        <f>+[31]Main!$J$4</f>
+        <f>+[33]Main!$J$4</f>
         <v>8463.2000000000007</v>
       </c>
       <c r="G38" s="17">
-        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)</f>
         <v>-992</v>
       </c>
       <c r="H38" s="17">
@@ -10022,7 +10284,7 @@
         <v>7471.2000000000007</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J38" s="26">
         <v>46345</v>
@@ -10081,15 +10343,15 @@
         <v>21</v>
       </c>
       <c r="E39" s="24">
-        <f>+[32]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>60.4</v>
       </c>
       <c r="F39" s="17">
-        <f>+[32]Main!$I$4</f>
+        <f>+[34]Main!$I$4</f>
         <v>9118.7085583999997</v>
       </c>
       <c r="G39" s="17">
-        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
+        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
         <v>-838.96200000000022</v>
       </c>
       <c r="H39" s="17">
@@ -10100,7 +10362,7 @@
         <v>337</v>
       </c>
       <c r="J39" s="30" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="K39" s="17"/>
       <c r="L39" s="21"/>
@@ -10144,15 +10406,15 @@
         <v>165</v>
       </c>
       <c r="E40" s="24">
-        <f>+[33]Main!$J$2</f>
+        <f>+[35]Main!$J$2</f>
         <v>87.92</v>
       </c>
       <c r="F40" s="17">
-        <f>+[33]Main!$J$4*FX!C3</f>
+        <f>+[35]Main!$J$4*FX!C3</f>
         <v>6217.1241536768002</v>
       </c>
       <c r="G40" s="17">
-        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
+        <f>+([35]Main!$J$6-[35]Main!$J$5)*FX!C3</f>
         <v>227.71215999999995</v>
       </c>
       <c r="H40" s="17">
@@ -10160,7 +10422,7 @@
         <v>6444.8363136768003</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J40" s="26">
         <v>46310</v>
@@ -10207,15 +10469,15 @@
         <v>107</v>
       </c>
       <c r="E41" s="24">
-        <f>+[34]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>55.89</v>
       </c>
       <c r="F41" s="17">
-        <f>+[34]Main!$I$4</f>
+        <f>+[36]Main!$I$4</f>
         <v>10349.486639999999</v>
       </c>
       <c r="G41" s="17">
-        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
+        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
         <v>4262.759</v>
       </c>
       <c r="H41" s="17">
@@ -10223,7 +10485,7 @@
         <v>14612.245639999999</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J41" s="26">
         <v>46323</v>
@@ -10270,15 +10532,15 @@
         <v>21</v>
       </c>
       <c r="E42" s="24">
-        <f>+[35]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>24.26</v>
       </c>
       <c r="F42" s="17">
-        <f>+[35]Main!$I$4</f>
+        <f>+[37]Main!$I$4</f>
         <v>8463.1146341200019</v>
       </c>
       <c r="G42" s="17">
-        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
+        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
         <v>65.200000000000045</v>
       </c>
       <c r="H42" s="17">
@@ -10286,7 +10548,7 @@
         <v>8528.3146341200027</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J42" s="26">
         <v>46303</v>
@@ -10345,15 +10607,15 @@
         <v>294</v>
       </c>
       <c r="E43" s="24">
-        <f>+[36]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>21560</v>
       </c>
       <c r="F43" s="17">
-        <f>+[36]Main!$I$4*FX!C11</f>
+        <f>+[38]Main!$I$4*FX!C11</f>
         <v>10018.43612</v>
       </c>
       <c r="G43" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
+        <f>+([38]Main!$I$6-[38]Main!$I$5)*FX!C11</f>
         <v>295.25</v>
       </c>
       <c r="H43" s="17">
@@ -10401,18 +10663,18 @@
         <v>600398</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E44" s="24">
-        <f>+[37]Main!$J$2</f>
+        <f>+[39]Main!$J$2</f>
         <v>8.7799999999999994</v>
       </c>
       <c r="F44" s="17">
-        <f>+[37]Main!$J$4*FX!C9</f>
+        <f>+[39]Main!$J$4*FX!C9</f>
         <v>5900.1600000000008</v>
       </c>
       <c r="G44" s="17">
-        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
+        <f>+([39]Main!$J$6-[39]Main!$J$5)*FX!C9</f>
         <v>-679.00000000000011</v>
       </c>
       <c r="H44" s="17">
@@ -10463,15 +10725,15 @@
         <v>185</v>
       </c>
       <c r="E45" s="24">
-        <f>+[38]Main!$H$2</f>
+        <f>+[40]Main!$H$2</f>
         <v>41240</v>
       </c>
       <c r="F45" s="17">
-        <f>+[38]Main!$H$4*FX!C12</f>
+        <f>+[40]Main!$H$4*FX!C12</f>
         <v>5059.9509140399996</v>
       </c>
       <c r="G45" s="17">
-        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
+        <f>+([40]Main!$H$6-[40]Main!$H$5)*FX!C12</f>
         <v>79.99563000000002</v>
       </c>
       <c r="H45" s="17">
@@ -10479,7 +10741,7 @@
         <v>5139.9465440399999</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J45" s="26">
         <v>45975</v>
@@ -10522,15 +10784,15 @@
         <v>21</v>
       </c>
       <c r="E46" s="24">
-        <f>+[39]Main!$H$2</f>
+        <f>+[41]Main!$H$2</f>
         <v>121.86</v>
       </c>
       <c r="F46" s="17">
-        <f>+[39]Main!$H$4</f>
+        <f>+[41]Main!$H$4</f>
         <v>5842.5868395000007</v>
       </c>
       <c r="G46" s="17">
-        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
+        <f>+[41]Main!$H$6-[41]Main!$H$5</f>
         <v>1137.3819999999998</v>
       </c>
       <c r="H46" s="17">
@@ -10538,7 +10800,7 @@
         <v>6979.9688395000003</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J46" s="26">
         <v>46324</v>
@@ -10585,15 +10847,15 @@
         <v>325</v>
       </c>
       <c r="E47" s="24">
-        <f>+[40]Main!$I$2</f>
+        <f>+[42]Main!$I$2</f>
         <v>27.8</v>
       </c>
       <c r="F47" s="17">
-        <f>+[40]Main!$I$4*FX!C14</f>
+        <f>+[42]Main!$I$4*FX!C14</f>
         <v>5512.4063999999998</v>
       </c>
       <c r="G47" s="17">
-        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
+        <f>+([42]Main!$I$6-[42]Main!$I$5)*FX!C14</f>
         <v>392.36399999999998</v>
       </c>
       <c r="H47" s="17">
@@ -10648,15 +10910,15 @@
         <v>219</v>
       </c>
       <c r="E48" s="24">
-        <f>+[41]Main!$I$2</f>
+        <f>+[43]Main!$I$2</f>
         <v>0.93779999999999997</v>
       </c>
       <c r="F48" s="17">
-        <f>+[41]Main!$I$4*FX!C8</f>
+        <f>+[43]Main!$I$4*FX!C8</f>
         <v>5962.0447439999998</v>
       </c>
       <c r="G48" s="17">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
+        <f>+([43]Main!$I$6-[43]Main!$I$5)*FX!C8</f>
         <v>155</v>
       </c>
       <c r="H48" s="17">
@@ -10664,7 +10926,7 @@
         <v>6117.0447439999998</v>
       </c>
       <c r="I48" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J48" s="26">
         <v>45981</v>
@@ -10711,15 +10973,15 @@
         <v>107</v>
       </c>
       <c r="E49" s="24">
-        <f>+[42]Main!$H$2</f>
+        <f>+[44]Main!$H$2</f>
         <v>86.42</v>
       </c>
       <c r="F49" s="17">
-        <f>+[42]Main!$H$4*FX!C13</f>
+        <f>+[44]Main!$H$4*FX!C13</f>
         <v>6825.0480185999995</v>
       </c>
       <c r="G49" s="17">
-        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
+        <f>+([44]Main!$H$6-[44]Main!$H$5)*FX!C13</f>
         <v>-201.90158999999997</v>
       </c>
       <c r="H49" s="17">
@@ -10727,7 +10989,7 @@
         <v>6623.1464285999991</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J49" s="26">
         <v>45939</v>
@@ -10764,21 +11026,21 @@
         <v>388</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E50" s="24">
-        <f>+[43]Main!$H$2</f>
+        <f>+[45]Main!$H$2</f>
         <v>16.02</v>
       </c>
       <c r="F50" s="17">
-        <f>+[43]Main!$H$5*FX!C9</f>
+        <f>+[45]Main!$H$5*FX!C9</f>
         <v>5313.5769879360005</v>
       </c>
       <c r="G50" s="17">
-        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
+        <f>+([45]Main!$H$7-[45]Main!$H$6)*FX!C9</f>
         <v>-2458.0551799999998</v>
       </c>
       <c r="H50" s="17">
@@ -10825,21 +11087,21 @@
         <v>47</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="E51" s="24">
-        <f>+[44]Main!$I$2</f>
+        <f>+[46]Main!$I$2</f>
         <v>8.01</v>
       </c>
       <c r="F51" s="17">
-        <f>+[44]Main!$I$4*FX!C9</f>
+        <f>+[46]Main!$I$4*FX!C9</f>
         <v>5141.5464790620008</v>
       </c>
       <c r="G51" s="17">
-        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
+        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C9</f>
         <v>1697.6221653999999</v>
       </c>
       <c r="H51" s="17">
@@ -10888,15 +11150,15 @@
         <v>21</v>
       </c>
       <c r="E52" s="24">
-        <f>+[45]Main!$J$2</f>
+        <f>+[47]Main!$J$2</f>
         <v>79.900000000000006</v>
       </c>
       <c r="F52" s="17">
-        <f>+[45]Main!$J$4</f>
+        <f>+[47]Main!$J$4</f>
         <v>6842.1251993000005</v>
       </c>
       <c r="G52" s="17">
-        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
+        <f>+[47]Main!$J$6-[47]Main!$J$5</f>
         <v>-716.12699999999995</v>
       </c>
       <c r="H52" s="17">
@@ -10904,7 +11166,7 @@
         <v>6125.9981993000001</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="J52" s="26">
         <v>46350</v>
@@ -10947,15 +11209,15 @@
         <v>82</v>
       </c>
       <c r="E53" s="24">
-        <f>+[46]Main!$I$2</f>
+        <f>+[48]Main!$I$2</f>
         <v>25.8</v>
       </c>
       <c r="F53" s="17">
-        <f>+[46]Main!$I$4*FX!C3</f>
+        <f>+[48]Main!$I$4*FX!C3</f>
         <v>3949.9093389599998</v>
       </c>
       <c r="G53" s="17">
-        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
+        <f>+([48]Main!$I$6-[48]Main!$I$5)*FX!C3</f>
         <v>1411.904</v>
       </c>
       <c r="H53" s="17">
@@ -10963,7 +11225,7 @@
         <v>5361.8133389599998</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J53" s="26">
         <v>46325</v>
@@ -11007,18 +11269,18 @@
         <v>390</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E54" s="24">
-        <f>+[47]Main!$I$2</f>
+        <f>+[49]Main!$I$2</f>
         <v>3.75</v>
       </c>
       <c r="F54" s="17">
-        <f>+[47]Main!$I$5*FX!C9</f>
+        <f>+[49]Main!$I$5*FX!C9</f>
         <v>5271.5025720000003</v>
       </c>
       <c r="G54" s="17">
-        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
+        <f>+([49]Main!$I$7-[49]Main!$I$6)*FX!C9</f>
         <v>-653.85012000000006</v>
       </c>
       <c r="H54" s="17">
@@ -11073,15 +11335,15 @@
         <v>21</v>
       </c>
       <c r="E55" s="24">
-        <f>+[48]Main!$I$2</f>
+        <f>+[50]Main!$I$2</f>
         <v>148.80000000000001</v>
       </c>
       <c r="F55" s="17">
-        <f>+[48]Main!$I$4</f>
+        <f>+[50]Main!$I$4</f>
         <v>6512.5296000000008</v>
       </c>
       <c r="G55" s="17">
-        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
+        <f>+[50]Main!$I$6-[50]Main!$I$5</f>
         <v>-637.99900000000002</v>
       </c>
       <c r="H55" s="17">
@@ -11089,7 +11351,7 @@
         <v>5874.530600000001</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J55" s="26">
         <v>46350</v>
@@ -11148,15 +11410,15 @@
         <v>21</v>
       </c>
       <c r="E56" s="24">
-        <f>+[49]Main!$I$2</f>
+        <f>+[51]Main!$I$2</f>
         <v>56.92</v>
       </c>
       <c r="F56" s="17">
-        <f>+[49]Main!$I$4</f>
+        <f>+[51]Main!$I$4</f>
         <v>2913.9166024800002</v>
       </c>
       <c r="G56" s="17">
-        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
+        <f>+[51]Main!$I$6-[51]Main!$I$5</f>
         <v>-624.601</v>
       </c>
       <c r="H56" s="17">
@@ -11164,7 +11426,7 @@
         <v>2289.3156024800001</v>
       </c>
       <c r="I56" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J56" s="26">
         <v>46324</v>
@@ -11211,15 +11473,15 @@
         <v>21</v>
       </c>
       <c r="E57" s="24">
-        <f>+[50]Main!$J$2</f>
+        <f>+[52]Main!$J$2</f>
         <v>72.459999999999994</v>
       </c>
       <c r="F57" s="17">
-        <f>+[50]Main!$J$4</f>
+        <f>+[52]Main!$J$4</f>
         <v>3343.1473791799999</v>
       </c>
       <c r="G57" s="17">
-        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
+        <f>+([52]Main!$J$6-[52]Main!$J$5)</f>
         <v>1270.5999999999999</v>
       </c>
       <c r="H57" s="17">
@@ -11227,7 +11489,7 @@
         <v>4613.7473791800003</v>
       </c>
       <c r="I57" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J57" s="26">
         <v>46359</v>
@@ -11274,15 +11536,15 @@
         <v>124</v>
       </c>
       <c r="E58" s="24">
-        <f>+[51]Main!$I$2</f>
+        <f>+[53]Main!$I$2</f>
         <v>2816.5</v>
       </c>
       <c r="F58" s="17">
-        <f>+[51]Main!$I$4*FX!C5</f>
+        <f>+[53]Main!$I$4*FX!C5</f>
         <v>4393.7011297651507</v>
       </c>
       <c r="G58" s="17">
-        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
+        <f>+([53]Main!$I$6-[53]Main!$I$5)*FX!C5</f>
         <v>-837.64170000000001</v>
       </c>
       <c r="H58" s="17">
@@ -11331,21 +11593,21 @@
         <v>48</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>219</v>
       </c>
       <c r="E59" s="24">
-        <f>+[52]Main!$I$2</f>
+        <f>+[54]Main!$I$2</f>
         <v>10.93</v>
       </c>
       <c r="F59" s="17">
-        <f>+[52]Main!$I$4*FX!C3</f>
+        <f>+[54]Main!$I$4*FX!C3</f>
         <v>4072.8677600000001</v>
       </c>
       <c r="G59" s="17">
-        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
+        <f>+([54]Main!$I$6-[54]Main!$I$5)*FX!C3</f>
         <v>-107.12</v>
       </c>
       <c r="H59" s="17">
@@ -11353,7 +11615,7 @@
         <v>3965.7477600000002</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="J59" s="26"/>
       <c r="K59" s="17"/>
@@ -11394,15 +11656,15 @@
         <v>21</v>
       </c>
       <c r="E60" s="24">
-        <f>+[53]Main!$I$2</f>
+        <f>+[55]Main!$I$2</f>
         <v>165.1</v>
       </c>
       <c r="F60" s="17">
-        <f>+[53]Main!$I$4</f>
+        <f>+[55]Main!$I$4</f>
         <v>5044.7333572999996</v>
       </c>
       <c r="G60" s="17">
-        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
+        <f>+[55]Main!$I$6-[55]Main!$I$5</f>
         <v>-95.319000000000003</v>
       </c>
       <c r="H60" s="17">
@@ -11410,7 +11672,7 @@
         <v>4949.4143572999992</v>
       </c>
       <c r="I60" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J60" s="26">
         <v>45957</v>
@@ -11457,15 +11719,15 @@
         <v>21</v>
       </c>
       <c r="E61" s="24">
-        <f>+[54]Main!$I$2</f>
+        <f>+[56]Main!$I$2</f>
         <v>78.680000000000007</v>
       </c>
       <c r="F61" s="17">
-        <f>+[54]Main!$I$4</f>
+        <f>+[56]Main!$I$4</f>
         <v>4372.5807311200006</v>
       </c>
       <c r="G61" s="17">
-        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
+        <f>+[56]Main!$I$6-[56]Main!$I$5</f>
         <v>1259.028</v>
       </c>
       <c r="H61" s="17">
@@ -11511,7 +11773,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>346</v>
@@ -11520,7 +11782,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F62" s="17"/>
       <c r="G62" s="17"/>
@@ -11561,21 +11823,21 @@
         <v>50</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>433</v>
       </c>
       <c r="E63" s="24">
-        <f>+[55]Main!$J$2</f>
+        <f>+[57]Main!$J$2</f>
         <v>132.5</v>
       </c>
       <c r="F63" s="17">
-        <f>+[55]Main!$J$4*FX!C15</f>
+        <f>+[57]Main!$J$4*FX!C15</f>
         <v>3925.244925</v>
       </c>
       <c r="G63" s="17">
-        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
+        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C15</f>
         <v>122.75229000000002</v>
       </c>
       <c r="H63" s="17">
@@ -11624,15 +11886,15 @@
         <v>21</v>
       </c>
       <c r="E64" s="24">
-        <f>+[56]Main!$J$2</f>
+        <f>+[58]Main!$J$2</f>
         <v>161.28</v>
       </c>
       <c r="F64" s="17">
-        <f>+[56]Main!$J$4</f>
+        <f>+[58]Main!$J$4</f>
         <v>2990.6024601600002</v>
       </c>
       <c r="G64" s="17">
-        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
+        <f>+[58]Main!$J$6-[58]Main!$J$5</f>
         <v>-211.91</v>
       </c>
       <c r="H64" s="17">
@@ -11640,7 +11902,7 @@
         <v>2778.6924601600003</v>
       </c>
       <c r="I64" s="16" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="J64" s="26">
         <v>45952</v>
@@ -11677,21 +11939,21 @@
         <v>53</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E65" s="24">
-        <f>+[57]Main!$J$2</f>
+        <f>+[59]Main!$J$2</f>
         <v>37.94</v>
       </c>
       <c r="F65" s="17">
-        <f>+[57]Main!$J$4*FX!C3</f>
+        <f>+[59]Main!$J$4*FX!C3</f>
         <v>2723.2123110191997</v>
       </c>
       <c r="G65" s="17">
-        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
+        <f>+([59]Main!$J$6-[59]Main!$J$5)*FX!C3</f>
         <v>-54.08</v>
       </c>
       <c r="H65" s="17">
@@ -11699,7 +11961,7 @@
         <v>2669.1323110191997</v>
       </c>
       <c r="I65" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J65" s="26">
         <v>46329</v>
@@ -11742,15 +12004,15 @@
         <v>21</v>
       </c>
       <c r="E66" s="24">
-        <f>+[58]Main!$I$2</f>
+        <f>+[60]Main!$I$2</f>
         <v>5.53</v>
       </c>
       <c r="F66" s="17">
-        <f>+[58]Main!$I$4</f>
+        <f>+[60]Main!$I$4</f>
         <v>1932.9868362000002</v>
       </c>
       <c r="G66" s="17">
-        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
+        <f>+[60]Main!$I$6-[60]Main!$I$5</f>
         <v>195.17700000000002</v>
       </c>
       <c r="H66" s="17">
@@ -11758,7 +12020,7 @@
         <v>2128.1638362000003</v>
       </c>
       <c r="I66" s="16" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="J66" s="26">
         <v>46331</v>
@@ -11801,15 +12063,15 @@
         <v>21</v>
       </c>
       <c r="E67" s="24">
-        <f>+[59]Main!$I$2</f>
+        <f>+[61]Main!$I$2</f>
         <v>17.37</v>
       </c>
       <c r="F67" s="17">
-        <f>+[59]Main!$I$4</f>
+        <f>+[61]Main!$I$4</f>
         <v>2910.7487942100001</v>
       </c>
       <c r="G67" s="17">
-        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
+        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
         <v>-18.286000000000001</v>
       </c>
       <c r="H67" s="17">
@@ -11817,7 +12079,7 @@
         <v>2892.4627942100001</v>
       </c>
       <c r="I67" s="16" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J67" s="26"/>
       <c r="K67" s="17"/>
@@ -11858,15 +12120,15 @@
         <v>185</v>
       </c>
       <c r="E68" s="24">
-        <f>+[60]Main!$I$2</f>
+        <f>+[62]Main!$I$2</f>
         <v>263.45</v>
       </c>
       <c r="F68" s="17">
-        <f>+[60]Main!$I$4*FX!C12</f>
+        <f>+[62]Main!$I$4*FX!C12</f>
         <v>2976.4027894628493</v>
       </c>
       <c r="G68" s="17">
-        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
+        <f>+([62]Main!$I$6-[62]Main!$I$5)*FX!C12</f>
         <v>26.92503</v>
       </c>
       <c r="H68" s="17">
@@ -11909,21 +12171,21 @@
         <v>161</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E69" s="24">
-        <f>+[61]Main!$I$2</f>
+        <f>+[63]Main!$I$2</f>
         <v>73.62</v>
       </c>
       <c r="F69" s="17">
-        <f>+[61]Main!$I$4</f>
+        <f>+[63]Main!$I$4</f>
         <v>5852.1810889800008</v>
       </c>
       <c r="G69" s="17">
-        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
+        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
         <v>783</v>
       </c>
       <c r="H69" s="17">
@@ -11931,7 +12193,7 @@
         <v>6635.1810889800008</v>
       </c>
       <c r="I69" s="25" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J69" s="26">
         <v>46360</v>
@@ -11978,15 +12240,15 @@
         <v>21</v>
       </c>
       <c r="E70" s="24">
-        <f>+[62]Main!$H$2</f>
+        <f>+[64]Main!$H$2</f>
         <v>44.03</v>
       </c>
       <c r="F70" s="17">
-        <f>+[62]Main!$H$4</f>
+        <f>+[64]Main!$H$4</f>
         <v>3217.9517470800001</v>
       </c>
       <c r="G70" s="17">
-        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
+        <f>+[64]Main!$H$6-[64]Main!$H$5</f>
         <v>209.34100000000001</v>
       </c>
       <c r="H70" s="17">
@@ -11994,7 +12256,7 @@
         <v>3427.29274708</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J70" s="26">
         <v>46232</v>
@@ -12037,15 +12299,15 @@
         <v>219</v>
       </c>
       <c r="E71" s="24">
-        <f>+[63]Main!$I$2</f>
+        <f>+[65]Main!$I$2</f>
         <v>18.14</v>
       </c>
       <c r="F71" s="17">
-        <f>+[63]Main!$I$4</f>
+        <f>+[65]Main!$I$4</f>
         <v>2154.9996926600002</v>
       </c>
       <c r="G71" s="17">
-        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
+        <f>+[65]Main!$I$6-[65]Main!$I$5</f>
         <v>222</v>
       </c>
       <c r="H71" s="17">
@@ -12053,7 +12315,7 @@
         <v>2376.9996926600002</v>
       </c>
       <c r="I71" s="16" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="J71" s="26">
         <v>46239</v>
@@ -12100,15 +12362,15 @@
         <v>165</v>
       </c>
       <c r="E72" s="24">
-        <f>+[64]Main!$J$2</f>
+        <f>+[66]Main!$J$2</f>
         <v>11.0596</v>
       </c>
       <c r="F72" s="17">
-        <f>+[64]Main!$J$4*FX!C3</f>
+        <f>+[66]Main!$J$4*FX!C3</f>
         <v>2910.2755841993599</v>
       </c>
       <c r="G72" s="17">
-        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
+        <f>+([66]Main!$J$6-[66]Main!$J$5)*FX!C3</f>
         <v>-1.9947199999999772</v>
       </c>
       <c r="H72" s="17">
@@ -12116,7 +12378,7 @@
         <v>2908.2808641993597</v>
       </c>
       <c r="I72" s="16" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="J72" s="26">
         <v>46317</v>
@@ -12159,15 +12421,15 @@
         <v>185</v>
       </c>
       <c r="E73" s="24">
-        <f>+[65]Main!$J$2</f>
+        <f>+[67]Main!$J$2</f>
         <v>828.4</v>
       </c>
       <c r="F73" s="17">
-        <f>+[65]Main!$J$4*FX!C12</f>
+        <f>+[67]Main!$J$4*FX!C12</f>
         <v>2214.6636811287999</v>
       </c>
       <c r="G73" s="17">
-        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
+        <f>+([67]Main!$J$6-[67]Main!$J$5)*FX!C12</f>
         <v>-1.8833099999999996</v>
       </c>
       <c r="H73" s="17">
@@ -12669,15 +12931,15 @@
         <v>21</v>
       </c>
       <c r="E85" s="24">
-        <f>+[66]Main!$I$2</f>
+        <f>+[68]Main!$I$2</f>
         <v>5.82</v>
       </c>
       <c r="F85" s="17">
-        <f>+[66]Main!$I$4</f>
+        <f>+[68]Main!$I$4</f>
         <v>2055.0937514400002</v>
       </c>
       <c r="G85" s="17">
-        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
+        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
         <v>1971.2029999999997</v>
       </c>
       <c r="H85" s="17">
@@ -12891,7 +13153,7 @@
         <v>162</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="17"/>
@@ -12937,15 +13199,15 @@
         <v>21</v>
       </c>
       <c r="E91" s="24">
-        <f>+[67]Main!$H$2</f>
+        <f>+[69]Main!$H$2</f>
         <v>41.42</v>
       </c>
       <c r="F91" s="17">
-        <f>+[67]Main!$H$4</f>
+        <f>+[69]Main!$H$4</f>
         <v>1491.5652650000002</v>
       </c>
       <c r="G91" s="17">
-        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
+        <f>+[69]Main!$H$6-[69]Main!$H$5</f>
         <v>85.194000000000017</v>
       </c>
       <c r="H91" s="17">
@@ -12994,15 +13256,15 @@
         <v>21</v>
       </c>
       <c r="E92" s="24">
-        <f>+[68]Main!$I$2</f>
+        <f>+[70]Main!$I$2</f>
         <v>38.119999999999997</v>
       </c>
       <c r="F92" s="17">
-        <f>+[68]Main!$I$4</f>
+        <f>+[70]Main!$I$4</f>
         <v>1935.4971035199997</v>
       </c>
       <c r="G92" s="17">
-        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
         <v>-325.44000000000005</v>
       </c>
       <c r="H92" s="17">
@@ -13051,15 +13313,15 @@
         <v>21</v>
       </c>
       <c r="E93" s="24">
-        <f>+[69]Main!$I$2</f>
+        <f>+[71]Main!$I$2</f>
         <v>24.73</v>
       </c>
       <c r="F93" s="17">
-        <f>+[69]Main!$I$4</f>
+        <f>+[71]Main!$I$4</f>
         <v>1761.5194085300002</v>
       </c>
       <c r="G93" s="17">
-        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
+        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
         <v>-256.60000000000002</v>
       </c>
       <c r="H93" s="17">
@@ -13146,24 +13408,24 @@
         <v>90</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E95" s="24">
-        <f>+[79]Main!$J$2</f>
+        <f>+[72]Main!$J$2</f>
         <v>19.989999999999998</v>
       </c>
       <c r="F95" s="17">
-        <f>+[79]Main!$J$4</f>
+        <f>+[72]Main!$J$4</f>
         <v>1640.5061166099999</v>
       </c>
       <c r="G95" s="17">
-        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
+        <f>+[72]Main!$J$6-[72]Main!$J$5</f>
         <v>388.6</v>
       </c>
       <c r="H95" s="17">
@@ -13300,15 +13562,15 @@
         <v>21</v>
       </c>
       <c r="E98" s="24">
-        <f>+[70]Main!$I$2</f>
+        <f>+[73]Main!$I$2</f>
         <v>27.07</v>
       </c>
       <c r="F98" s="17">
-        <f>+[70]Main!$I$4</f>
+        <f>+[73]Main!$I$4</f>
         <v>1188.01315849</v>
       </c>
       <c r="G98" s="17">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
         <v>119.48899999999998</v>
       </c>
       <c r="H98" s="17">
@@ -13357,15 +13619,15 @@
         <v>21</v>
       </c>
       <c r="E99" s="24">
-        <f>+[71]Main!$I$2</f>
+        <f>+[74]Main!$I$2</f>
         <v>59.85</v>
       </c>
       <c r="F99" s="17">
-        <f>+[71]Main!$I$4</f>
+        <f>+[74]Main!$I$4</f>
         <v>939.70682505000002</v>
       </c>
       <c r="G99" s="17">
-        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
         <v>50.789000000000001</v>
       </c>
       <c r="H99" s="17">
@@ -13414,15 +13676,15 @@
         <v>107</v>
       </c>
       <c r="E100" s="24">
-        <f>+[72]Main!$J$2</f>
+        <f>+[75]Main!$J$2</f>
         <v>12.17</v>
       </c>
       <c r="F100" s="17">
-        <f>+[72]Main!$J$4*FX!C13</f>
+        <f>+[75]Main!$J$4*FX!C13</f>
         <v>817.17420560790003</v>
       </c>
       <c r="G100" s="17">
-        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
+        <f>+([75]Main!$J$6-[75]Main!$J$5)*FX!C13</f>
         <v>158.286</v>
       </c>
       <c r="H100" s="17">
@@ -13430,7 +13692,7 @@
         <v>975.46020560789998</v>
       </c>
       <c r="I100" s="16" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="J100" s="26">
         <v>46331</v>
@@ -13559,15 +13821,15 @@
         <v>21</v>
       </c>
       <c r="E103" s="24">
-        <f>+[73]Main!$I$2</f>
+        <f>+[76]Main!$I$2</f>
         <v>4.53</v>
       </c>
       <c r="F103" s="17">
-        <f>+[73]Main!$I$4</f>
+        <f>+[76]Main!$I$4</f>
         <v>736.21656488999997</v>
       </c>
       <c r="G103" s="17">
-        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
+        <f>+[76]Main!$I$6-[76]Main!$I$5</f>
         <v>-235.51</v>
       </c>
       <c r="H103" s="17">
@@ -13616,15 +13878,15 @@
         <v>21</v>
       </c>
       <c r="E104" s="24">
-        <f>+[74]Main!$I$2</f>
+        <f>+[77]Main!$I$2</f>
         <v>16.75</v>
       </c>
       <c r="F104" s="17">
-        <f>+[74]Main!$I$4</f>
+        <f>+[77]Main!$I$4</f>
         <v>872.38125524999998</v>
       </c>
       <c r="G104" s="17">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
         <v>434.077</v>
       </c>
       <c r="H104" s="17">
@@ -14275,15 +14537,15 @@
         <v>219</v>
       </c>
       <c r="E119" s="24">
-        <f>+'[75]Main '!$F$2</f>
+        <f>+'[78]Main '!$F$2</f>
         <v>2.4350000000000001</v>
       </c>
       <c r="F119" s="17">
-        <f>+'[75]Main '!$F$4*FX!C8</f>
+        <f>+'[78]Main '!$F$4*FX!C8</f>
         <v>360.19879762439996</v>
       </c>
       <c r="G119" s="17">
-        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
+        <f>+('[78]Main '!$F$6-'[78]Main '!$F$5)*FX!C8</f>
         <v>229.02800000000005</v>
       </c>
       <c r="H119" s="17">
@@ -14590,15 +14852,15 @@
         <v>21</v>
       </c>
       <c r="E126" s="24">
-        <f>+[76]Main!$H$2</f>
+        <f>+[79]Main!$H$2</f>
         <v>0.98</v>
       </c>
       <c r="F126" s="17">
-        <f>+[76]Main!$H$4</f>
+        <f>+[79]Main!$H$4</f>
         <v>97.21301296</v>
       </c>
       <c r="G126" s="17">
-        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
+        <f>+[79]Main!$H$6-[79]Main!$H$5</f>
         <v>274.101</v>
       </c>
       <c r="H126" s="17">
@@ -14606,7 +14868,7 @@
         <v>371.31401296000001</v>
       </c>
       <c r="I126" s="16" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="J126" s="26"/>
       <c r="K126" s="17"/>
@@ -14690,15 +14952,15 @@
         <v>21</v>
       </c>
       <c r="E128" s="24">
-        <f>+[77]Main!$I$2</f>
+        <f>+[80]Main!$I$2</f>
         <v>17.79</v>
       </c>
       <c r="F128" s="17">
-        <f>+[77]Main!$I$4</f>
+        <f>+[80]Main!$I$4</f>
         <v>270.90115659000003</v>
       </c>
       <c r="G128" s="17">
-        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
+        <f>+[80]Main!$I$6-[80]Main!$I$5</f>
         <v>24.493000000000002</v>
       </c>
       <c r="H128" s="17">
@@ -15942,24 +16204,24 @@
         <v>152</v>
       </c>
       <c r="B157" s="23" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>124</v>
       </c>
       <c r="E157" s="24">
-        <f>+[78]Main!$I$2</f>
+        <f>+[81]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F157" s="17">
-        <f>+[78]Main!$I$4*FX!C5</f>
+        <f>+[81]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G157" s="17">
-        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
+        <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H157" s="17">
@@ -15999,10 +16261,10 @@
         <v>153</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>124</v>
@@ -16042,10 +16304,10 @@
         <v>154</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>21</v>
@@ -16085,10 +16347,10 @@
         <v>155</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>124</v>
@@ -16128,10 +16390,10 @@
         <v>156</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>21</v>
@@ -16171,10 +16433,10 @@
         <v>157</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>294</v>
@@ -16214,10 +16476,10 @@
         <v>158</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>156</v>
@@ -16257,10 +16519,10 @@
         <v>159</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>185</v>
@@ -16300,10 +16562,10 @@
         <v>160</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>21</v>
@@ -16343,10 +16605,10 @@
         <v>161</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C166" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>499</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>21</v>
@@ -16386,10 +16648,10 @@
         <v>162</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C167" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>156</v>
@@ -16429,10 +16691,10 @@
         <v>163</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>352</v>
@@ -16472,10 +16734,10 @@
         <v>164</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>21</v>
@@ -16515,13 +16777,13 @@
         <v>165</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>378</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E170" s="24"/>
       <c r="F170" s="17"/>
@@ -16558,10 +16820,10 @@
         <v>166</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>21</v>
@@ -16601,10 +16863,10 @@
         <v>167</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>21</v>
@@ -16644,10 +16906,10 @@
         <v>168</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>219</v>
@@ -16687,10 +16949,10 @@
         <v>169</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>185</v>
@@ -16730,10 +16992,10 @@
         <v>170</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>21</v>
@@ -16773,10 +17035,10 @@
         <v>171</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>21</v>
@@ -16816,10 +17078,10 @@
         <v>172</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>21</v>
@@ -16859,10 +17121,10 @@
         <v>173</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>21</v>
@@ -16902,10 +17164,10 @@
         <v>174</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>21</v>
@@ -16945,13 +17207,13 @@
         <v>175</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C180" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C180" s="3" t="s">
-        <v>527</v>
-      </c>
       <c r="D180" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E180" s="24"/>
       <c r="F180" s="17"/>
@@ -16988,10 +17250,10 @@
         <v>176</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>21</v>
@@ -17031,10 +17293,10 @@
         <v>177</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>21</v>
@@ -17074,10 +17336,10 @@
         <v>178</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>21</v>
@@ -18019,17 +18281,17 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="95" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.85546875" style="95" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="95" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="95" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.28515625" style="95" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="95"/>
+    <col min="1" max="1" width="5.42578125" style="94" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.85546875" style="94" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="94" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="94" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" style="94" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="94"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -18037,227 +18299,227 @@
         <v>2</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="D2" s="74" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F2" s="75" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="75" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="H2" s="75" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="95" t="s">
-        <v>718</v>
+      <c r="B3" s="94" t="s">
+        <v>715</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>719</v>
-      </c>
-      <c r="D3" s="95" t="s">
+        <v>716</v>
+      </c>
+      <c r="D3" s="94" t="s">
+        <v>724</v>
+      </c>
+      <c r="E3" s="95">
+        <v>45757</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>473</v>
+      </c>
+      <c r="G3" s="96">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" s="94" t="s">
+        <v>689</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>689</v>
+      </c>
+      <c r="D4" s="94" t="s">
+        <v>722</v>
+      </c>
+      <c r="E4" s="95">
+        <v>45782</v>
+      </c>
+      <c r="F4" s="97" t="s">
+        <v>723</v>
+      </c>
+      <c r="G4" s="98">
+        <v>9420</v>
+      </c>
+      <c r="H4" s="94" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="94" t="s">
+        <v>725</v>
+      </c>
+      <c r="E5" s="95">
+        <v>45637</v>
+      </c>
+      <c r="F5" s="96" t="s">
+        <v>473</v>
+      </c>
+      <c r="G5" s="98">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="94" t="s">
+        <v>726</v>
+      </c>
+      <c r="C6" s="94" t="s">
+        <v>726</v>
+      </c>
+      <c r="D6" s="94" t="s">
         <v>727</v>
       </c>
-      <c r="E3" s="96">
-        <v>45757</v>
-      </c>
-      <c r="F3" s="97" t="s">
-        <v>474</v>
-      </c>
-      <c r="G3" s="97">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="B4" s="95" t="s">
-        <v>692</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>692</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>725</v>
-      </c>
-      <c r="E4" s="96">
-        <v>45782</v>
-      </c>
-      <c r="F4" s="98" t="s">
-        <v>726</v>
-      </c>
-      <c r="G4" s="99">
-        <v>9420</v>
-      </c>
-      <c r="H4" s="95" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>728</v>
-      </c>
-      <c r="E5" s="96">
-        <v>45637</v>
-      </c>
-      <c r="F5" s="97" t="s">
-        <v>474</v>
-      </c>
-      <c r="G5" s="99">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="95" t="s">
-        <v>729</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>729</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>730</v>
-      </c>
-      <c r="E6" s="96">
+      <c r="E6" s="95">
         <v>45669</v>
       </c>
-      <c r="F6" s="107" t="s">
-        <v>474</v>
-      </c>
-      <c r="G6" s="99">
+      <c r="F6" s="106" t="s">
+        <v>473</v>
+      </c>
+      <c r="G6" s="98">
         <v>2200</v>
       </c>
-      <c r="H6" s="95" t="s">
-        <v>897</v>
+      <c r="H6" s="94" t="s">
+        <v>893</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="94" t="s">
         <v>191</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="95" t="s">
-        <v>680</v>
-      </c>
-      <c r="E7" s="96">
+      <c r="D7" s="94" t="s">
+        <v>678</v>
+      </c>
+      <c r="E7" s="95">
         <v>45889</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="94">
         <v>16.75</v>
       </c>
-      <c r="G7" s="95" t="s">
-        <v>797</v>
-      </c>
-      <c r="H7" s="95" t="s">
-        <v>796</v>
+      <c r="G7" s="94" t="s">
+        <v>794</v>
+      </c>
+      <c r="H7" s="94" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="94" t="s">
         <v>420</v>
       </c>
-      <c r="C8" s="100" t="s">
-        <v>476</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>802</v>
-      </c>
-      <c r="E8" s="96">
+      <c r="C8" s="99" t="s">
+        <v>474</v>
+      </c>
+      <c r="D8" s="94" t="s">
+        <v>799</v>
+      </c>
+      <c r="E8" s="95">
         <v>45322</v>
       </c>
-      <c r="G8" s="95">
+      <c r="G8" s="94">
         <v>500</v>
       </c>
-      <c r="H8" s="95" t="s">
+      <c r="H8" s="94" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="94" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="95" t="s">
-        <v>806</v>
-      </c>
-      <c r="C9" s="95" t="s">
-        <v>807</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>689</v>
-      </c>
-      <c r="E9" s="96">
+      <c r="C9" s="94" t="s">
+        <v>804</v>
+      </c>
+      <c r="D9" s="94" t="s">
+        <v>686</v>
+      </c>
+      <c r="E9" s="95">
         <v>45808</v>
       </c>
-      <c r="G9" s="95">
+      <c r="G9" s="94">
         <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10" s="95" t="s">
+      <c r="B10" s="94" t="s">
+        <v>861</v>
+      </c>
+      <c r="C10" s="94" t="s">
+        <v>861</v>
+      </c>
+      <c r="D10" s="94" t="s">
+        <v>860</v>
+      </c>
+      <c r="E10" s="95">
+        <v>46112</v>
+      </c>
+      <c r="F10" s="97" t="s">
+        <v>473</v>
+      </c>
+      <c r="G10" s="94">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="94" t="s">
+        <v>862</v>
+      </c>
+      <c r="C11" s="94" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="94" t="s">
+        <v>863</v>
+      </c>
+      <c r="E11" s="95">
+        <v>46156</v>
+      </c>
+      <c r="F11" s="97" t="s">
+        <v>473</v>
+      </c>
+      <c r="G11" s="94">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="94" t="s">
+        <v>865</v>
+      </c>
+      <c r="C12" s="94" t="s">
+        <v>867</v>
+      </c>
+      <c r="D12" s="94" t="s">
         <v>864</v>
       </c>
-      <c r="C10" s="95" t="s">
-        <v>864</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>863</v>
-      </c>
-      <c r="E10" s="96">
-        <v>46112</v>
-      </c>
-      <c r="F10" s="98" t="s">
-        <v>474</v>
-      </c>
-      <c r="G10" s="95">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="95" t="s">
-        <v>866</v>
-      </c>
-      <c r="C11" s="95" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>867</v>
-      </c>
-      <c r="E11" s="96">
-        <v>46156</v>
-      </c>
-      <c r="F11" s="98" t="s">
-        <v>474</v>
-      </c>
-      <c r="G11" s="95">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="B12" s="95" t="s">
-        <v>869</v>
-      </c>
-      <c r="C12" s="95" t="s">
-        <v>871</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>868</v>
-      </c>
-      <c r="E12" s="96">
+      <c r="E12" s="95">
         <v>46160</v>
       </c>
-      <c r="F12" s="98" t="s">
-        <v>474</v>
-      </c>
-      <c r="G12" s="95">
+      <c r="F12" s="97" t="s">
+        <v>473</v>
+      </c>
+      <c r="G12" s="94">
         <v>100</v>
       </c>
     </row>
@@ -18287,7 +18549,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -18311,13 +18573,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="F2" s="45" t="s">
         <v>126</v>
@@ -18336,16 +18598,16 @@
     <row r="3" spans="1:16">
       <c r="A3" s="45"/>
       <c r="B3" s="45" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
@@ -18362,16 +18624,16 @@
     <row r="4" spans="1:16">
       <c r="A4" s="45"/>
       <c r="B4" s="45" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D4" s="45" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F4" s="45"/>
       <c r="G4" s="45"/>
@@ -18388,19 +18650,19 @@
     <row r="5" spans="1:16">
       <c r="A5" s="45"/>
       <c r="B5" s="45" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D5" s="45" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="45" t="s">
+        <v>732</v>
+      </c>
+      <c r="F5" s="45" t="s">
         <v>735</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>738</v>
       </c>
       <c r="G5" s="45"/>
       <c r="H5" s="45"/>
@@ -18416,16 +18678,16 @@
     <row r="6" spans="1:16">
       <c r="A6" s="45"/>
       <c r="B6" s="45" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
@@ -18442,19 +18704,19 @@
     <row r="7" spans="1:16">
       <c r="A7" s="45"/>
       <c r="B7" s="45" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D7" s="45" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="G7" s="45"/>
       <c r="H7" s="45"/>
@@ -18473,16 +18735,16 @@
         <v>135</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>135</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F8" s="45" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="G8" s="45"/>
       <c r="H8" s="45"/>
@@ -18498,19 +18760,19 @@
     <row r="9" spans="1:16">
       <c r="A9" s="45"/>
       <c r="B9" s="45" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E9" s="45" t="s">
+        <v>745</v>
+      </c>
+      <c r="F9" s="45" t="s">
         <v>748</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>751</v>
       </c>
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
@@ -18526,19 +18788,19 @@
     <row r="10" spans="1:16">
       <c r="A10" s="45"/>
       <c r="B10" s="45" t="s">
+        <v>749</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>750</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>751</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>745</v>
+      </c>
+      <c r="F10" s="45" t="s">
         <v>752</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>753</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>754</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>748</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>755</v>
       </c>
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
@@ -18554,19 +18816,19 @@
     <row r="11" spans="1:16">
       <c r="A11" s="45"/>
       <c r="B11" s="45" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D11" s="45" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="F11" s="45" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G11" s="45"/>
       <c r="H11" s="45"/>
@@ -18582,19 +18844,19 @@
     <row r="12" spans="1:16">
       <c r="A12" s="45"/>
       <c r="B12" s="45" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D12" s="45" t="s">
         <v>123</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="G12" s="45"/>
       <c r="H12" s="45"/>
@@ -18610,16 +18872,16 @@
     <row r="13" spans="1:16">
       <c r="A13" s="45"/>
       <c r="B13" s="45" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D13" s="45" t="s">
         <v>135</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="45"/>
@@ -18636,16 +18898,16 @@
     <row r="14" spans="1:16">
       <c r="A14" s="45"/>
       <c r="B14" s="45" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D14" s="45" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F14" s="45"/>
       <c r="G14" s="45"/>
@@ -18662,16 +18924,16 @@
     <row r="15" spans="1:16">
       <c r="A15" s="45"/>
       <c r="B15" s="45" t="s">
+        <v>766</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>767</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>768</v>
+      </c>
+      <c r="E15" s="45" t="s">
         <v>769</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>770</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>771</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>772</v>
       </c>
       <c r="F15" s="45"/>
       <c r="G15" s="45"/>
@@ -18688,19 +18950,19 @@
     <row r="16" spans="1:16">
       <c r="A16" s="45"/>
       <c r="B16" s="45" t="s">
+        <v>771</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>772</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>773</v>
+      </c>
+      <c r="E16" s="45" t="s">
         <v>774</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="F16" s="45" t="s">
         <v>775</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>776</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>777</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>778</v>
       </c>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -18716,16 +18978,16 @@
     <row r="17" spans="1:16">
       <c r="A17" s="45"/>
       <c r="B17" s="45" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45"/>
@@ -18777,7 +19039,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="B20" s="74" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="45"/>
@@ -18797,16 +19059,16 @@
     <row r="21" spans="1:16">
       <c r="A21" s="45"/>
       <c r="B21" s="89" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D21" s="77" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="E21" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
@@ -18823,13 +19085,13 @@
     <row r="22" spans="1:16">
       <c r="A22" s="45"/>
       <c r="B22" s="45" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D22" s="77" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
@@ -18847,16 +19109,16 @@
     <row r="23" spans="1:16">
       <c r="A23" s="45"/>
       <c r="B23" s="45" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D23" s="77" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E23" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
@@ -18873,16 +19135,16 @@
     <row r="24" spans="1:16">
       <c r="A24" s="45"/>
       <c r="B24" s="45" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E24" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F24" s="45"/>
       <c r="G24" s="45"/>
@@ -18902,13 +19164,13 @@
         <v>98</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D25" s="77" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
@@ -18925,16 +19187,16 @@
     <row r="26" spans="1:16">
       <c r="A26" s="45"/>
       <c r="B26" s="45" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D26" s="77" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E26" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F26" s="45"/>
       <c r="G26" s="45"/>
@@ -18951,16 +19213,16 @@
     <row r="27" spans="1:16">
       <c r="A27" s="45"/>
       <c r="B27" s="45" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D27" s="77" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E27" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
@@ -18977,16 +19239,16 @@
     <row r="28" spans="1:16">
       <c r="A28" s="45"/>
       <c r="B28" s="45" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D28" s="77" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E28" s="77" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F28" s="45"/>
       <c r="G28" s="45"/>
@@ -19006,7 +19268,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="89" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D29" s="45"/>
       <c r="E29" s="45"/>
@@ -19058,72 +19320,72 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="B2" s="90" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="44" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -19137,7 +19399,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FC56C3-8711-45A1-8A34-862C4185F0B3}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -19147,7 +19409,7 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -19186,13 +19448,21 @@
       <c r="Q2" s="45"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="45"/>
+      <c r="A3" s="113" t="s">
+        <v>315</v>
+      </c>
       <c r="B3" s="72" t="s">
-        <v>804</v>
-      </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="58"/>
+        <v>801</v>
+      </c>
+      <c r="C3" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="112" t="s">
+        <v>903</v>
+      </c>
       <c r="F3" s="56"/>
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
@@ -19208,14 +19478,16 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="45"/>
-      <c r="B4" s="109" t="s">
-        <v>434</v>
-      </c>
-      <c r="C4" s="110" t="s">
-        <v>903</v>
+      <c r="B4" s="45" t="s">
+        <v>472</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>124</v>
       </c>
       <c r="D4" s="45"/>
-      <c r="E4" s="58"/>
+      <c r="E4" s="110" t="s">
+        <v>984</v>
+      </c>
       <c r="F4" s="56"/>
       <c r="G4" s="56"/>
       <c r="H4" s="56"/>
@@ -19232,16 +19504,14 @@
     <row r="5" spans="1:17">
       <c r="A5" s="45"/>
       <c r="B5" s="45" t="s">
-        <v>473</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>474</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>475</v>
+        <v>675</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="45"/>
+      <c r="E5" s="110" t="s">
+        <v>675</v>
       </c>
       <c r="F5" s="56"/>
       <c r="G5" s="56"/>
@@ -19259,11 +19529,15 @@
     <row r="6" spans="1:17">
       <c r="A6" s="45"/>
       <c r="B6" s="45" t="s">
-        <v>677</v>
-      </c>
-      <c r="C6" s="57"/>
+        <v>676</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>905</v>
+      </c>
       <c r="D6" s="45"/>
-      <c r="E6" s="58"/>
+      <c r="E6" s="110" t="s">
+        <v>985</v>
+      </c>
       <c r="F6" s="56"/>
       <c r="G6" s="56"/>
       <c r="H6" s="56"/>
@@ -19280,11 +19554,15 @@
     <row r="7" spans="1:17">
       <c r="A7" s="45"/>
       <c r="B7" s="45" t="s">
-        <v>678</v>
-      </c>
-      <c r="C7" s="57"/>
+        <v>677</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>972</v>
+      </c>
       <c r="D7" s="45"/>
-      <c r="E7" s="58"/>
+      <c r="E7" s="110" t="s">
+        <v>431</v>
+      </c>
       <c r="F7" s="56"/>
       <c r="G7" s="56"/>
       <c r="H7" s="56"/>
@@ -19300,12 +19578,16 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="45"/>
-      <c r="B8" s="45" t="s">
-        <v>679</v>
-      </c>
-      <c r="C8" s="57"/>
+      <c r="B8" s="108" t="s">
+        <v>901</v>
+      </c>
+      <c r="C8" s="92" t="s">
+        <v>905</v>
+      </c>
       <c r="D8" s="45"/>
-      <c r="E8" s="58"/>
+      <c r="E8" s="109" t="s">
+        <v>902</v>
+      </c>
       <c r="F8" s="56"/>
       <c r="G8" s="56"/>
       <c r="H8" s="56"/>
@@ -19322,11 +19604,15 @@
     <row r="9" spans="1:17">
       <c r="A9" s="45"/>
       <c r="B9" s="45" t="s">
-        <v>680</v>
-      </c>
-      <c r="C9" s="57"/>
+        <v>678</v>
+      </c>
+      <c r="C9" s="109" t="s">
+        <v>972</v>
+      </c>
       <c r="D9" s="45"/>
-      <c r="E9" s="58"/>
+      <c r="E9" s="110" t="s">
+        <v>986</v>
+      </c>
       <c r="F9" s="56"/>
       <c r="G9" s="56"/>
       <c r="H9" s="56"/>
@@ -19343,11 +19629,15 @@
     <row r="10" spans="1:17">
       <c r="A10" s="45"/>
       <c r="B10" s="45" t="s">
-        <v>681</v>
-      </c>
-      <c r="C10" s="57"/>
+        <v>679</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>905</v>
+      </c>
       <c r="D10" s="45"/>
-      <c r="E10" s="58"/>
+      <c r="E10" s="110" t="s">
+        <v>118</v>
+      </c>
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
       <c r="H10" s="56"/>
@@ -19364,11 +19654,15 @@
     <row r="11" spans="1:17">
       <c r="A11" s="45"/>
       <c r="B11" s="45" t="s">
-        <v>682</v>
-      </c>
-      <c r="C11" s="57"/>
+        <v>680</v>
+      </c>
+      <c r="C11" s="109" t="s">
+        <v>165</v>
+      </c>
       <c r="D11" s="45"/>
-      <c r="E11" s="58"/>
+      <c r="E11" s="110" t="s">
+        <v>680</v>
+      </c>
       <c r="F11" s="56"/>
       <c r="G11" s="56"/>
       <c r="H11" s="56"/>
@@ -19385,11 +19679,15 @@
     <row r="12" spans="1:17">
       <c r="A12" s="45"/>
       <c r="B12" s="45" t="s">
-        <v>683</v>
-      </c>
-      <c r="C12" s="57"/>
+        <v>681</v>
+      </c>
+      <c r="C12" s="109" t="s">
+        <v>905</v>
+      </c>
       <c r="D12" s="45"/>
-      <c r="E12" s="58"/>
+      <c r="E12" s="110" t="s">
+        <v>987</v>
+      </c>
       <c r="F12" s="56"/>
       <c r="G12" s="56"/>
       <c r="H12" s="56"/>
@@ -19406,11 +19704,15 @@
     <row r="13" spans="1:17">
       <c r="A13" s="45"/>
       <c r="B13" s="45" t="s">
-        <v>684</v>
-      </c>
-      <c r="C13" s="45"/>
+        <v>682</v>
+      </c>
+      <c r="C13" s="108" t="s">
+        <v>905</v>
+      </c>
       <c r="D13" s="45"/>
-      <c r="E13" s="58"/>
+      <c r="E13" s="110" t="s">
+        <v>988</v>
+      </c>
       <c r="F13" s="56"/>
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
@@ -19427,11 +19729,15 @@
     <row r="14" spans="1:17">
       <c r="A14" s="45"/>
       <c r="B14" s="45" t="s">
-        <v>685</v>
-      </c>
-      <c r="C14" s="57"/>
+        <v>683</v>
+      </c>
+      <c r="C14" s="109" t="s">
+        <v>972</v>
+      </c>
       <c r="D14" s="45"/>
-      <c r="E14" s="58"/>
+      <c r="E14" s="110" t="s">
+        <v>989</v>
+      </c>
       <c r="F14" s="56"/>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
@@ -19448,13 +19754,15 @@
     <row r="15" spans="1:17">
       <c r="A15" s="45"/>
       <c r="B15" s="92" t="s">
-        <v>862</v>
-      </c>
-      <c r="C15" s="93" t="s">
-        <v>865</v>
+        <v>859</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>972</v>
       </c>
       <c r="D15" s="45"/>
-      <c r="E15" s="58"/>
+      <c r="E15" s="110" t="s">
+        <v>983</v>
+      </c>
       <c r="F15" s="56"/>
       <c r="G15" s="56"/>
       <c r="H15" s="56"/>
@@ -19470,14 +19778,16 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="45"/>
-      <c r="B16" s="45" t="s">
-        <v>686</v>
-      </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
+      <c r="B16" s="92" t="s">
+        <v>684</v>
+      </c>
+      <c r="C16" s="108" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
       <c r="H16" s="56"/>
       <c r="I16" s="46"/>
       <c r="J16" s="45"/>
@@ -19491,35 +19801,30 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="45"/>
-      <c r="B17" s="45" t="s">
-        <v>687</v>
-      </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
+      <c r="B17" s="92" t="s">
+        <v>904</v>
+      </c>
+      <c r="C17" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="E17" s="92" t="s">
+        <v>906</v>
+      </c>
+      <c r="F17" s="92"/>
+      <c r="G17" s="92"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="45"/>
-      <c r="B18" s="45" t="s">
-        <v>695</v>
-      </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
+      <c r="B18" s="92" t="s">
+        <v>907</v>
+      </c>
+      <c r="C18" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
       <c r="H18" s="56"/>
       <c r="I18" s="46"/>
       <c r="J18" s="45"/>
@@ -19533,18 +19838,16 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="45"/>
-      <c r="B19" s="89" t="s">
-        <v>847</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>800</v>
-      </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="58" t="s">
-        <v>801</v>
-      </c>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+      <c r="B19" s="92" t="s">
+        <v>908</v>
+      </c>
+      <c r="C19" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
       <c r="H19" s="56"/>
       <c r="I19" s="46"/>
       <c r="J19" s="45"/>
@@ -19558,12 +19861,16 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="45"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
+      <c r="B20" s="92" t="s">
+        <v>909</v>
+      </c>
+      <c r="C20" s="92" t="s">
+        <v>910</v>
+      </c>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
       <c r="H20" s="56"/>
       <c r="I20" s="46"/>
       <c r="J20" s="45"/>
@@ -19577,14 +19884,16 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="45"/>
-      <c r="B21" s="77" t="s">
-        <v>819</v>
-      </c>
-      <c r="C21" s="57"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
+      <c r="B21" s="92" t="s">
+        <v>911</v>
+      </c>
+      <c r="C21" s="92" t="s">
+        <v>912</v>
+      </c>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
       <c r="H21" s="56"/>
       <c r="I21" s="46"/>
       <c r="J21" s="45"/>
@@ -19598,16 +19907,17 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="45"/>
-      <c r="B22" s="77" t="s">
-        <v>820</v>
-      </c>
-      <c r="C22" s="77" t="s">
-        <v>821</v>
-      </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
+      <c r="B22" s="92" t="s">
+        <v>913</v>
+      </c>
+      <c r="C22" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="92" t="s">
+        <v>914</v>
+      </c>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
       <c r="H22" s="56"/>
       <c r="I22" s="46"/>
       <c r="J22" s="45"/>
@@ -19621,12 +19931,17 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
+      <c r="B23" s="92" t="s">
+        <v>915</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="92" t="s">
+        <v>916</v>
+      </c>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
       <c r="H23" s="56"/>
       <c r="I23" s="46"/>
       <c r="J23" s="45"/>
@@ -19640,12 +19955,17 @@
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
+      <c r="B24" s="92" t="s">
+        <v>917</v>
+      </c>
+      <c r="C24" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="92" t="s">
+        <v>918</v>
+      </c>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
       <c r="H24" s="56"/>
       <c r="I24" s="46"/>
       <c r="J24" s="45"/>
@@ -19656,6 +19976,752 @@
       <c r="O24" s="45"/>
       <c r="P24" s="45"/>
       <c r="Q24" s="45"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="45"/>
+      <c r="B25" s="92" t="s">
+        <v>919</v>
+      </c>
+      <c r="C25" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="92" t="s">
+        <v>920</v>
+      </c>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="45"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="45"/>
+      <c r="B26" s="92" t="s">
+        <v>921</v>
+      </c>
+      <c r="C26" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="B27" s="92" t="s">
+        <v>922</v>
+      </c>
+      <c r="C27" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="B28" s="92" t="s">
+        <v>923</v>
+      </c>
+      <c r="C28" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="B29" s="92" t="s">
+        <v>924</v>
+      </c>
+      <c r="C29" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="B30" s="92" t="s">
+        <v>925</v>
+      </c>
+      <c r="C30" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="B31" s="92" t="s">
+        <v>926</v>
+      </c>
+      <c r="C31" s="92" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="B32" s="92" t="s">
+        <v>927</v>
+      </c>
+      <c r="C32" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="92" t="s">
+        <v>928</v>
+      </c>
+      <c r="C33" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="92"/>
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="92"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="92" t="s">
+        <v>929</v>
+      </c>
+      <c r="C34" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="92" t="s">
+        <v>930</v>
+      </c>
+      <c r="C35" s="92" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="92" t="s">
+        <v>931</v>
+      </c>
+      <c r="F35" s="92"/>
+      <c r="G35" s="92"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="92" t="s">
+        <v>932</v>
+      </c>
+      <c r="C36" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="92" t="s">
+        <v>933</v>
+      </c>
+      <c r="F36" s="92"/>
+      <c r="G36" s="92"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="92" t="s">
+        <v>934</v>
+      </c>
+      <c r="C37" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="92"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="92" t="s">
+        <v>935</v>
+      </c>
+      <c r="C38" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="92"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="92" t="s">
+        <v>936</v>
+      </c>
+      <c r="C39" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="92" t="s">
+        <v>937</v>
+      </c>
+      <c r="C40" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="92" t="s">
+        <v>938</v>
+      </c>
+      <c r="F40" s="92"/>
+      <c r="G40" s="92"/>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="92" t="s">
+        <v>939</v>
+      </c>
+      <c r="C41" s="92" t="s">
+        <v>912</v>
+      </c>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="92" t="s">
+        <v>940</v>
+      </c>
+      <c r="C42" s="92" t="s">
+        <v>912</v>
+      </c>
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="92"/>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="92" t="s">
+        <v>941</v>
+      </c>
+      <c r="C43" s="92" t="s">
+        <v>912</v>
+      </c>
+      <c r="E43" s="92" t="s">
+        <v>942</v>
+      </c>
+      <c r="F43" s="92"/>
+      <c r="G43" s="92"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="92" t="s">
+        <v>943</v>
+      </c>
+      <c r="C44" s="92" t="s">
+        <v>912</v>
+      </c>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="92"/>
+      <c r="G44" s="92"/>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="92" t="s">
+        <v>944</v>
+      </c>
+      <c r="C45" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="92" t="s">
+        <v>945</v>
+      </c>
+      <c r="F45" s="92"/>
+      <c r="G45" s="92"/>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="92" t="s">
+        <v>946</v>
+      </c>
+      <c r="C46" s="92" t="s">
+        <v>947</v>
+      </c>
+      <c r="E46" s="92" t="s">
+        <v>948</v>
+      </c>
+      <c r="F46" s="92"/>
+      <c r="G46" s="92"/>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="92" t="s">
+        <v>949</v>
+      </c>
+      <c r="C47" s="92" t="s">
+        <v>947</v>
+      </c>
+      <c r="D47" s="92"/>
+      <c r="E47" s="92"/>
+      <c r="F47" s="92"/>
+      <c r="G47" s="92"/>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="92" t="s">
+        <v>950</v>
+      </c>
+      <c r="C48" s="92" t="s">
+        <v>951</v>
+      </c>
+      <c r="D48" s="92"/>
+      <c r="E48" s="92"/>
+      <c r="F48" s="92"/>
+      <c r="G48" s="92"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="92" t="s">
+        <v>952</v>
+      </c>
+      <c r="C49" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="92" t="s">
+        <v>953</v>
+      </c>
+      <c r="F49" s="92"/>
+      <c r="G49" s="92"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="92" t="s">
+        <v>954</v>
+      </c>
+      <c r="C50" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="92" t="s">
+        <v>955</v>
+      </c>
+      <c r="F50" s="92"/>
+      <c r="G50" s="92"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="92" t="s">
+        <v>956</v>
+      </c>
+      <c r="C51" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="92" t="s">
+        <v>957</v>
+      </c>
+      <c r="F51" s="92"/>
+      <c r="G51" s="92"/>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="92" t="s">
+        <v>958</v>
+      </c>
+      <c r="C52" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="92" t="s">
+        <v>959</v>
+      </c>
+      <c r="F52" s="92"/>
+      <c r="G52" s="92"/>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="92" t="s">
+        <v>960</v>
+      </c>
+      <c r="C53" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="92" t="s">
+        <v>961</v>
+      </c>
+      <c r="F53" s="92"/>
+      <c r="G53" s="92"/>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="92" t="s">
+        <v>962</v>
+      </c>
+      <c r="C54" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="92"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="92"/>
+      <c r="G54" s="92"/>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="92" t="s">
+        <v>963</v>
+      </c>
+      <c r="C55" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="92"/>
+      <c r="E55" s="92"/>
+      <c r="F55" s="92"/>
+      <c r="G55" s="92"/>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="92" t="s">
+        <v>964</v>
+      </c>
+      <c r="C56" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+      <c r="G56" s="92"/>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="92" t="s">
+        <v>965</v>
+      </c>
+      <c r="C57" s="92" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="92"/>
+      <c r="E57" s="92"/>
+      <c r="F57" s="92"/>
+      <c r="G57" s="92"/>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="92" t="s">
+        <v>966</v>
+      </c>
+      <c r="C58" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="E58" s="92" t="s">
+        <v>967</v>
+      </c>
+      <c r="F58" s="92"/>
+      <c r="G58" s="92"/>
+    </row>
+    <row r="59" spans="2:7">
+      <c r="B59" s="92" t="s">
+        <v>968</v>
+      </c>
+      <c r="C59" s="92" t="s">
+        <v>969</v>
+      </c>
+      <c r="D59" s="92"/>
+      <c r="E59" s="92"/>
+      <c r="F59" s="92"/>
+      <c r="G59" s="92"/>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="92" t="s">
+        <v>970</v>
+      </c>
+      <c r="C60" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="92"/>
+      <c r="E60" s="92"/>
+      <c r="F60" s="92"/>
+      <c r="G60" s="92"/>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="92" t="s">
+        <v>971</v>
+      </c>
+      <c r="C61" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D61" s="92"/>
+      <c r="E61" s="92"/>
+      <c r="F61" s="92"/>
+      <c r="G61" s="92"/>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="92" t="s">
+        <v>973</v>
+      </c>
+      <c r="C62" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="B63" s="92" t="s">
+        <v>974</v>
+      </c>
+      <c r="C63" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D63" s="92"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="92"/>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="92" t="s">
+        <v>975</v>
+      </c>
+      <c r="C64" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="B65" s="92" t="s">
+        <v>976</v>
+      </c>
+      <c r="C65" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D65" s="92"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="92"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="B66" s="92" t="s">
+        <v>977</v>
+      </c>
+      <c r="C66" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="B67" s="92" t="s">
+        <v>978</v>
+      </c>
+      <c r="C67" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D67" s="92"/>
+      <c r="E67" s="92"/>
+      <c r="F67" s="92"/>
+      <c r="G67" s="92"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="B68" s="92" t="s">
+        <v>979</v>
+      </c>
+      <c r="C68" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="D68" s="92"/>
+      <c r="E68" s="92"/>
+      <c r="F68" s="92"/>
+      <c r="G68" s="92"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="B69" s="92" t="s">
+        <v>980</v>
+      </c>
+      <c r="C69" s="92" t="s">
+        <v>972</v>
+      </c>
+      <c r="E69" s="92" t="s">
+        <v>981</v>
+      </c>
+      <c r="F69" s="92"/>
+      <c r="G69" s="92"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="B70" s="92" t="s">
+        <v>982</v>
+      </c>
+      <c r="C70" s="92" t="s">
+        <v>896</v>
+      </c>
+      <c r="D70" s="92"/>
+      <c r="E70" s="92"/>
+      <c r="F70" s="92"/>
+      <c r="G70" s="92"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="B71" s="92"/>
+      <c r="C71" s="92"/>
+      <c r="D71" s="92"/>
+      <c r="E71" s="92"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="92"/>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="B72" s="45" t="s">
+        <v>692</v>
+      </c>
+      <c r="C72" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" s="108" t="s">
+        <v>990</v>
+      </c>
+      <c r="E72" s="92"/>
+      <c r="F72" s="92"/>
+      <c r="G72" s="92"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="B73" s="89" t="s">
+        <v>844</v>
+      </c>
+      <c r="C73" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" s="57" t="s">
+        <v>797</v>
+      </c>
+      <c r="F73" s="92"/>
+      <c r="G73" s="92"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="D74" s="92"/>
+      <c r="E74" s="92"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="92"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="113" t="s">
+        <v>315</v>
+      </c>
+      <c r="B75" s="72" t="s">
+        <v>816</v>
+      </c>
+      <c r="C75" s="109"/>
+      <c r="D75" s="92"/>
+      <c r="E75" s="92"/>
+      <c r="F75" s="92"/>
+      <c r="G75" s="92"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="B76" s="77" t="s">
+        <v>817</v>
+      </c>
+      <c r="C76" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" s="92"/>
+      <c r="E76" s="77" t="s">
+        <v>818</v>
+      </c>
+      <c r="F76" s="92"/>
+      <c r="G76" s="92"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="B77" s="92"/>
+      <c r="C77" s="92"/>
+      <c r="D77" s="92"/>
+      <c r="E77" s="92"/>
+      <c r="F77" s="92"/>
+      <c r="G77" s="92"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="B78" s="92"/>
+      <c r="C78" s="92"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="92"/>
+      <c r="F78" s="92"/>
+      <c r="G78" s="92"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="B79" s="92"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="92"/>
+      <c r="F79" s="92"/>
+      <c r="G79" s="92"/>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="B80" s="92"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="92"/>
+      <c r="F80" s="92"/>
+      <c r="G80" s="92"/>
+    </row>
+    <row r="81" spans="2:17">
+      <c r="B81" s="92"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="92"/>
+      <c r="F81" s="92"/>
+      <c r="G81" s="92"/>
+    </row>
+    <row r="82" spans="2:17">
+      <c r="B82" s="92"/>
+      <c r="C82" s="92"/>
+      <c r="D82" s="92"/>
+      <c r="E82" s="92"/>
+      <c r="F82" s="92"/>
+      <c r="G82" s="92"/>
+    </row>
+    <row r="83" spans="2:17">
+      <c r="B83" s="92"/>
+      <c r="C83" s="92"/>
+      <c r="D83" s="92"/>
+      <c r="E83" s="92"/>
+      <c r="F83" s="92"/>
+      <c r="G83" s="92"/>
+    </row>
+    <row r="86" spans="2:17">
+      <c r="D86" s="45"/>
+      <c r="E86" s="58"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="56"/>
+      <c r="H86" s="56"/>
+      <c r="I86" s="46"/>
+      <c r="J86" s="45"/>
+      <c r="K86" s="45"/>
+      <c r="L86" s="45"/>
+      <c r="M86" s="45"/>
+      <c r="N86" s="45"/>
+      <c r="O86" s="45"/>
+      <c r="P86" s="45"/>
+      <c r="Q86" s="45"/>
+    </row>
+    <row r="87" spans="2:17">
+      <c r="D87" s="45"/>
+      <c r="E87" s="58" t="s">
+        <v>798</v>
+      </c>
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="56"/>
+      <c r="I87" s="46"/>
+      <c r="J87" s="45"/>
+      <c r="K87" s="45"/>
+      <c r="L87" s="45"/>
+      <c r="M87" s="45"/>
+      <c r="N87" s="45"/>
+      <c r="O87" s="45"/>
+      <c r="P87" s="45"/>
+      <c r="Q87" s="45"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19679,7 +20745,7 @@
   <sheetData>
     <row r="1" spans="1:38">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -19785,10 +20851,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="49" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" s="49" t="s">
         <v>442</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>443</v>
       </c>
       <c r="K3" s="50" t="s">
         <v>147</v>
@@ -19842,10 +20908,10 @@
         <v>79</v>
       </c>
       <c r="AB3" s="50" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC3" s="48" t="s">
         <v>435</v>
-      </c>
-      <c r="AC3" s="48" t="s">
-        <v>436</v>
       </c>
       <c r="AD3" s="53" t="s">
         <v>398</v>
@@ -19966,13 +21032,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C6" s="45" t="s">
         <v>106</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E6" s="45"/>
       <c r="F6" s="56"/>
@@ -20015,13 +21081,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E7" s="45"/>
       <c r="F7" s="56"/>
@@ -20064,7 +21130,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C8" s="45" t="s">
         <v>17</v>
@@ -20162,7 +21228,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C10" s="45" t="s">
         <v>23</v>
@@ -20260,7 +21326,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C12" s="45" t="s">
         <v>29</v>
@@ -20315,7 +21381,7 @@
         <v>39</v>
       </c>
       <c r="D13" s="45" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E13" s="45"/>
       <c r="F13" s="56"/>
@@ -20410,10 +21476,10 @@
         <v>388</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E15" s="45"/>
       <c r="F15" s="56"/>
@@ -20554,7 +21620,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>280</v>
@@ -20603,34 +21669,34 @@
         <v>16</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D19" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="105">
-        <f>+[79]Main!$J$2</f>
+      <c r="E19" s="104">
+        <f>+[72]Main!$J$2</f>
         <v>19.989999999999998</v>
       </c>
       <c r="F19" s="56">
-        <f>+[79]Main!$J$4</f>
+        <f>+[72]Main!$J$4</f>
         <v>1640.5061166099999</v>
       </c>
       <c r="G19" s="56">
-        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
+        <f>+[72]Main!$J$6-[72]Main!$J$5</f>
         <v>388.6</v>
       </c>
       <c r="H19" s="56">
         <f>+F19+G19</f>
         <v>2029.1061166099998</v>
       </c>
-      <c r="I19" s="106" t="s">
-        <v>805</v>
-      </c>
-      <c r="J19" s="105"/>
+      <c r="I19" s="105" t="s">
+        <v>802</v>
+      </c>
+      <c r="J19" s="104"/>
       <c r="K19" s="45"/>
       <c r="L19" s="45"/>
       <c r="M19" s="45"/>
@@ -20666,32 +21732,32 @@
         <v>17</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="45">
-        <f>+[81]Main!$J$2</f>
+        <f>+[82]Main!$J$2</f>
         <v>127.52</v>
       </c>
       <c r="F20" s="56">
-        <f>+[81]Main!$J$4</f>
+        <f>+[82]Main!$J$4</f>
         <v>11289.983199999999</v>
       </c>
       <c r="G20" s="56">
-        <f>+[81]Main!$J$6-[81]Main!$J$5</f>
+        <f>+[82]Main!$J$6-[82]Main!$J$5</f>
         <v>992.61199999999997</v>
       </c>
       <c r="H20" s="56">
         <f>+F20+G20</f>
         <v>12282.595199999998</v>
       </c>
-      <c r="I20" s="108" t="s">
-        <v>805</v>
+      <c r="I20" s="107" t="s">
+        <v>802</v>
       </c>
       <c r="J20" s="60">
         <v>46350</v>
@@ -20731,10 +21797,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D21" s="45" t="s">
         <v>124</v>
@@ -20780,10 +21846,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D22" s="45" t="s">
         <v>124</v>
@@ -20829,16 +21895,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F23" s="56"/>
       <c r="G23" s="56"/>
@@ -20880,10 +21946,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D24" s="45" t="s">
         <v>21</v>
@@ -20929,10 +21995,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D25" s="45" t="s">
         <v>21</v>
@@ -20978,7 +22044,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C26" s="45" t="s">
         <v>43</v>
@@ -21027,10 +22093,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D27" s="45" t="s">
         <v>21</v>
@@ -21076,10 +22142,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D28" s="45" t="s">
         <v>165</v>
@@ -21125,7 +22191,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C29" s="45" t="s">
         <v>162</v>
@@ -21174,10 +22240,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D30" s="45" t="s">
         <v>21</v>
@@ -21223,10 +22289,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D31" s="45" t="s">
         <v>21</v>
@@ -21272,10 +22338,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D32" s="45" t="s">
         <v>21</v>
@@ -21321,13 +22387,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="C33" s="45" t="s">
         <v>525</v>
       </c>
-      <c r="C33" s="45" t="s">
-        <v>527</v>
-      </c>
       <c r="D33" s="45" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E33" s="45"/>
       <c r="F33" s="56"/>
@@ -21370,10 +22436,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D34" s="45" t="s">
         <v>21</v>
@@ -21419,10 +22485,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="45" t="s">
+        <v>707</v>
+      </c>
+      <c r="C35" s="45" t="s">
         <v>710</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>713</v>
       </c>
       <c r="D35" s="45" t="s">
         <v>21</v>
@@ -21468,10 +22534,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D36" s="45" t="s">
         <v>21</v>
@@ -31118,7 +32184,7 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -31155,7 +32221,7 @@
     </row>
     <row r="2" spans="1:34">
       <c r="A2" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -31216,10 +32282,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="49" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" s="49" t="s">
         <v>442</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>443</v>
       </c>
       <c r="K3" s="50" t="s">
         <v>147</v>
@@ -31273,10 +32339,10 @@
         <v>79</v>
       </c>
       <c r="AB3" s="50" t="s">
+        <v>434</v>
+      </c>
+      <c r="AC3" s="48" t="s">
         <v>435</v>
-      </c>
-      <c r="AC3" s="48" t="s">
-        <v>436</v>
       </c>
       <c r="AD3" s="53" t="s">
         <v>398</v>
@@ -31623,7 +32689,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C9" s="57" t="s">
         <v>346</v>
@@ -39238,7 +40304,7 @@
   <sheetData>
     <row r="1" spans="1:39">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -39281,7 +40347,7 @@
     </row>
     <row r="2" spans="1:39">
       <c r="A2" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -39330,7 +40396,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>19</v>
@@ -39348,10 +40414,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J3" s="69" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K3" s="67"/>
       <c r="L3" s="70"/>
@@ -39397,23 +40463,23 @@
         <v>20</v>
       </c>
       <c r="E4" s="58">
-        <f>+[82]Main!$I$2</f>
+        <f>+[83]Main!$I$2</f>
         <v>165.3</v>
       </c>
       <c r="F4" s="56">
-        <f>+[82]Main!$I$4*FX!C3</f>
+        <f>+[83]Main!$I$4*FX!C3</f>
         <v>78910.853010912018</v>
       </c>
       <c r="G4" s="56">
-        <f>+([82]Main!$I$6-[82]Main!$I$5)*FX!C3</f>
+        <f>+([83]Main!$I$6-[83]Main!$I$5)*FX!C3</f>
         <v>9857.1200000000008</v>
       </c>
       <c r="H4" s="56">
         <f>+F4+G4</f>
         <v>88767.973010912014</v>
       </c>
-      <c r="I4" s="104" t="s">
-        <v>805</v>
+      <c r="I4" s="103" t="s">
+        <v>802</v>
       </c>
       <c r="J4" s="60">
         <v>46315</v>
@@ -39463,25 +40529,25 @@
         <v>85</v>
       </c>
       <c r="E5" s="58">
-        <f>+[83]Main!$J$2</f>
+        <f>+[84]Main!$J$2</f>
         <v>157.35</v>
       </c>
       <c r="F5" s="56">
-        <f>+[83]Main!$J$5*FX!C7</f>
+        <f>+[84]Main!$J$5*FX!C7</f>
         <v>109823.20036800001</v>
       </c>
       <c r="G5" s="56">
-        <f>+([83]Main!$J$7-[83]Main!$J$6)*FX!C7</f>
+        <f>+([84]Main!$J$7-[84]Main!$J$6)*FX!C7</f>
         <v>243.04000000000002</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" ref="H5:H6" si="0">+F5+G5</f>
         <v>110066.240368</v>
       </c>
-      <c r="I5" s="103" t="s">
-        <v>872</v>
-      </c>
-      <c r="J5" s="102">
+      <c r="I5" s="102" t="s">
+        <v>868</v>
+      </c>
+      <c r="J5" s="101">
         <v>46339</v>
       </c>
       <c r="K5" s="58"/>
@@ -39520,32 +40586,32 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="58">
-        <f>+[84]Main!$K$2</f>
+        <f>+[85]Main!$K$2</f>
         <v>80.58</v>
       </c>
       <c r="F6" s="56">
-        <f>+[84]Main!$K$4</f>
+        <f>+[85]Main!$K$4</f>
         <v>29153.4342507</v>
       </c>
       <c r="G6" s="56">
-        <f>+([84]Main!$K$6-[84]Main!$K$5)</f>
+        <f>+([85]Main!$K$6-[85]Main!$K$5)</f>
         <v>4186</v>
       </c>
       <c r="H6" s="56">
         <f t="shared" si="0"/>
         <v>33339.434250699996</v>
       </c>
-      <c r="I6" s="94" t="s">
-        <v>818</v>
+      <c r="I6" s="93" t="s">
+        <v>815</v>
       </c>
       <c r="J6" s="60"/>
       <c r="K6" s="58"/>
@@ -39587,21 +40653,21 @@
         <v>421</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D7" s="45" t="s">
         <v>85</v>
       </c>
       <c r="E7" s="58">
-        <f>+[85]Main!$I$3</f>
+        <f>+[86]Main!$I$3</f>
         <v>177.95</v>
       </c>
       <c r="F7" s="56">
-        <f>+[85]Main!$I$5*FX!C7</f>
+        <f>+[86]Main!$I$5*FX!C7</f>
         <v>10344.705947284801</v>
       </c>
       <c r="G7" s="56">
-        <f>+([85]Main!$I$7-[85]Main!$I$6)*FX!C7</f>
+        <f>+([86]Main!$I$7-[86]Main!$I$6)*FX!C7</f>
         <v>-1336.16</v>
       </c>
       <c r="H7" s="56">
@@ -39756,7 +40822,7 @@
         <v>340</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E10" s="58"/>
       <c r="F10" s="56"/>
@@ -40706,7 +41772,7 @@
         <v>378</v>
       </c>
       <c r="D29" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="45"/>
@@ -40753,7 +41819,7 @@
         <v>429</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D30" s="45"/>
       <c r="E30" s="58"/>
@@ -40798,10 +41864,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D31" s="45" t="s">
         <v>124</v>
@@ -40848,10 +41914,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D32" s="45" t="s">
         <v>21</v>
@@ -40898,10 +41964,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D33" s="45" t="s">
         <v>82</v>
@@ -40948,13 +42014,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="45" t="s">
+        <v>538</v>
+      </c>
+      <c r="C34" s="57" t="s">
+        <v>539</v>
+      </c>
+      <c r="D34" s="45" t="s">
         <v>540</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>541</v>
-      </c>
-      <c r="D34" s="45" t="s">
-        <v>542</v>
       </c>
       <c r="E34" s="45"/>
       <c r="F34" s="45"/>
@@ -40998,10 +42064,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D35" s="45" t="s">
         <v>21</v>
@@ -41048,10 +42114,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D36" s="45" t="s">
         <v>21</v>
@@ -41098,10 +42164,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D37" s="45" t="s">
         <v>109</v>
@@ -41148,10 +42214,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D38" s="45" t="s">
         <v>124</v>
@@ -41198,10 +42264,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D39" s="45" t="s">
         <v>165</v>
@@ -41248,13 +42314,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D40" s="45" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E40" s="45"/>
       <c r="F40" s="45"/>
@@ -41298,10 +42364,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D41" s="45" t="s">
         <v>82</v>
@@ -41348,10 +42414,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D42" s="45" t="s">
         <v>21</v>
@@ -41398,10 +42464,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D43" s="45" t="s">
         <v>219</v>
@@ -41448,10 +42514,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D44" s="45" t="s">
         <v>21</v>
@@ -41498,10 +42564,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D45" s="45" t="s">
         <v>85</v>
@@ -41548,10 +42614,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D46" s="45" t="s">
         <v>21</v>
@@ -41598,10 +42664,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D47" s="45" t="s">
         <v>82</v>
@@ -41648,10 +42714,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C48" s="45" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D48" s="45" t="s">
         <v>100</v>
@@ -41748,10 +42814,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C50" s="45" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D50" s="45" t="s">
         <v>21</v>
@@ -41798,10 +42864,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C51" s="45" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D51" s="45" t="s">
         <v>20</v>
@@ -41848,10 +42914,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C52" s="45" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D52" s="45" t="s">
         <v>124</v>
@@ -41898,10 +42964,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C53" s="45" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D53" s="45" t="s">
         <v>223</v>
@@ -41948,13 +43014,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C54" s="45" t="s">
+        <v>574</v>
+      </c>
+      <c r="D54" s="45" t="s">
         <v>576</v>
-      </c>
-      <c r="D54" s="45" t="s">
-        <v>578</v>
       </c>
       <c r="E54" s="45"/>
       <c r="F54" s="45"/>
@@ -42550,7 +43616,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -42573,7 +43639,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -42602,7 +43668,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>19</v>
@@ -42620,13 +43686,13 @@
         <v>6</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J3" s="69" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K3" s="67" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="L3" s="70"/>
       <c r="M3" s="67"/>
@@ -42658,7 +43724,7 @@
       <c r="I4" s="45"/>
       <c r="J4" s="45"/>
       <c r="K4" s="89" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L4" s="45"/>
       <c r="M4" s="45"/>
@@ -42678,7 +43744,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D5" s="89" t="s">
         <v>20</v>
@@ -42690,7 +43756,7 @@
       <c r="I5" s="45"/>
       <c r="J5" s="45"/>
       <c r="K5" s="89" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L5" s="45"/>
       <c r="M5" s="45"/>
@@ -42707,7 +43773,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="89" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C6" s="89" t="s">
         <v>139</v>
@@ -42722,7 +43788,7 @@
       <c r="I6" s="45"/>
       <c r="J6" s="45"/>
       <c r="K6" s="89" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
@@ -42754,7 +43820,7 @@
       <c r="I7" s="45"/>
       <c r="J7" s="45"/>
       <c r="K7" s="89" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="L7" s="45"/>
       <c r="M7" s="45"/>
@@ -42786,7 +43852,7 @@
       <c r="I8" s="45"/>
       <c r="J8" s="45"/>
       <c r="K8" s="89" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L8" s="45"/>
       <c r="M8" s="45"/>
@@ -42818,7 +43884,7 @@
       <c r="I9" s="45"/>
       <c r="J9" s="45"/>
       <c r="K9" s="89" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="L9" s="45"/>
       <c r="M9" s="45"/>
@@ -42838,7 +43904,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D10" s="89" t="s">
         <v>20</v>
@@ -42850,7 +43916,7 @@
       <c r="I10" s="45"/>
       <c r="J10" s="45"/>
       <c r="K10" s="89" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="L10" s="45"/>
       <c r="M10" s="45"/>
@@ -42870,7 +43936,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D11" s="89" t="s">
         <v>165</v>
@@ -42882,7 +43948,7 @@
       <c r="I11" s="45"/>
       <c r="J11" s="45"/>
       <c r="K11" s="89" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L11" s="45"/>
       <c r="M11" s="45"/>
@@ -42944,7 +44010,7 @@
       <c r="I13" s="45"/>
       <c r="J13" s="45"/>
       <c r="K13" s="89" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L13" s="45"/>
       <c r="M13" s="45"/>
@@ -42976,7 +44042,7 @@
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
       <c r="K14" s="89" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L14" s="45"/>
       <c r="M14" s="45"/>
@@ -42993,10 +44059,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="89" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C15" s="89" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D15" s="89" t="s">
         <v>143</v>
@@ -43023,10 +44089,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C16" s="89" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D16" s="89" t="s">
         <v>219</v>
@@ -43038,7 +44104,7 @@
       <c r="I16" s="45"/>
       <c r="J16" s="45"/>
       <c r="K16" s="89" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L16" s="45"/>
       <c r="M16" s="45"/>
@@ -43055,7 +44121,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="89" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C17" s="89" t="s">
         <v>349</v>
@@ -43085,7 +44151,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="89" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C18" s="89" t="s">
         <v>46</v>
@@ -43130,7 +44196,7 @@
       <c r="I19" s="45"/>
       <c r="J19" s="45"/>
       <c r="K19" s="89" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="L19" s="45"/>
       <c r="M19" s="45"/>
@@ -43147,10 +44213,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="89" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C20" s="89" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D20" s="89" t="s">
         <v>21</v>
@@ -43183,7 +44249,7 @@
         <v>351</v>
       </c>
       <c r="D21" s="89" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
@@ -43207,10 +44273,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="89" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C22" s="89" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D22" s="89" t="s">
         <v>219</v>
@@ -43240,7 +44306,7 @@
         <v>421</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>85</v>
@@ -43267,7 +44333,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="89" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C24" s="89" t="s">
         <v>357</v>
@@ -43327,10 +44393,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="89" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C26" s="89" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D26" s="89" t="s">
         <v>21</v>
@@ -43992,7 +45058,7 @@
   <sheetData>
     <row r="1" spans="1:36">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -44032,7 +45098,7 @@
     </row>
     <row r="2" spans="1:36">
       <c r="A2" s="45" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
@@ -44078,7 +45144,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>19</v>
@@ -44096,10 +45162,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J3" s="69" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K3" s="67"/>
       <c r="L3" s="70"/>
@@ -44133,10 +45199,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D4" s="45" t="s">
         <v>21</v>
@@ -44180,10 +45246,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D5" s="45" t="s">
         <v>21</v>
@@ -44227,10 +45293,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D6" s="45" t="s">
         <v>21</v>
@@ -44274,10 +45340,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D7" s="45" t="s">
         <v>352</v>
@@ -44321,10 +45387,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D8" s="45" t="s">
         <v>21</v>
@@ -44368,10 +45434,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D9" s="45" t="s">
         <v>21</v>
@@ -44415,10 +45481,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D10" s="45" t="s">
         <v>21</v>
@@ -44462,10 +45528,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D11" s="45" t="s">
         <v>21</v>
@@ -44509,10 +45575,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D12" s="45" t="s">
         <v>109</v>
@@ -44556,10 +45622,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D13" s="45" t="s">
         <v>21</v>
@@ -44603,10 +45669,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D14" s="45" t="s">
         <v>21</v>
@@ -44650,13 +45716,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
@@ -44697,10 +45763,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D16" s="45" t="s">
         <v>21</v>
@@ -44744,10 +45810,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D17" s="45" t="s">
         <v>352</v>
@@ -44791,13 +45857,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D18" s="45" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E18" s="45"/>
       <c r="F18" s="45"/>
@@ -44838,10 +45904,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D19" s="45" t="s">
         <v>21</v>
@@ -44885,10 +45951,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>223</v>
@@ -44932,13 +45998,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
@@ -44979,7 +46045,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="45"/>
@@ -45022,10 +46088,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>124</v>
@@ -45069,13 +46135,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D24" s="45" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
@@ -45116,10 +46182,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D25" s="45" t="s">
         <v>219</v>
@@ -45163,13 +46229,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D26" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E26" s="45"/>
       <c r="F26" s="45"/>
@@ -45210,10 +46276,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D27" s="45" t="s">
         <v>21</v>
@@ -45257,10 +46323,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D28" s="45" t="s">
         <v>82</v>
@@ -45304,10 +46370,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D29" s="45" t="s">
         <v>21</v>
@@ -45351,10 +46417,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D30" s="45" t="s">
         <v>109</v>
@@ -45398,10 +46464,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D31" s="45" t="s">
         <v>165</v>
@@ -45445,13 +46511,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D32" s="45" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E32" s="45"/>
       <c r="F32" s="45"/>
@@ -45492,10 +46558,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D33" s="45" t="s">
         <v>21</v>
@@ -45539,10 +46605,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C34" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D34" s="45" t="s">
         <v>82</v>
@@ -45586,10 +46652,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D35" s="45" t="s">
         <v>21</v>
@@ -45633,10 +46699,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D36" s="45" t="s">
         <v>21</v>
@@ -45680,13 +46746,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D37" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E37" s="45"/>
       <c r="F37" s="45"/>
@@ -45727,13 +46793,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C38" s="45" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D38" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E38" s="45"/>
       <c r="F38" s="45"/>
@@ -45774,10 +46840,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C39" s="45" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D39" s="45" t="s">
         <v>21</v>
@@ -45821,13 +46887,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D40" s="45" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E40" s="45"/>
       <c r="F40" s="45"/>
@@ -45868,10 +46934,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D41" s="45" t="s">
         <v>21</v>
@@ -45915,10 +46981,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D42" s="45" t="s">
         <v>21</v>
@@ -45962,13 +47028,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C43" s="45" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D43" s="45" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E43" s="45"/>
       <c r="F43" s="45"/>
@@ -46009,10 +47075,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C44" s="45" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D44" s="45" t="s">
         <v>165</v>
@@ -46056,13 +47122,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D45" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E45" s="45"/>
       <c r="F45" s="45"/>
@@ -46103,10 +47169,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D46" s="45" t="s">
         <v>21</v>
@@ -46150,10 +47216,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D47" s="45" t="s">
         <v>21</v>
@@ -46197,10 +47263,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C48" s="45" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D48" s="45" t="s">
         <v>21</v>
@@ -50325,7 +51391,7 @@
   <sheetData>
     <row r="1" spans="1:34">
       <c r="A1" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="77"/>
@@ -50956,7 +52022,7 @@
     </row>
     <row r="19" spans="2:34">
       <c r="B19" s="77" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C19" s="77"/>
       <c r="D19" s="77"/>
@@ -50993,7 +52059,7 @@
     </row>
     <row r="20" spans="2:34">
       <c r="B20" s="77" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -51064,10 +52130,10 @@
     </row>
     <row r="6" spans="2:11">
       <c r="B6" s="45" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -51080,10 +52146,10 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
@@ -51096,10 +52162,10 @@
     </row>
     <row r="8" spans="2:11">
       <c r="B8" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D8" s="45"/>
       <c r="E8" s="45"/>
@@ -51112,10 +52178,10 @@
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="45" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
@@ -51128,10 +52194,10 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>467</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>468</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="45"/>
@@ -51144,10 +52210,10 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="45" t="s">
+        <v>468</v>
+      </c>
+      <c r="C11" s="45" t="s">
         <v>469</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>470</v>
       </c>
       <c r="D11" s="45"/>
       <c r="E11" s="45"/>
@@ -51160,10 +52226,10 @@
     </row>
     <row r="12" spans="2:11">
       <c r="B12" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>471</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>472</v>
       </c>
       <c r="D12" s="45"/>
       <c r="E12" s="45"/>
@@ -51176,10 +52242,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="76" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D13" s="45"/>
       <c r="E13" s="45"/>
@@ -51191,96 +52257,96 @@
       <c r="K13" s="45"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="101" t="s">
+      <c r="B14" s="100" t="s">
+        <v>870</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="100" t="s">
+        <v>872</v>
+      </c>
+      <c r="C15" s="100" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="100" t="s">
         <v>874</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C16" s="100" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="101" t="s">
+    <row r="17" spans="2:3">
+      <c r="B17" s="100" t="s">
         <v>876</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C17" s="100" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="101" t="s">
+    <row r="18" spans="2:3">
+      <c r="B18" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="100" t="s">
         <v>878</v>
       </c>
-      <c r="C16" s="101" t="s">
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="100" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="101" t="s">
+      <c r="C19" s="100" t="s">
         <v>880</v>
       </c>
-      <c r="C17" s="101" t="s">
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="100" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="101" t="s">
+      <c r="C20" s="100" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="101" t="s">
+    <row r="21" spans="2:3">
+      <c r="B21" s="100" t="s">
         <v>883</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C21" s="100" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="101" t="s">
+    <row r="22" spans="2:3">
+      <c r="B22" s="100" t="s">
         <v>885</v>
       </c>
-      <c r="C20" s="101" t="s">
+      <c r="C22" s="100" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="101" t="s">
+    <row r="23" spans="2:3">
+      <c r="B23" s="100" t="s">
         <v>887</v>
       </c>
-      <c r="C21" s="101" t="s">
+      <c r="C23" s="100" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="101" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" s="100" t="s">
         <v>889</v>
       </c>
-      <c r="C22" s="101" t="s">
+      <c r="C24" s="100" t="s">
         <v>890</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="101" t="s">
-        <v>891</v>
-      </c>
-      <c r="C23" s="101" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="101" t="s">
-        <v>893</v>
-      </c>
-      <c r="C24" s="101" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" s="44" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
   </sheetData>
@@ -51404,7 +52470,7 @@
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="45" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C15" s="73">
         <v>0.03</v>
